--- a/2026/BRIN 2970/Agosto/Agosto-BRIN2970.xlsx
+++ b/2026/BRIN 2970/Agosto/Agosto-BRIN2970.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\BRIN 2970\Agosto\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\BRIN 2970\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B6F7144-C2BB-4935-9F62-6F7C1B4BCF50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5D96D9F-0880-4A4B-BC09-0D7DCEE0A61C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="850" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -18,15 +18,20 @@
     <sheet name="ANOTACIONES" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$T$35</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$122</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$T$34</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$117</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="163">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -205,9 +210,6 @@
     <t>PREVISION ORDINARIA</t>
   </si>
   <si>
-    <t>Gustavo Padron - Sr. Contador</t>
-  </si>
-  <si>
     <t>CUIT DEL EDIFICIO: 30-71424193-8</t>
   </si>
   <si>
@@ -382,21 +384,9 @@
     <t xml:space="preserve"> (%) Coch</t>
   </si>
   <si>
-    <t>Speziale Karina - Vidrio Laminado 3+3 colocacion - Retirar virio corte y colocacion</t>
-  </si>
-  <si>
-    <t>Herreelec - Servicios: saldo pendiente servicios realizados</t>
-  </si>
-  <si>
     <t>Efectivo</t>
   </si>
   <si>
-    <t>Transf 16/07</t>
-  </si>
-  <si>
-    <t>Transf 23/07</t>
-  </si>
-  <si>
     <t>Ariel Sebastian Amaya</t>
   </si>
   <si>
@@ -418,15 +408,6 @@
     <t>Gonzalez Maximiliano</t>
   </si>
   <si>
-    <t>Espinola Christian - Arreglo de rampa</t>
-  </si>
-  <si>
-    <t>Debito 16/07</t>
-  </si>
-  <si>
-    <t>Debito 30/07</t>
-  </si>
-  <si>
     <t>Abona por</t>
   </si>
   <si>
@@ -445,9 +426,6 @@
     <t>Ingresos en efectivo</t>
   </si>
   <si>
-    <t>Casa Ruan compra de luces</t>
-  </si>
-  <si>
     <t>Rubinetti Agostina</t>
   </si>
   <si>
@@ -481,40 +459,67 @@
     <t>PERÍODO: AGOSTO</t>
   </si>
   <si>
-    <t>Abono celular + Jardin - Ariel Pereyra - JULIO y AGOSTO</t>
-  </si>
-  <si>
-    <t>Se abona en efectivo el sueldo de JULIO (ultimo liquidado por la Sra. Mariana) por un total de $721.423,68. El abono se realiza mediante deposito bancario.</t>
-  </si>
-  <si>
     <t>Sindicatos mes de JULIO</t>
   </si>
   <si>
-    <t>Abono de sueldo mes de JULIO - Deposito en efectivo</t>
-  </si>
-  <si>
-    <t>Cuello Natalia - Repaso de colectora cloacal</t>
-  </si>
-  <si>
     <t>Transf 21/08</t>
   </si>
   <si>
-    <t>Articulos de limpieza</t>
-  </si>
-  <si>
-    <t>SA Seguridad</t>
-  </si>
-  <si>
     <t>Transf 05/08</t>
   </si>
   <si>
-    <t>Ariel</t>
-  </si>
-  <si>
     <t>Tramsf 10/08</t>
   </si>
   <si>
-    <t>Galvan Zaffalon - Cambio de swich de prezu rizadra mano de obra y repuesto</t>
+    <t>Transf 03/08</t>
+  </si>
+  <si>
+    <t>Debito 03/08</t>
+  </si>
+  <si>
+    <t>Debito 05/08</t>
+  </si>
+  <si>
+    <t>Galvan Zaffalon - Cambio de swich de presurizadora mano de obra y repuesto</t>
+  </si>
+  <si>
+    <t>Cuello Natalia - CUIT: 27304166237 - Fc. 000358  - Repaso de colectora cloacal</t>
+  </si>
+  <si>
+    <t>Quimica Edelweiss - Articulos de limpieza - Remito 7108</t>
+  </si>
+  <si>
+    <t>Transf 31/08</t>
+  </si>
+  <si>
+    <t>SA Seguridad - Presupuesto nro. 17753 - Colocacion de motor a cadena para porton guillotina - Mano de obra, instalacion - Automatizacion porton</t>
+  </si>
+  <si>
+    <t>Mes de junio</t>
+  </si>
+  <si>
+    <t>Debito 12/08</t>
+  </si>
+  <si>
+    <t>Mes de julio</t>
+  </si>
+  <si>
+    <t>Abono celular + Jardin - Ariel Pereyra - Agosto +  Diferencia de Julio y Junio</t>
+  </si>
+  <si>
+    <t>Extraccion e efectivo 19/08</t>
+  </si>
+  <si>
+    <t>Ingreso - Extraccion bancaria 19/08</t>
+  </si>
+  <si>
+    <t>SOLICITAMOS ENCARECIDAMENTE RESPETAR LOS CENTAVOS AL ABONAR.</t>
+  </si>
+  <si>
+    <t>Gustavo Padron - Sr. Contador - CUIT: 200271220 - Fc. 0000185 - 2 meses</t>
+  </si>
+  <si>
+    <t>El 5A, 6A, 7A y dptoo 11/12 Deben recibir una quita de punitorios, ya que pagaron el monto de prorrateo indebido por un error en el importe del primer archivo emitido como pdf, luego se volvio a emitir otro prorrateo con distintos montos pero ellos ya habian pagado</t>
   </si>
 </sst>
 </file>
@@ -531,7 +536,7 @@
     <numFmt numFmtId="167" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="168" formatCode="0.000"/>
   </numFmts>
-  <fonts count="24" x14ac:knownFonts="1">
+  <fonts count="25" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -714,6 +719,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="12">
     <fill>
@@ -1233,7 +1245,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="240">
+  <cellXfs count="242">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1411,9 +1423,6 @@
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1439,9 +1448,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="44" fontId="23" fillId="0" borderId="25" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1458,9 +1464,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="16" fontId="18" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="16" fontId="18" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="44" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1509,10 +1512,6 @@
     </xf>
     <xf numFmtId="168" fontId="20" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="167" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1547,27 +1546,53 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="8" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="24" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="24" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="24" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1604,23 +1629,23 @@
     <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1672,17 +1697,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1762,9 +1776,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -1802,9 +1816,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1837,9 +1851,26 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -1872,9 +1903,26 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2048,49 +2096,49 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M126"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:M121"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="37.5546875" customWidth="1"/>
-    <col min="2" max="2" width="24.6640625" customWidth="1"/>
-    <col min="3" max="3" width="15.6640625" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.6640625" customWidth="1"/>
-    <col min="5" max="5" width="14.6640625" customWidth="1"/>
+    <col min="1" max="1" width="37.5703125" customWidth="1"/>
+    <col min="2" max="2" width="24.7109375" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" customWidth="1"/>
     <col min="6" max="6" width="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.33203125" customWidth="1"/>
+    <col min="12" max="12" width="18.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="14"/>
-      <c r="B1" s="200" t="s">
-        <v>147</v>
-      </c>
-      <c r="C1" s="200"/>
-      <c r="D1" s="200"/>
+      <c r="B1" s="207" t="s">
+        <v>138</v>
+      </c>
+      <c r="C1" s="207"/>
+      <c r="D1" s="207"/>
       <c r="E1" s="47"/>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="15"/>
       <c r="B2" s="48" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C2" s="48"/>
       <c r="D2" s="48"/>
       <c r="E2" s="49"/>
     </row>
-    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="15"/>
-      <c r="B3" s="201" t="s">
-        <v>148</v>
-      </c>
-      <c r="C3" s="201"/>
-      <c r="D3" s="201"/>
-      <c r="E3" s="202"/>
-    </row>
-    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B3" s="208" t="s">
+        <v>139</v>
+      </c>
+      <c r="C3" s="208"/>
+      <c r="D3" s="208"/>
+      <c r="E3" s="209"/>
+    </row>
+    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
         <v>0</v>
       </c>
@@ -2101,12 +2149,12 @@
       <c r="D4" s="19"/>
       <c r="E4" s="20"/>
     </row>
-    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="15" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B5" s="19" t="s">
-        <v>150</v>
+        <v>141</v>
       </c>
       <c r="C5" s="16"/>
       <c r="D5" s="48" t="s">
@@ -2114,9 +2162,9 @@
       </c>
       <c r="E5" s="17"/>
     </row>
-    <row r="6" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="18" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B6" s="19"/>
       <c r="C6" s="19"/>
@@ -2125,57 +2173,57 @@
       </c>
       <c r="E6" s="20"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="204" t="s">
-        <v>149</v>
-      </c>
-      <c r="C8" s="204"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="204"/>
-      <c r="C9" s="204"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="204"/>
-      <c r="C10" s="204"/>
-    </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="203" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B8" s="211" t="s">
+        <v>140</v>
+      </c>
+      <c r="C8" s="211"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B9" s="211"/>
+      <c r="C9" s="211"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B10" s="211"/>
+      <c r="C10" s="211"/>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="210" t="s">
         <v>46</v>
       </c>
-      <c r="B13" s="203"/>
-      <c r="C13" s="203"/>
-      <c r="D13" s="203"/>
-      <c r="E13" s="203"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="203"/>
-      <c r="B14" s="203"/>
-      <c r="C14" s="203"/>
-      <c r="D14" s="203"/>
-      <c r="E14" s="203"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="203"/>
-      <c r="B15" s="203"/>
-      <c r="C15" s="203"/>
-      <c r="D15" s="203"/>
-      <c r="E15" s="203"/>
-    </row>
-    <row r="16" spans="1:5" ht="127.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="203"/>
-      <c r="B16" s="203"/>
-      <c r="C16" s="203"/>
-      <c r="D16" s="203"/>
-      <c r="E16" s="203"/>
-    </row>
-    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="210"/>
+      <c r="C13" s="210"/>
+      <c r="D13" s="210"/>
+      <c r="E13" s="210"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="210"/>
+      <c r="B14" s="210"/>
+      <c r="C14" s="210"/>
+      <c r="D14" s="210"/>
+      <c r="E14" s="210"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="210"/>
+      <c r="B15" s="210"/>
+      <c r="C15" s="210"/>
+      <c r="D15" s="210"/>
+      <c r="E15" s="210"/>
+    </row>
+    <row r="16" spans="1:5" ht="127.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="210"/>
+      <c r="B16" s="210"/>
+      <c r="C16" s="210"/>
+      <c r="D16" s="210"/>
+      <c r="E16" s="210"/>
+    </row>
+    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
     </row>
-    <row r="19" spans="1:7" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="10" t="s">
         <v>9</v>
       </c>
@@ -2184,7 +2232,7 @@
       <c r="D20" s="8"/>
       <c r="E20" s="13"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="26" t="s">
         <v>25</v>
       </c>
@@ -2193,9 +2241,9 @@
       <c r="D21" s="25"/>
       <c r="E21" s="25"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="53" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
@@ -2204,7 +2252,7 @@
       </c>
       <c r="E22" s="5"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>47</v>
       </c>
@@ -2215,7 +2263,7 @@
       </c>
       <c r="E23" s="5"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>48</v>
       </c>
@@ -2226,1000 +2274,940 @@
       </c>
       <c r="E24" s="5"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A25" s="172" t="s">
-        <v>151</v>
-      </c>
-      <c r="B25" s="102"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="108">
-        <f>3500*2</f>
-        <v>7000</v>
-      </c>
-      <c r="E25" s="5"/>
-    </row>
-    <row r="26" spans="1:7" ht="56.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="196" t="s">
-        <v>152</v>
-      </c>
-      <c r="B26" s="197"/>
+    <row r="25" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="43" t="s">
+        <v>26</v>
+      </c>
+      <c r="B25" s="43"/>
+      <c r="C25" s="43"/>
+      <c r="D25" s="109">
+        <f>SUM(D22:D24)</f>
+        <v>692958</v>
+      </c>
+      <c r="E25" s="80"/>
+      <c r="G25" s="21"/>
+    </row>
+    <row r="26" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B26" s="5"/>
       <c r="C26" s="5"/>
       <c r="D26" s="108"/>
       <c r="E26" s="5"/>
     </row>
-    <row r="27" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="43" t="s">
-        <v>26</v>
-      </c>
-      <c r="B27" s="43"/>
-      <c r="C27" s="43"/>
-      <c r="D27" s="109">
-        <f>SUM(D22:D25)</f>
-        <v>699958</v>
-      </c>
-      <c r="E27" s="80"/>
-      <c r="G27" s="21"/>
-    </row>
-    <row r="28" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="5" t="s">
-        <v>31</v>
-      </c>
+    <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="22"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
+      <c r="D27" s="108"/>
+      <c r="E27" s="5"/>
+    </row>
+    <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="5"/>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
       <c r="D28" s="108"/>
       <c r="E28" s="5"/>
     </row>
-    <row r="29" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="22"/>
+    <row r="29" spans="1:7" ht="0.4" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="5"/>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
-      <c r="D29" s="108"/>
+      <c r="D29" s="125"/>
       <c r="E29" s="5"/>
     </row>
-    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="5"/>
-      <c r="B30" s="5"/>
-      <c r="C30" s="5"/>
-      <c r="D30" s="108"/>
-      <c r="E30" s="5"/>
-    </row>
-    <row r="31" spans="1:7" ht="0.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="5"/>
-      <c r="B31" s="5"/>
-      <c r="C31" s="5"/>
-      <c r="D31" s="125"/>
-      <c r="E31" s="5"/>
-    </row>
-    <row r="32" spans="1:7" hidden="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="43" t="s">
+    <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="43" t="s">
         <v>26</v>
       </c>
-      <c r="B32" s="43"/>
-      <c r="C32" s="43"/>
-      <c r="D32" s="110">
-        <f>SUM(D28:D31)</f>
-        <v>0</v>
-      </c>
-      <c r="E32" s="80"/>
-    </row>
-    <row r="33" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A33" s="23" t="s">
+      <c r="B30" s="43"/>
+      <c r="C30" s="43"/>
+      <c r="D30" s="110">
+        <f>SUM(D26:D29)</f>
+        <v>0</v>
+      </c>
+      <c r="E30" s="80"/>
+    </row>
+    <row r="31" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="B33" s="23"/>
-      <c r="C33" s="23"/>
-      <c r="D33" s="111"/>
-      <c r="E33" s="81">
-        <f>D27+D32</f>
-        <v>699958</v>
-      </c>
-      <c r="F33" s="21"/>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A34" s="26" t="s">
+      <c r="B31" s="23"/>
+      <c r="C31" s="23"/>
+      <c r="D31" s="111"/>
+      <c r="E31" s="81">
+        <f>D25+D30</f>
+        <v>692958</v>
+      </c>
+      <c r="F31" s="21"/>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A32" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="B34" s="26"/>
-      <c r="C34" s="26"/>
-      <c r="D34" s="112"/>
-      <c r="E34" s="82"/>
-    </row>
-    <row r="35" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="198" t="s">
-        <v>59</v>
-      </c>
-      <c r="B35" s="199"/>
-      <c r="C35" s="40"/>
-      <c r="D35" s="236">
+      <c r="B32" s="26"/>
+      <c r="C32" s="26"/>
+      <c r="D32" s="112"/>
+      <c r="E32" s="82"/>
+    </row>
+    <row r="33" spans="1:7" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="200" t="s">
+        <v>161</v>
+      </c>
+      <c r="B33" s="201"/>
+      <c r="C33" s="40"/>
+      <c r="D33" s="189">
         <v>100000</v>
       </c>
-      <c r="E35" s="83" t="s">
+      <c r="E33" s="83" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="200" t="s">
+        <v>63</v>
+      </c>
+      <c r="B34" s="201"/>
+      <c r="C34" s="40"/>
+      <c r="D34" s="126">
+        <v>0</v>
+      </c>
+      <c r="E34" s="83"/>
+    </row>
+    <row r="35" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="B35" s="23"/>
+      <c r="C35" s="23"/>
+      <c r="D35" s="119"/>
+      <c r="E35" s="84">
+        <f>SUM(D33:D34)</f>
+        <v>100000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A36" s="26" t="s">
+        <v>23</v>
+      </c>
+      <c r="B36" s="23"/>
+      <c r="C36" s="23"/>
+      <c r="D36" s="120"/>
+      <c r="E36" s="85"/>
+    </row>
+    <row r="37" spans="1:7" s="29" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="206" t="s">
+        <v>64</v>
+      </c>
+      <c r="B37" s="206"/>
+      <c r="C37" s="41"/>
+      <c r="D37" s="191">
+        <v>44249</v>
+      </c>
+      <c r="E37" s="141" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A38" s="142" t="s">
+        <v>65</v>
+      </c>
+      <c r="B38" s="143"/>
+      <c r="C38" s="41"/>
+      <c r="D38" s="191">
+        <v>4406</v>
+      </c>
+      <c r="E38" s="147" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="144" t="s">
+        <v>2</v>
+      </c>
+      <c r="B39" s="144"/>
+      <c r="C39" s="23"/>
+      <c r="D39" s="119"/>
+      <c r="E39" s="54">
+        <f>SUM(D37:D38)</f>
+        <v>48655</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="B40" s="86"/>
+      <c r="C40" s="86"/>
+      <c r="D40" s="121"/>
+      <c r="E40" s="114"/>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A41" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>154</v>
+      </c>
+      <c r="C41" s="40"/>
+      <c r="D41" s="188">
+        <v>839936.9</v>
+      </c>
+      <c r="E41" s="89" t="s">
+        <v>152</v>
+      </c>
+      <c r="G41" s="71"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A42" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="B42" s="5" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A36" s="198" t="s">
-        <v>64</v>
-      </c>
-      <c r="B36" s="199"/>
-      <c r="C36" s="40"/>
-      <c r="D36" s="126">
-        <v>0</v>
-      </c>
-      <c r="E36" s="83"/>
-    </row>
-    <row r="37" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A37" s="23" t="s">
+      <c r="C42" s="40"/>
+      <c r="D42" s="188">
+        <v>518193.32</v>
+      </c>
+      <c r="E42" s="89" t="s">
+        <v>152</v>
+      </c>
+      <c r="G42" s="71"/>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A43" s="5" t="s">
+        <v>142</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="C43" s="5"/>
+      <c r="D43" s="188">
+        <v>84552.82</v>
+      </c>
+      <c r="E43" s="89" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A44" s="5" t="str">
+        <f>A43</f>
+        <v>Sindicatos mes de JULIO</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C44" s="5"/>
+      <c r="D44" s="188">
+        <v>41439.33</v>
+      </c>
+      <c r="E44" s="90" t="str">
+        <f>E43</f>
+        <v>Debito 12/08</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A45" s="5" t="str">
+        <f>A44</f>
+        <v>Sindicatos mes de JULIO</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C45" s="5"/>
+      <c r="D45" s="188">
+        <v>4604.37</v>
+      </c>
+      <c r="E45" s="91" t="str">
+        <f>E44</f>
+        <v>Debito 12/08</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="23" t="s">
+        <v>3</v>
+      </c>
+      <c r="B46" s="86"/>
+      <c r="C46" s="86"/>
+      <c r="D46" s="122"/>
+      <c r="E46" s="54">
+        <f>SUM(D41:D45)</f>
+        <v>1488726.7400000002</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A47" s="26" t="s">
+        <v>16</v>
+      </c>
+      <c r="B47" s="86"/>
+      <c r="C47" s="86"/>
+      <c r="D47" s="121"/>
+      <c r="E47" s="114"/>
+    </row>
+    <row r="48" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A48" s="53" t="s">
+        <v>68</v>
+      </c>
+      <c r="B48" s="5"/>
+      <c r="C48" s="5"/>
+      <c r="D48" s="188">
+        <v>334964.3</v>
+      </c>
+      <c r="E48" s="89" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A49" s="145" t="s">
+        <v>70</v>
+      </c>
+      <c r="B49" s="102"/>
+      <c r="C49" s="5"/>
+      <c r="D49" s="188">
+        <v>0</v>
+      </c>
+      <c r="E49" s="89"/>
+    </row>
+    <row r="50" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A50" s="145" t="s">
+        <v>67</v>
+      </c>
+      <c r="B50" s="102"/>
+      <c r="C50" s="5"/>
+      <c r="D50" s="188">
+        <v>783602.88</v>
+      </c>
+      <c r="E50" s="105" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="51" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="23" t="s">
+        <v>4</v>
+      </c>
+      <c r="B51" s="23"/>
+      <c r="C51" s="23"/>
+      <c r="D51" s="123"/>
+      <c r="E51" s="54">
+        <f>SUM(D48:D50)</f>
+        <v>1118567.18</v>
+      </c>
+    </row>
+    <row r="52" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="26"/>
+      <c r="B52" s="23"/>
+      <c r="C52" s="23"/>
+      <c r="D52" s="119"/>
+      <c r="E52" s="115"/>
+    </row>
+    <row r="53" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A53" s="140" t="s">
+        <v>66</v>
+      </c>
+      <c r="B53" s="146"/>
+      <c r="C53" s="5"/>
+      <c r="D53" s="113">
+        <v>0</v>
+      </c>
+      <c r="E53" s="89"/>
+    </row>
+    <row r="54" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A54" s="140" t="s">
+        <v>69</v>
+      </c>
+      <c r="B54" s="190"/>
+      <c r="C54" s="5"/>
+      <c r="D54" s="188">
+        <v>48746</v>
+      </c>
+      <c r="E54" s="105" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="55" spans="1:5" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="204" t="s">
+        <v>149</v>
+      </c>
+      <c r="B55" s="205"/>
+      <c r="C55" s="5"/>
+      <c r="D55" s="188">
+        <v>330000</v>
+      </c>
+      <c r="E55" s="105" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="140" t="s">
+        <v>151</v>
+      </c>
+      <c r="B56" s="146"/>
+      <c r="C56" s="5"/>
+      <c r="D56" s="188">
+        <v>81000</v>
+      </c>
+      <c r="E56" s="105" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="204" t="s">
+        <v>150</v>
+      </c>
+      <c r="B57" s="205"/>
+      <c r="C57" s="5"/>
+      <c r="D57" s="188">
+        <v>95700</v>
+      </c>
+      <c r="E57" s="105" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="23" t="s">
+        <v>8</v>
+      </c>
+      <c r="B58" s="26"/>
+      <c r="C58" s="26"/>
+      <c r="D58" s="25"/>
+      <c r="E58" s="116">
+        <f>SUM(D53:D57)</f>
+        <v>555446</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="B59" s="45"/>
+      <c r="C59" s="23"/>
+      <c r="D59" s="111"/>
+      <c r="E59" s="87"/>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A60" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B60" s="5"/>
+      <c r="C60" s="5"/>
+      <c r="D60" s="113">
+        <v>0</v>
+      </c>
+      <c r="E60" s="88"/>
+    </row>
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A61" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B61" s="5"/>
+      <c r="C61" s="5"/>
+      <c r="D61" s="188">
+        <f>6403.5+74344.13</f>
+        <v>80747.63</v>
+      </c>
+      <c r="E61" s="30"/>
+    </row>
+    <row r="62" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="B37" s="23"/>
-      <c r="C37" s="23"/>
-      <c r="D37" s="119"/>
-      <c r="E37" s="84">
-        <f>SUM(D35:D36)</f>
-        <v>100000</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A38" s="26" t="s">
-        <v>23</v>
-      </c>
-      <c r="B38" s="23"/>
-      <c r="C38" s="23"/>
-      <c r="D38" s="120"/>
-      <c r="E38" s="85"/>
-    </row>
-    <row r="39" spans="1:7" s="29" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="193" t="s">
-        <v>65</v>
-      </c>
-      <c r="B39" s="193"/>
-      <c r="C39" s="41"/>
-      <c r="D39" s="173">
-        <v>44249</v>
-      </c>
-      <c r="E39" s="143" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A40" s="144" t="s">
-        <v>66</v>
-      </c>
-      <c r="B40" s="145"/>
-      <c r="C40" s="41"/>
-      <c r="D40" s="173">
-        <v>4406</v>
-      </c>
-      <c r="E40" s="149" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A41" s="193" t="s">
-        <v>65</v>
-      </c>
-      <c r="B41" s="193"/>
-      <c r="C41" s="41"/>
-      <c r="D41" s="173">
-        <v>44249</v>
-      </c>
-      <c r="E41" s="150" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A42" s="146" t="s">
-        <v>2</v>
-      </c>
-      <c r="B42" s="146"/>
-      <c r="C42" s="23"/>
-      <c r="D42" s="119"/>
-      <c r="E42" s="54">
-        <f>SUM(D39:D41)</f>
-        <v>92904</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A43" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="B43" s="86"/>
-      <c r="C43" s="86"/>
-      <c r="D43" s="121"/>
-      <c r="E43" s="114"/>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A44" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="B44" s="5"/>
-      <c r="C44" s="40"/>
-      <c r="D44" s="235">
-        <v>839936.9</v>
-      </c>
-      <c r="E44" s="89"/>
-      <c r="G44" s="71"/>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A45" s="5" t="s">
-        <v>153</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C45" s="5"/>
-      <c r="D45" s="235">
-        <v>84552.82</v>
-      </c>
-      <c r="E45" s="89"/>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A46" s="5" t="str">
-        <f>A45</f>
-        <v>Sindicatos mes de JULIO</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="C46" s="5"/>
-      <c r="D46" s="235">
-        <v>41439.33</v>
-      </c>
-      <c r="E46" s="90"/>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A47" s="5" t="str">
-        <f>A46</f>
-        <v>Sindicatos mes de JULIO</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C47" s="5"/>
-      <c r="D47" s="235">
-        <v>4604.37</v>
-      </c>
-      <c r="E47" s="91"/>
-    </row>
-    <row r="48" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A48" s="23" t="s">
-        <v>3</v>
-      </c>
-      <c r="B48" s="86"/>
-      <c r="C48" s="86"/>
-      <c r="D48" s="122"/>
-      <c r="E48" s="54">
-        <f>SUM(D44:D47)</f>
-        <v>970533.41999999993</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A49" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="B49" s="86"/>
-      <c r="C49" s="86"/>
-      <c r="D49" s="121"/>
-      <c r="E49" s="114"/>
-    </row>
-    <row r="50" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="53" t="s">
-        <v>69</v>
-      </c>
-      <c r="B50" s="5"/>
-      <c r="C50" s="5"/>
-      <c r="D50" s="235">
-        <v>334964.3</v>
-      </c>
-      <c r="E50" s="89" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="147" t="s">
-        <v>71</v>
-      </c>
-      <c r="B51" s="102"/>
-      <c r="C51" s="5"/>
-      <c r="D51" s="235">
-        <v>8417.26</v>
-      </c>
-      <c r="E51" s="89" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="147" t="s">
-        <v>71</v>
-      </c>
-      <c r="B52" s="102"/>
-      <c r="C52" s="5"/>
-      <c r="D52" s="113">
-        <v>8417.26</v>
-      </c>
-      <c r="E52" s="89" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="147" t="s">
-        <v>68</v>
-      </c>
-      <c r="B53" s="102"/>
-      <c r="C53" s="5"/>
-      <c r="D53" s="235">
-        <v>783602.88</v>
-      </c>
-      <c r="E53" s="89" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A54" s="23" t="s">
-        <v>4</v>
-      </c>
-      <c r="B54" s="23"/>
-      <c r="C54" s="23"/>
-      <c r="D54" s="123"/>
-      <c r="E54" s="54">
-        <f>SUM(D50:D53)</f>
-        <v>1135401.7</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A55" s="26"/>
-      <c r="B55" s="23"/>
-      <c r="C55" s="23"/>
-      <c r="D55" s="119"/>
-      <c r="E55" s="115"/>
-    </row>
-    <row r="56" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="142" t="s">
-        <v>67</v>
-      </c>
-      <c r="B56" s="148"/>
-      <c r="C56" s="5"/>
-      <c r="D56" s="113">
-        <v>104000</v>
-      </c>
-      <c r="E56" s="89" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="142" t="s">
-        <v>70</v>
-      </c>
-      <c r="B57" s="148"/>
-      <c r="C57" s="5"/>
-      <c r="D57" s="113">
-        <v>0</v>
-      </c>
-      <c r="E57" s="105"/>
-    </row>
-    <row r="58" spans="1:5" ht="43.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="238" t="s">
-        <v>162</v>
-      </c>
-      <c r="B58" s="239"/>
-      <c r="C58" s="5"/>
-      <c r="D58" s="235">
-        <v>330000</v>
-      </c>
-      <c r="E58" s="105" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="142" t="s">
-        <v>157</v>
-      </c>
-      <c r="B59" s="148"/>
-      <c r="C59" s="5"/>
-      <c r="D59" s="235">
-        <v>81000</v>
-      </c>
-      <c r="E59" s="105" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="237" t="s">
-        <v>158</v>
-      </c>
-      <c r="B60" s="148"/>
-      <c r="C60" s="5"/>
-      <c r="D60" s="235">
-        <v>3320350</v>
-      </c>
-      <c r="E60" s="105"/>
-    </row>
-    <row r="61" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="141" t="s">
-        <v>155</v>
-      </c>
-      <c r="B61" s="148"/>
-      <c r="C61" s="5"/>
-      <c r="D61" s="235">
-        <v>95700</v>
-      </c>
-      <c r="E61" s="105" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="237" t="s">
-        <v>160</v>
-      </c>
-      <c r="B62" s="131"/>
-      <c r="C62" s="5"/>
-      <c r="D62" s="235">
-        <v>40000</v>
-      </c>
-      <c r="E62" s="89" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A63" s="23" t="s">
-        <v>8</v>
-      </c>
-      <c r="B63" s="26"/>
-      <c r="C63" s="26"/>
-      <c r="D63" s="25"/>
-      <c r="E63" s="116">
-        <f>SUM(D56:D62)</f>
-        <v>3971050</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A64" s="26" t="s">
-        <v>10</v>
-      </c>
-      <c r="B64" s="45"/>
-      <c r="C64" s="23"/>
-      <c r="D64" s="111"/>
-      <c r="E64" s="87"/>
-    </row>
-    <row r="65" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A65" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B65" s="5"/>
-      <c r="C65" s="5"/>
-      <c r="D65" s="113">
-        <v>0</v>
-      </c>
-      <c r="E65" s="88"/>
-    </row>
-    <row r="66" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A66" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B66" s="5"/>
-      <c r="C66" s="5"/>
-      <c r="D66" s="113">
-        <f>-596+61144.22</f>
-        <v>60548.22</v>
-      </c>
-      <c r="E66" s="30"/>
-    </row>
-    <row r="67" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A67" s="39" t="s">
-        <v>14</v>
-      </c>
-      <c r="B67" s="39"/>
-      <c r="C67" s="39"/>
-      <c r="D67" s="59"/>
-      <c r="E67" s="54">
-        <f>SUM(D65:D66)</f>
-        <v>60548.22</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A68" s="5"/>
-      <c r="B68" s="5"/>
-      <c r="C68" s="5"/>
-      <c r="D68" s="53"/>
-      <c r="E68" s="60"/>
-    </row>
-    <row r="69" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A69" s="24" t="s">
+      <c r="B62" s="39"/>
+      <c r="C62" s="39"/>
+      <c r="D62" s="59"/>
+      <c r="E62" s="54">
+        <f>SUM(D60:D61)</f>
+        <v>80747.63</v>
+      </c>
+    </row>
+    <row r="63" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="5"/>
+      <c r="B63" s="5"/>
+      <c r="C63" s="5"/>
+      <c r="D63" s="53"/>
+      <c r="E63" s="60"/>
+    </row>
+    <row r="64" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="B69" s="24"/>
-      <c r="C69" s="24"/>
-      <c r="D69" s="61"/>
-      <c r="E69" s="62">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A70" s="1"/>
-      <c r="D70" s="63"/>
-      <c r="E70" s="64"/>
-      <c r="F70" s="32"/>
-    </row>
-    <row r="71" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A71" s="3" t="s">
+      <c r="B64" s="24"/>
+      <c r="C64" s="24"/>
+      <c r="D64" s="61"/>
+      <c r="E64" s="62">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="1"/>
+      <c r="D65" s="63"/>
+      <c r="E65" s="64"/>
+      <c r="F65" s="32"/>
+    </row>
+    <row r="66" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A66" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B71" s="9"/>
-      <c r="C71" s="4"/>
-      <c r="D71" s="65"/>
-      <c r="E71" s="66">
-        <f>(SUM(E30:E69))</f>
-        <v>7030395.3399999999</v>
-      </c>
-      <c r="F71" s="79"/>
-      <c r="G71" s="32"/>
+      <c r="B66" s="9"/>
+      <c r="C66" s="4"/>
+      <c r="D66" s="65"/>
+      <c r="E66" s="66">
+        <f>(SUM(E28:E64))</f>
+        <v>4085100.55</v>
+      </c>
+      <c r="F66" s="79"/>
+      <c r="G66" s="32"/>
+      <c r="H66" s="71"/>
+      <c r="I66" s="71"/>
+      <c r="J66" s="71"/>
+      <c r="K66" s="71"/>
+      <c r="L66" s="71"/>
+    </row>
+    <row r="67" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D67" s="63"/>
+      <c r="E67" s="63"/>
+      <c r="H67" s="71"/>
+      <c r="I67" s="71"/>
+      <c r="J67" s="71"/>
+      <c r="K67" s="71"/>
+      <c r="L67" s="71"/>
+    </row>
+    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A68" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="B68" s="11"/>
+      <c r="C68" s="12"/>
+      <c r="D68" s="67"/>
+      <c r="E68" s="68"/>
+      <c r="H68" s="71"/>
+      <c r="I68" s="71"/>
+      <c r="J68" s="71"/>
+      <c r="K68" s="71"/>
+      <c r="L68" s="71"/>
+    </row>
+    <row r="69" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A69" s="202"/>
+      <c r="B69" s="203"/>
+      <c r="C69" s="5"/>
+      <c r="D69" s="113"/>
+      <c r="E69" s="105"/>
+      <c r="H69" s="71"/>
+      <c r="I69" s="71"/>
+      <c r="J69" s="71"/>
+      <c r="K69" s="71"/>
+      <c r="L69" s="71"/>
+    </row>
+    <row r="70" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A70" s="202"/>
+      <c r="B70" s="203"/>
+      <c r="C70" s="5"/>
+      <c r="D70" s="113"/>
+      <c r="E70" s="55"/>
+      <c r="H70" s="71"/>
+      <c r="I70" s="71"/>
+      <c r="J70" s="71"/>
+      <c r="K70" s="71"/>
+      <c r="L70" s="71"/>
+    </row>
+    <row r="71" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A71" s="56"/>
+      <c r="B71" s="58"/>
+      <c r="C71" s="5"/>
+      <c r="D71" s="57"/>
+      <c r="E71" s="55"/>
       <c r="H71" s="71"/>
       <c r="I71" s="71"/>
       <c r="J71" s="71"/>
       <c r="K71" s="71"/>
       <c r="L71" s="71"/>
     </row>
-    <row r="72" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D72" s="63"/>
-      <c r="E72" s="63"/>
+    <row r="72" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A72" s="37"/>
+      <c r="B72" s="36"/>
+      <c r="C72" s="36"/>
+      <c r="D72" s="127"/>
+      <c r="E72" s="170">
+        <f>SUM(D69:D71)</f>
+        <v>0</v>
+      </c>
       <c r="H72" s="71"/>
       <c r="I72" s="71"/>
       <c r="J72" s="71"/>
       <c r="K72" s="71"/>
       <c r="L72" s="71"/>
     </row>
-    <row r="73" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A73" s="10" t="s">
-        <v>142</v>
-      </c>
-      <c r="B73" s="11"/>
-      <c r="C73" s="12"/>
-      <c r="D73" s="67"/>
-      <c r="E73" s="68"/>
+    <row r="73" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="D73" s="63"/>
+      <c r="E73" s="63"/>
       <c r="H73" s="71"/>
       <c r="I73" s="71"/>
       <c r="J73" s="71"/>
       <c r="K73" s="71"/>
       <c r="L73" s="71"/>
     </row>
-    <row r="74" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A74" s="196" t="s">
-        <v>130</v>
-      </c>
-      <c r="B74" s="197"/>
-      <c r="C74" s="5"/>
-      <c r="D74" s="113">
-        <v>80000</v>
-      </c>
-      <c r="E74" s="105" t="s">
-        <v>121</v>
-      </c>
-      <c r="H74" s="71"/>
-      <c r="I74" s="71"/>
-      <c r="J74" s="71"/>
-      <c r="K74" s="71"/>
-      <c r="L74" s="71"/>
-    </row>
-    <row r="75" spans="1:12" ht="34.200000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A75" s="196" t="s">
-        <v>118</v>
-      </c>
-      <c r="B75" s="197"/>
-      <c r="C75" s="5"/>
-      <c r="D75" s="57">
-        <v>650000</v>
-      </c>
-      <c r="E75" s="55"/>
-      <c r="H75" s="71"/>
-      <c r="I75" s="71"/>
-      <c r="J75" s="71"/>
-      <c r="K75" s="71"/>
-      <c r="L75" s="71"/>
-    </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A76" s="196" t="s">
-        <v>119</v>
-      </c>
-      <c r="B76" s="197"/>
+    <row r="74" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D74" s="63"/>
+      <c r="E74" s="63"/>
+      <c r="H74" s="92"/>
+    </row>
+    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A75" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="B75" s="11"/>
+      <c r="C75" s="12"/>
+      <c r="D75" s="67"/>
+      <c r="E75" s="68"/>
+    </row>
+    <row r="76" spans="1:12" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="198" t="s">
+        <v>153</v>
+      </c>
+      <c r="B76" s="199"/>
       <c r="C76" s="5"/>
-      <c r="D76" s="113">
-        <v>1109418.75</v>
-      </c>
-      <c r="E76" s="55"/>
-      <c r="H76" s="71"/>
-      <c r="I76" s="71"/>
-      <c r="J76" s="71"/>
-      <c r="K76" s="71"/>
-      <c r="L76" s="71"/>
-    </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A77" s="56"/>
-      <c r="B77" s="58"/>
+      <c r="D76" s="188">
+        <v>3320350</v>
+      </c>
+      <c r="E76" s="105" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="77" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="200"/>
+      <c r="B77" s="201"/>
       <c r="C77" s="5"/>
       <c r="D77" s="57"/>
       <c r="E77" s="55"/>
-      <c r="H77" s="71"/>
-      <c r="I77" s="71"/>
-      <c r="J77" s="71"/>
-      <c r="K77" s="71"/>
-      <c r="L77" s="71"/>
-    </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A78" s="37"/>
-      <c r="B78" s="36"/>
-      <c r="C78" s="36"/>
-      <c r="D78" s="127"/>
-      <c r="E78" s="175">
-        <f>SUM(D74:D77)</f>
-        <v>1839418.75</v>
-      </c>
-      <c r="H78" s="71"/>
-      <c r="I78" s="71"/>
-      <c r="J78" s="71"/>
-      <c r="K78" s="71"/>
-      <c r="L78" s="71"/>
-    </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="D79" s="63"/>
-      <c r="E79" s="63"/>
-      <c r="H79" s="71"/>
-      <c r="I79" s="71"/>
-      <c r="J79" s="71"/>
-      <c r="K79" s="71"/>
-      <c r="L79" s="71"/>
-    </row>
-    <row r="80" spans="1:12" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A78" s="56"/>
+      <c r="B78" s="58"/>
+      <c r="C78" s="5"/>
+      <c r="D78" s="57"/>
+      <c r="E78" s="55"/>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A79" s="37"/>
+      <c r="B79" s="36"/>
+      <c r="C79" s="36"/>
+      <c r="D79" s="127"/>
+      <c r="E79" s="170">
+        <f>SUM(D76:D78)</f>
+        <v>3320350</v>
+      </c>
+    </row>
+    <row r="80" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D80" s="63"/>
-      <c r="E80" s="63"/>
-      <c r="H80" s="92"/>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A81" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="B81" s="11"/>
-      <c r="C81" s="12"/>
-      <c r="D81" s="67"/>
-      <c r="E81" s="68"/>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A82" s="196"/>
-      <c r="B82" s="197"/>
-      <c r="C82" s="5"/>
-      <c r="D82" s="113"/>
-      <c r="E82" s="55"/>
-    </row>
-    <row r="83" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A83" s="198"/>
-      <c r="B83" s="199"/>
-      <c r="C83" s="5"/>
-      <c r="D83" s="57"/>
-      <c r="E83" s="55"/>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A84" s="56"/>
-      <c r="B84" s="58"/>
-      <c r="C84" s="5"/>
-      <c r="D84" s="57"/>
-      <c r="E84" s="55"/>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A85" s="37"/>
-      <c r="B85" s="36"/>
-      <c r="C85" s="36"/>
-      <c r="D85" s="127"/>
-      <c r="E85" s="175">
-        <f>SUM(D82:D84)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    </row>
+    <row r="81" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D81" s="63"/>
+    </row>
+    <row r="82" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="106" t="s">
+        <v>57</v>
+      </c>
+      <c r="B82" s="107"/>
+      <c r="C82" s="107"/>
+      <c r="D82" s="128"/>
+      <c r="E82" s="117">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D83" s="63"/>
+    </row>
+    <row r="84" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B84" s="9"/>
+      <c r="C84" s="4"/>
+      <c r="D84" s="65"/>
+      <c r="E84" s="46">
+        <f>E79+E82</f>
+        <v>3320350</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D85" s="63"/>
+    </row>
+    <row r="86" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="51" t="s">
+        <v>12</v>
+      </c>
+      <c r="B86" s="52">
+        <f>E66</f>
+        <v>4085100.55</v>
+      </c>
       <c r="D86" s="63"/>
     </row>
-    <row r="87" spans="1:5" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="51" t="s">
+        <v>13</v>
+      </c>
+      <c r="B87" s="52">
+        <f>E66-E64</f>
+        <v>4085100.55</v>
+      </c>
       <c r="D87" s="63"/>
     </row>
-    <row r="88" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A88" s="106" t="s">
-        <v>57</v>
-      </c>
-      <c r="B88" s="107"/>
-      <c r="C88" s="107"/>
-      <c r="D88" s="128"/>
-      <c r="E88" s="117">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="51" t="s">
+        <v>19</v>
+      </c>
+      <c r="B88" s="52">
+        <f>E84-E82</f>
+        <v>3320350</v>
+      </c>
+      <c r="D88" s="63"/>
+    </row>
+    <row r="89" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="51" t="s">
+        <v>30</v>
+      </c>
+      <c r="B89" s="52">
+        <f>E84</f>
+        <v>3320350</v>
+      </c>
       <c r="D89" s="63"/>
     </row>
-    <row r="90" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A90" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B90" s="9"/>
-      <c r="C90" s="4"/>
-      <c r="D90" s="65"/>
-      <c r="E90" s="46">
-        <f>E85+E88</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D90" s="63"/>
+    </row>
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D91" s="63"/>
     </row>
-    <row r="92" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A92" s="51" t="s">
-        <v>12</v>
-      </c>
-      <c r="B92" s="52">
-        <f>E71</f>
-        <v>7030395.3399999999</v>
-      </c>
-      <c r="D92" s="63"/>
-    </row>
-    <row r="93" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A93" s="51" t="s">
-        <v>13</v>
-      </c>
-      <c r="B93" s="52">
-        <f>E71-E69</f>
-        <v>7030395.3399999999</v>
-      </c>
-      <c r="D93" s="63"/>
-    </row>
-    <row r="94" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A94" s="51" t="s">
-        <v>19</v>
-      </c>
-      <c r="B94" s="52">
-        <f>E90-E88</f>
-        <v>0</v>
-      </c>
-      <c r="D94" s="63"/>
-    </row>
-    <row r="95" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A95" s="51" t="s">
-        <v>30</v>
-      </c>
-      <c r="B95" s="52">
-        <f>E90</f>
-        <v>0</v>
-      </c>
-      <c r="D95" s="63"/>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D96" s="63"/>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="D97" s="63"/>
-    </row>
-    <row r="98" spans="1:5" s="29" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A98"/>
-      <c r="B98" s="31"/>
-      <c r="C98" s="28"/>
-      <c r="D98"/>
-    </row>
-    <row r="99" spans="1:5" s="29" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A99" s="72" t="s">
-        <v>141</v>
-      </c>
-      <c r="B99" s="73">
-        <v>8196318.3700000001</v>
-      </c>
-      <c r="C99" s="28"/>
-      <c r="D99" s="35"/>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A100" s="41" t="s">
+    <row r="92" spans="1:5" s="29" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A92"/>
+      <c r="B92" s="31"/>
+      <c r="C92" s="28"/>
+      <c r="D92"/>
+    </row>
+    <row r="93" spans="1:5" s="29" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="72" t="s">
+        <v>132</v>
+      </c>
+      <c r="B93" s="73">
+        <v>7227046.5299999993</v>
+      </c>
+      <c r="C93" s="28"/>
+      <c r="D93" s="35"/>
+    </row>
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A94" s="41" t="s">
         <v>36</v>
       </c>
-      <c r="B100" s="77">
-        <f>-B93</f>
-        <v>-7030395.3399999999</v>
-      </c>
+      <c r="B94" s="77">
+        <f>-B87</f>
+        <v>-4085100.55</v>
+      </c>
+      <c r="E94" s="32"/>
+    </row>
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A95" s="41" t="s">
+        <v>37</v>
+      </c>
+      <c r="B95" s="77">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="1:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="A96" s="41" t="s">
+        <v>134</v>
+      </c>
+      <c r="B96" s="77">
+        <f>-E72</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A97" s="41" t="s">
+        <v>158</v>
+      </c>
+      <c r="B97" s="148">
+        <v>-3000000</v>
+      </c>
+    </row>
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A98" s="41" t="s">
+        <v>38</v>
+      </c>
+      <c r="B98" s="77">
+        <f>B116</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A99" s="41" t="s">
+        <v>128</v>
+      </c>
+      <c r="B99" s="78">
+        <f>PRORRATEO!L35</f>
+        <v>3698520.92</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="75" t="s">
+        <v>34</v>
+      </c>
+      <c r="B100" s="76">
+        <f>SUM(B93:C99)</f>
+        <v>3840466.8999999994</v>
+      </c>
+      <c r="D100" s="31"/>
       <c r="E100" s="32"/>
     </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A101" s="41" t="s">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A101" s="74"/>
+      <c r="B101" s="74"/>
+    </row>
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A102" s="72" t="s">
+        <v>129</v>
+      </c>
+      <c r="B102" s="73">
+        <v>198159.40000000002</v>
+      </c>
+    </row>
+    <row r="103" spans="1:5" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A103" s="41" t="s">
+        <v>157</v>
+      </c>
+      <c r="B103" s="148">
+        <v>-75000</v>
+      </c>
+    </row>
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A104" s="41" t="s">
+        <v>159</v>
+      </c>
+      <c r="B104" s="192">
+        <v>3000000</v>
+      </c>
+    </row>
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A105" s="41" t="s">
         <v>37</v>
       </c>
-      <c r="B101" s="77">
-        <f>-B94</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A102" s="41" t="s">
-        <v>143</v>
-      </c>
-      <c r="B102" s="77">
-        <f>-E78</f>
-        <v>-1839418.75</v>
-      </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A103" s="41" t="s">
-        <v>38</v>
-      </c>
-      <c r="B103" s="77">
-        <f>B121</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A104" s="41" t="s">
-        <v>136</v>
-      </c>
-      <c r="B104" s="78">
+      <c r="B105" s="148">
+        <f>-B88</f>
+        <v>-3320350</v>
+      </c>
+    </row>
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A106" s="41" t="s">
+        <v>130</v>
+      </c>
+      <c r="B106" s="78">
         <f>PRORRATEO!L36</f>
-        <v>3548957.26</v>
-      </c>
-    </row>
-    <row r="105" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A105" s="75" t="s">
+        <v>218300.27</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="75" t="s">
         <v>34</v>
       </c>
-      <c r="B105" s="76">
-        <f>SUM(B99:C104)</f>
-        <v>2875461.54</v>
-      </c>
-      <c r="D105" s="31"/>
-      <c r="E105" s="32"/>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A106" s="74"/>
-      <c r="B106" s="74"/>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A107" s="72" t="s">
-        <v>137</v>
-      </c>
-      <c r="B107" s="73">
-        <v>747013</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="41" t="s">
-        <v>154</v>
-      </c>
-      <c r="B108" s="151">
-        <v>-721423.6</v>
-      </c>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A109" s="41" t="s">
-        <v>139</v>
-      </c>
-      <c r="B109" s="151">
-        <v>-36000</v>
-      </c>
-    </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A110" s="41" t="s">
-        <v>37</v>
-      </c>
-      <c r="B110" s="77">
-        <f>-B101</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A111" s="41" t="s">
-        <v>138</v>
-      </c>
-      <c r="B111" s="78">
-        <f>PRORRATEO!L37</f>
-        <v>208570</v>
-      </c>
-    </row>
-    <row r="112" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A112" s="75" t="s">
-        <v>34</v>
-      </c>
-      <c r="B112" s="76">
-        <f>SUM(B107:C111)</f>
-        <v>198159.40000000002</v>
-      </c>
-    </row>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A113" s="74"/>
-      <c r="B113" s="74"/>
-    </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A114" s="74"/>
-      <c r="B114" s="74"/>
-    </row>
-    <row r="115" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A115" s="74"/>
-      <c r="B115" s="74"/>
-    </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A116" s="74"/>
-      <c r="B116" s="74"/>
-    </row>
-    <row r="117" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="118" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A118" s="195" t="s">
+      <c r="B107" s="76">
+        <f>SUM(B102:C106)</f>
+        <v>21109.669999999896</v>
+      </c>
+    </row>
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A108" s="74"/>
+      <c r="B108" s="74"/>
+    </row>
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A109" s="74"/>
+      <c r="B109" s="74"/>
+    </row>
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A110" s="74"/>
+      <c r="B110" s="74"/>
+    </row>
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A111" s="74"/>
+      <c r="B111" s="74"/>
+    </row>
+    <row r="112" spans="1:5" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A113" s="197" t="s">
         <v>24</v>
       </c>
-      <c r="B118" s="195"/>
-      <c r="C118" s="195"/>
-    </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A119" s="195"/>
-      <c r="B119" s="195"/>
-      <c r="C119" s="195"/>
-    </row>
-    <row r="120" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="69"/>
-      <c r="B120" s="27"/>
-      <c r="C120" s="27">
+      <c r="B113" s="197"/>
+      <c r="C113" s="197"/>
+    </row>
+    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A114" s="197"/>
+      <c r="B114" s="197"/>
+      <c r="C114" s="197"/>
+    </row>
+    <row r="115" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A115" s="69"/>
+      <c r="B115" s="27"/>
+      <c r="C115" s="27">
         <v>40000</v>
       </c>
-      <c r="E120" s="79"/>
-    </row>
-    <row r="121" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A121" s="33" t="s">
+      <c r="E115" s="79"/>
+    </row>
+    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A116" s="33" t="s">
         <v>8</v>
       </c>
-      <c r="B121" s="70">
-        <f>SUM(B120:B120)</f>
-        <v>0</v>
-      </c>
-      <c r="C121" s="34"/>
-    </row>
-    <row r="122" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="M122" s="7"/>
-    </row>
-    <row r="123" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="194"/>
-      <c r="B123" s="194"/>
-      <c r="C123" s="194"/>
-      <c r="D123" s="194"/>
-      <c r="E123" s="194"/>
-    </row>
-    <row r="124" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A124" s="194"/>
-      <c r="B124" s="194"/>
-      <c r="C124" s="194"/>
-      <c r="D124" s="194"/>
-      <c r="E124" s="194"/>
-    </row>
-    <row r="125" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A125" s="194"/>
-      <c r="B125" s="194"/>
-      <c r="C125" s="194"/>
-      <c r="D125" s="194"/>
-      <c r="E125" s="194"/>
-    </row>
-    <row r="126" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A126" s="194"/>
-      <c r="B126" s="194"/>
-      <c r="C126" s="194"/>
-      <c r="D126" s="194"/>
-      <c r="E126" s="194"/>
+      <c r="B116" s="70">
+        <f>SUM(B115:B115)</f>
+        <v>0</v>
+      </c>
+      <c r="C116" s="34"/>
+    </row>
+    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M117" s="7"/>
+    </row>
+    <row r="118" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A118" s="196"/>
+      <c r="B118" s="196"/>
+      <c r="C118" s="196"/>
+      <c r="D118" s="196"/>
+      <c r="E118" s="196"/>
+    </row>
+    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A119" s="196"/>
+      <c r="B119" s="196"/>
+      <c r="C119" s="196"/>
+      <c r="D119" s="196"/>
+      <c r="E119" s="196"/>
+    </row>
+    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A120" s="196"/>
+      <c r="B120" s="196"/>
+      <c r="C120" s="196"/>
+      <c r="D120" s="196"/>
+      <c r="E120" s="196"/>
+    </row>
+    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A121" s="196"/>
+      <c r="B121" s="196"/>
+      <c r="C121" s="196"/>
+      <c r="D121" s="196"/>
+      <c r="E121" s="196"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="A26:B26"/>
+  <mergeCells count="15">
+    <mergeCell ref="A55:B55"/>
+    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A37:B37"/>
     <mergeCell ref="B1:D1"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A33:B33"/>
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="A13:E16"/>
     <mergeCell ref="B8:C10"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="A123:E126"/>
-    <mergeCell ref="A118:C119"/>
-    <mergeCell ref="A82:B82"/>
-    <mergeCell ref="A83:B83"/>
-    <mergeCell ref="A74:B74"/>
-    <mergeCell ref="A75:B75"/>
+    <mergeCell ref="A118:E121"/>
+    <mergeCell ref="A113:C114"/>
     <mergeCell ref="A76:B76"/>
-    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="A70:B70"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3229,30 +3217,30 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:W53"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:W52"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="4.33203125" customWidth="1"/>
-    <col min="2" max="4" width="6.5546875" customWidth="1"/>
-    <col min="5" max="5" width="20.44140625" customWidth="1"/>
-    <col min="6" max="6" width="9.109375" customWidth="1"/>
-    <col min="7" max="8" width="8.33203125" customWidth="1"/>
-    <col min="9" max="9" width="8.44140625" customWidth="1"/>
-    <col min="10" max="10" width="14.33203125" customWidth="1"/>
-    <col min="11" max="11" width="13.44140625" customWidth="1"/>
-    <col min="12" max="12" width="12.44140625" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="4.28515625" customWidth="1"/>
+    <col min="2" max="4" width="6.5703125" customWidth="1"/>
+    <col min="5" max="5" width="20.42578125" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" customWidth="1"/>
+    <col min="7" max="8" width="8.28515625" customWidth="1"/>
+    <col min="9" max="9" width="8.42578125" customWidth="1"/>
+    <col min="10" max="10" width="14.28515625" customWidth="1"/>
+    <col min="11" max="11" width="13.42578125" customWidth="1"/>
+    <col min="12" max="12" width="12.42578125" hidden="1" customWidth="1"/>
     <col min="13" max="13" width="13" customWidth="1"/>
-    <col min="14" max="14" width="11.109375" customWidth="1"/>
-    <col min="15" max="15" width="11.33203125" customWidth="1"/>
-    <col min="16" max="18" width="12.44140625" customWidth="1"/>
-    <col min="19" max="19" width="14.6640625" customWidth="1"/>
-    <col min="20" max="20" width="14.33203125" customWidth="1"/>
-    <col min="21" max="21" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.140625" customWidth="1"/>
+    <col min="15" max="15" width="11.28515625" customWidth="1"/>
+    <col min="16" max="18" width="12.42578125" customWidth="1"/>
+    <col min="19" max="19" width="14.7109375" customWidth="1"/>
+    <col min="20" max="20" width="14.28515625" customWidth="1"/>
+    <col min="21" max="21" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:23" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6"/>
       <c r="B1" s="6"/>
       <c r="C1" s="6"/>
@@ -3260,21 +3248,21 @@
       <c r="E1" s="6"/>
       <c r="F1" s="6"/>
       <c r="G1" s="6"/>
-      <c r="H1" s="205"/>
-      <c r="I1" s="205"/>
-      <c r="J1" s="205"/>
-      <c r="K1" s="205"/>
-      <c r="L1" s="205"/>
-      <c r="M1" s="205"/>
-      <c r="N1" s="205"/>
-      <c r="O1" s="205"/>
-      <c r="P1" s="205"/>
-      <c r="Q1" s="205"/>
-      <c r="R1" s="205"/>
-      <c r="S1" s="205"/>
+      <c r="H1" s="212"/>
+      <c r="I1" s="212"/>
+      <c r="J1" s="212"/>
+      <c r="K1" s="212"/>
+      <c r="L1" s="212"/>
+      <c r="M1" s="212"/>
+      <c r="N1" s="212"/>
+      <c r="O1" s="212"/>
+      <c r="P1" s="212"/>
+      <c r="Q1" s="212"/>
+      <c r="R1" s="212"/>
+      <c r="S1" s="212"/>
       <c r="T1" s="6"/>
     </row>
-    <row r="2" spans="1:23" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:23" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="6"/>
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
@@ -3282,37 +3270,37 @@
       <c r="E2" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="F2" s="220">
-        <v>0</v>
-      </c>
-      <c r="G2" s="220"/>
-      <c r="H2" s="174"/>
-      <c r="I2" s="174"/>
+      <c r="F2" s="227">
+        <v>0</v>
+      </c>
+      <c r="G2" s="227"/>
+      <c r="H2" s="169"/>
+      <c r="I2" s="169"/>
       <c r="J2" s="16" t="s">
-        <v>144</v>
-      </c>
-      <c r="K2" s="221">
+        <v>135</v>
+      </c>
+      <c r="K2" s="228">
         <v>1839418.75</v>
       </c>
-      <c r="L2" s="221"/>
-      <c r="M2" s="221"/>
+      <c r="L2" s="228"/>
+      <c r="M2" s="228"/>
       <c r="N2" s="16"/>
       <c r="O2" s="16"/>
       <c r="P2" s="16" t="s">
         <v>54</v>
       </c>
-      <c r="Q2" s="220">
+      <c r="Q2" s="227">
         <v>2678810.35</v>
       </c>
-      <c r="R2" s="220"/>
-      <c r="S2" s="220"/>
+      <c r="R2" s="227"/>
+      <c r="S2" s="227"/>
       <c r="T2" s="42"/>
       <c r="U2" s="21"/>
       <c r="V2">
         <v>4095718.96</v>
       </c>
     </row>
-    <row r="3" spans="1:23" ht="13.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:23" ht="13.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
       <c r="B3" s="6"/>
       <c r="C3" s="6"/>
@@ -3334,1985 +3322,1960 @@
       <c r="S3" s="44"/>
       <c r="T3" s="44"/>
     </row>
-    <row r="4" spans="1:23" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="212" t="str">
-        <f>RESUMEN!A13</f>
-        <v>Importante para dueños o inquilinos de departamentos o coheras: Queremos recordarles una cuestión importante respecto a los pagos de expensas que ayuda a evitar errores en la imputación de los mismos. El sistema que utilizamos asigna centavos únicos a cada Unidad Funcional (UF), lo cual nos permite identificar automáticamente a qué unidad corresponde cada transferencia. Es decir, cada UF tiene un número específico de centavos que actúa como "identificador". Por ejemplo, si tu UF es la 45, el importe a abonar debería terminar en $...,45. Si tenés más de una unidad (por ejemplo, un departamento y una cochera), cada una tiene su propio código de centavos. En esos casos, te pedimos por favor que realices una transferencia por cada UF, respetando el importe con sus centavos correspondientes. Sabemos que a veces por comodidad se suele enviar todo junto en una sola transferencia, pero esto puede generar confusión o errores en la imputación automática. Realizar los pagos por separado nos permite asegurar que cada importe se asigne correctamente. Agradecemos muchísimo la colaboración para seguir manteniendo todo ordenado. Saludos cordiales.</v>
-      </c>
-      <c r="B4" s="213"/>
-      <c r="C4" s="213"/>
-      <c r="D4" s="213"/>
-      <c r="E4" s="213"/>
-      <c r="F4" s="213"/>
-      <c r="G4" s="213"/>
-      <c r="H4" s="213"/>
-      <c r="I4" s="213"/>
-      <c r="J4" s="213"/>
-      <c r="K4" s="213"/>
-      <c r="L4" s="213"/>
-      <c r="M4" s="213"/>
-      <c r="N4" s="213"/>
-      <c r="O4" s="213"/>
-      <c r="P4" s="213"/>
-      <c r="Q4" s="213"/>
-      <c r="R4" s="213"/>
-      <c r="S4" s="213"/>
-      <c r="T4" s="214"/>
-    </row>
-    <row r="5" spans="1:23" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="215"/>
-      <c r="B5" s="216"/>
-      <c r="C5" s="216"/>
-      <c r="D5" s="216"/>
-      <c r="E5" s="216"/>
-      <c r="F5" s="216"/>
-      <c r="G5" s="216"/>
-      <c r="H5" s="216"/>
-      <c r="I5" s="216"/>
-      <c r="J5" s="216"/>
-      <c r="K5" s="216"/>
-      <c r="L5" s="216"/>
-      <c r="M5" s="216"/>
-      <c r="N5" s="216"/>
-      <c r="O5" s="216"/>
-      <c r="P5" s="216"/>
-      <c r="Q5" s="216"/>
-      <c r="R5" s="216"/>
-      <c r="S5" s="216"/>
-      <c r="T5" s="217"/>
-    </row>
-    <row r="6" spans="1:23" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="215"/>
-      <c r="B6" s="216"/>
-      <c r="C6" s="216"/>
-      <c r="D6" s="216"/>
-      <c r="E6" s="216"/>
-      <c r="F6" s="216"/>
-      <c r="G6" s="216"/>
-      <c r="H6" s="216"/>
-      <c r="I6" s="216"/>
-      <c r="J6" s="216"/>
-      <c r="K6" s="216"/>
-      <c r="L6" s="216"/>
-      <c r="M6" s="216"/>
-      <c r="N6" s="216"/>
-      <c r="O6" s="216"/>
-      <c r="P6" s="216"/>
-      <c r="Q6" s="216"/>
-      <c r="R6" s="216"/>
-      <c r="S6" s="216"/>
-      <c r="T6" s="217"/>
-    </row>
-    <row r="7" spans="1:23" ht="64.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="215"/>
-      <c r="B7" s="216"/>
-      <c r="C7" s="216"/>
-      <c r="D7" s="216"/>
-      <c r="E7" s="216"/>
-      <c r="F7" s="216"/>
-      <c r="G7" s="216"/>
-      <c r="H7" s="216"/>
-      <c r="I7" s="216"/>
-      <c r="J7" s="216"/>
-      <c r="K7" s="216"/>
-      <c r="L7" s="216"/>
-      <c r="M7" s="216"/>
-      <c r="N7" s="216"/>
-      <c r="O7" s="216"/>
-      <c r="P7" s="216"/>
-      <c r="Q7" s="216"/>
-      <c r="R7" s="216"/>
-      <c r="S7" s="216"/>
-      <c r="T7" s="217"/>
-    </row>
-    <row r="8" spans="1:23" ht="45.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="215"/>
-      <c r="B8" s="216"/>
-      <c r="C8" s="216"/>
-      <c r="D8" s="216"/>
-      <c r="E8" s="216"/>
-      <c r="F8" s="216"/>
-      <c r="G8" s="216"/>
-      <c r="H8" s="216"/>
-      <c r="I8" s="216"/>
-      <c r="J8" s="216"/>
-      <c r="K8" s="216"/>
-      <c r="L8" s="216"/>
-      <c r="M8" s="216"/>
-      <c r="N8" s="216"/>
-      <c r="O8" s="216"/>
-      <c r="P8" s="216"/>
-      <c r="Q8" s="216"/>
-      <c r="R8" s="216"/>
-      <c r="S8" s="216"/>
-      <c r="T8" s="217"/>
-    </row>
-    <row r="9" spans="1:23" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="206" t="s">
+    <row r="4" spans="1:23" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="219" t="s">
+        <v>160</v>
+      </c>
+      <c r="B4" s="220"/>
+      <c r="C4" s="220"/>
+      <c r="D4" s="220"/>
+      <c r="E4" s="220"/>
+      <c r="F4" s="220"/>
+      <c r="G4" s="220"/>
+      <c r="H4" s="220"/>
+      <c r="I4" s="220"/>
+      <c r="J4" s="220"/>
+      <c r="K4" s="220"/>
+      <c r="L4" s="220"/>
+      <c r="M4" s="220"/>
+      <c r="N4" s="220"/>
+      <c r="O4" s="220"/>
+      <c r="P4" s="220"/>
+      <c r="Q4" s="220"/>
+      <c r="R4" s="220"/>
+      <c r="S4" s="220"/>
+      <c r="T4" s="221"/>
+    </row>
+    <row r="5" spans="1:23" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="222"/>
+      <c r="B5" s="223"/>
+      <c r="C5" s="223"/>
+      <c r="D5" s="223"/>
+      <c r="E5" s="223"/>
+      <c r="F5" s="223"/>
+      <c r="G5" s="223"/>
+      <c r="H5" s="223"/>
+      <c r="I5" s="223"/>
+      <c r="J5" s="223"/>
+      <c r="K5" s="223"/>
+      <c r="L5" s="223"/>
+      <c r="M5" s="223"/>
+      <c r="N5" s="223"/>
+      <c r="O5" s="223"/>
+      <c r="P5" s="223"/>
+      <c r="Q5" s="223"/>
+      <c r="R5" s="223"/>
+      <c r="S5" s="223"/>
+      <c r="T5" s="224"/>
+    </row>
+    <row r="6" spans="1:23" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="222"/>
+      <c r="B6" s="223"/>
+      <c r="C6" s="223"/>
+      <c r="D6" s="223"/>
+      <c r="E6" s="223"/>
+      <c r="F6" s="223"/>
+      <c r="G6" s="223"/>
+      <c r="H6" s="223"/>
+      <c r="I6" s="223"/>
+      <c r="J6" s="223"/>
+      <c r="K6" s="223"/>
+      <c r="L6" s="223"/>
+      <c r="M6" s="223"/>
+      <c r="N6" s="223"/>
+      <c r="O6" s="223"/>
+      <c r="P6" s="223"/>
+      <c r="Q6" s="223"/>
+      <c r="R6" s="223"/>
+      <c r="S6" s="223"/>
+      <c r="T6" s="224"/>
+    </row>
+    <row r="7" spans="1:23" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="222"/>
+      <c r="B7" s="223"/>
+      <c r="C7" s="223"/>
+      <c r="D7" s="223"/>
+      <c r="E7" s="223"/>
+      <c r="F7" s="223"/>
+      <c r="G7" s="223"/>
+      <c r="H7" s="223"/>
+      <c r="I7" s="223"/>
+      <c r="J7" s="223"/>
+      <c r="K7" s="223"/>
+      <c r="L7" s="223"/>
+      <c r="M7" s="223"/>
+      <c r="N7" s="223"/>
+      <c r="O7" s="223"/>
+      <c r="P7" s="223"/>
+      <c r="Q7" s="223"/>
+      <c r="R7" s="223"/>
+      <c r="S7" s="223"/>
+      <c r="T7" s="224"/>
+    </row>
+    <row r="8" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="213" t="s">
         <v>5</v>
       </c>
-      <c r="B9" s="208" t="s">
+      <c r="B8" s="215" t="s">
+        <v>72</v>
+      </c>
+      <c r="C8" s="215" t="s">
         <v>73</v>
       </c>
-      <c r="C9" s="208" t="s">
-        <v>74</v>
-      </c>
-      <c r="D9" s="208" t="s">
-        <v>78</v>
-      </c>
-      <c r="E9" s="208" t="s">
+      <c r="D8" s="215" t="s">
+        <v>77</v>
+      </c>
+      <c r="E8" s="215" t="s">
         <v>6</v>
       </c>
-      <c r="F9" s="208" t="s">
+      <c r="F8" s="215" t="s">
+        <v>115</v>
+      </c>
+      <c r="G8" s="215" t="s">
         <v>116</v>
       </c>
-      <c r="G9" s="208" t="s">
-        <v>117</v>
-      </c>
-      <c r="H9" s="206" t="s">
-        <v>115</v>
-      </c>
-      <c r="I9" s="152" t="s">
+      <c r="H8" s="213" t="s">
+        <v>114</v>
+      </c>
+      <c r="I8" s="149" t="s">
         <v>14</v>
       </c>
-      <c r="J9" s="206" t="s">
+      <c r="J8" s="213" t="s">
         <v>35</v>
       </c>
-      <c r="K9" s="208" t="s">
+      <c r="K8" s="215" t="s">
         <v>7</v>
       </c>
-      <c r="L9" s="208" t="s">
-        <v>133</v>
-      </c>
-      <c r="M9" s="210" t="s">
+      <c r="L8" s="215" t="s">
+        <v>125</v>
+      </c>
+      <c r="M8" s="217" t="s">
         <v>22</v>
       </c>
-      <c r="N9" s="206" t="s">
-        <v>146</v>
-      </c>
-      <c r="O9" s="206" t="s">
+      <c r="N8" s="213" t="s">
+        <v>137</v>
+      </c>
+      <c r="O8" s="213" t="s">
         <v>56</v>
       </c>
-      <c r="P9" s="206" t="s">
+      <c r="P8" s="213" t="s">
         <v>20</v>
       </c>
-      <c r="Q9" s="206" t="s">
+      <c r="Q8" s="213" t="s">
         <v>43</v>
       </c>
-      <c r="R9" s="230" t="s">
-        <v>145</v>
-      </c>
-      <c r="S9" s="153" t="s">
+      <c r="R8" s="237" t="s">
+        <v>136</v>
+      </c>
+      <c r="S8" s="150" t="s">
         <v>28</v>
       </c>
-      <c r="T9" s="218" t="s">
+      <c r="T8" s="225" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="10" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="207"/>
-      <c r="B10" s="209"/>
-      <c r="C10" s="209"/>
-      <c r="D10" s="209"/>
-      <c r="E10" s="209"/>
-      <c r="F10" s="209"/>
-      <c r="G10" s="209"/>
-      <c r="H10" s="207"/>
-      <c r="I10" s="165" t="s">
-        <v>114</v>
-      </c>
-      <c r="J10" s="207"/>
-      <c r="K10" s="209"/>
-      <c r="L10" s="209"/>
-      <c r="M10" s="211"/>
-      <c r="N10" s="207"/>
-      <c r="O10" s="207"/>
-      <c r="P10" s="207"/>
-      <c r="Q10" s="207"/>
-      <c r="R10" s="231"/>
-      <c r="S10" s="192" t="str">
+    <row r="9" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="214"/>
+      <c r="B9" s="216"/>
+      <c r="C9" s="216"/>
+      <c r="D9" s="216"/>
+      <c r="E9" s="216"/>
+      <c r="F9" s="216"/>
+      <c r="G9" s="216"/>
+      <c r="H9" s="214"/>
+      <c r="I9" s="162" t="s">
+        <v>113</v>
+      </c>
+      <c r="J9" s="214"/>
+      <c r="K9" s="216"/>
+      <c r="L9" s="216"/>
+      <c r="M9" s="218"/>
+      <c r="N9" s="214"/>
+      <c r="O9" s="214"/>
+      <c r="P9" s="214"/>
+      <c r="Q9" s="214"/>
+      <c r="R9" s="238"/>
+      <c r="S9" s="187" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 17/09</v>
       </c>
-      <c r="T10" s="219"/>
-    </row>
-    <row r="11" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="170">
+      <c r="T9" s="226"/>
+    </row>
+    <row r="10" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="167">
         <v>19</v>
       </c>
-      <c r="B11" s="155">
+      <c r="B10" s="152">
         <v>17</v>
       </c>
-      <c r="C11" s="155"/>
-      <c r="D11" s="155" t="s">
-        <v>79</v>
-      </c>
-      <c r="E11" s="167" t="s">
-        <v>97</v>
-      </c>
-      <c r="F11" s="168">
+      <c r="C10" s="152"/>
+      <c r="D10" s="152" t="s">
+        <v>78</v>
+      </c>
+      <c r="E10" s="164" t="s">
+        <v>96</v>
+      </c>
+      <c r="F10" s="165">
         <v>5.44</v>
       </c>
-      <c r="G11" s="168">
+      <c r="G10" s="165">
         <v>0.12</v>
       </c>
-      <c r="H11" s="169"/>
-      <c r="I11" s="171">
-        <f>SUM(F11:H11)</f>
+      <c r="H10" s="166"/>
+      <c r="I10" s="168">
+        <f>SUM(F10:H10)</f>
         <v>5.5600000000000005</v>
       </c>
-      <c r="J11" s="166">
-        <v>208571.19</v>
-      </c>
-      <c r="K11" s="164">
-        <f>J11</f>
-        <v>208571.19</v>
-      </c>
-      <c r="L11" s="164" t="s">
-        <v>134</v>
-      </c>
-      <c r="M11" s="163">
-        <f t="shared" ref="M11:M34" si="0">J11-K11</f>
-        <v>0</v>
-      </c>
-      <c r="N11" s="163">
-        <f>IF(M11&gt;0,M11*2%,0)</f>
-        <v>0</v>
-      </c>
-      <c r="O11" s="163"/>
-      <c r="P11" s="161">
-        <f>Q$2*I11/100</f>
+      <c r="J10" s="163">
+        <v>251132.19</v>
+      </c>
+      <c r="K10" s="195">
+        <f>J10</f>
+        <v>251132.19</v>
+      </c>
+      <c r="L10" s="161" t="s">
+        <v>126</v>
+      </c>
+      <c r="M10" s="160">
+        <f t="shared" ref="M10:M33" si="0">J10-K10</f>
+        <v>0</v>
+      </c>
+      <c r="N10" s="160">
+        <f>IF(M10&gt;0,M10*2%,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O10" s="160"/>
+      <c r="P10" s="158">
+        <f>Q$2*I10/100</f>
         <v>148941.85546000002</v>
       </c>
-      <c r="Q11" s="162">
-        <f>F$2*I11/100</f>
-        <v>0</v>
-      </c>
-      <c r="R11" s="162">
+      <c r="Q10" s="159">
+        <f>F$2*I10/100</f>
+        <v>0</v>
+      </c>
+      <c r="R10" s="159">
         <f>K$2/18</f>
         <v>102189.93055555556</v>
       </c>
-      <c r="S11" s="160">
-        <f>ROUND(SUM(M11:R11),0) + U11</f>
+      <c r="S10" s="157">
+        <f>ROUND(SUM(M10:R10),0) + U10</f>
         <v>251132.19</v>
       </c>
-      <c r="T11" s="160">
-        <f t="shared" ref="T11:T34" si="1">ROUND(S11*3%,0) + S11</f>
+      <c r="T10" s="157">
+        <f t="shared" ref="T10:T33" si="1">ROUND(S10*3%,0) + S10</f>
         <v>258666.19</v>
       </c>
+      <c r="U10" s="32">
+        <f t="shared" ref="U10:U15" si="2">A10/100</f>
+        <v>0.19</v>
+      </c>
+      <c r="V10" s="32" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="11" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="155">
+        <v>20</v>
+      </c>
+      <c r="B11" s="131"/>
+      <c r="C11" s="131"/>
+      <c r="D11" s="131" t="s">
+        <v>79</v>
+      </c>
+      <c r="E11" s="93" t="s">
+        <v>97</v>
+      </c>
+      <c r="F11" s="94">
+        <v>2.87</v>
+      </c>
+      <c r="G11" s="94"/>
+      <c r="H11" s="137"/>
+      <c r="I11" s="138">
+        <f t="shared" ref="I11:I33" si="3">SUM(F11:H11)</f>
+        <v>2.87</v>
+      </c>
+      <c r="J11" s="95">
+        <v>76882.2</v>
+      </c>
+      <c r="K11" s="193">
+        <v>99395</v>
+      </c>
+      <c r="L11" s="118" t="s">
+        <v>126</v>
+      </c>
+      <c r="M11" s="96">
+        <f t="shared" si="0"/>
+        <v>-22512.800000000003</v>
+      </c>
+      <c r="N11" s="160">
+        <f t="shared" ref="N11:N33" si="4">IF(M11&gt;0,M11*2%,0)</f>
+        <v>0</v>
+      </c>
+      <c r="O11" s="96"/>
+      <c r="P11" s="97">
+        <f t="shared" ref="P11:P33" si="5">Q$2*I11/100</f>
+        <v>76881.857045000012</v>
+      </c>
+      <c r="Q11" s="98">
+        <f t="shared" ref="Q11:Q33" si="6">F$2*I11/100</f>
+        <v>0</v>
+      </c>
+      <c r="R11" s="98"/>
+      <c r="S11" s="157">
+        <f t="shared" ref="S11:S26" si="7">ROUND(SUM(M11:R11),0) + U11</f>
+        <v>54369.2</v>
+      </c>
+      <c r="T11" s="139">
+        <f t="shared" si="1"/>
+        <v>56000.2</v>
+      </c>
       <c r="U11" s="32">
-        <f t="shared" ref="U11:U16" si="2">A11/100</f>
-        <v>0.19</v>
+        <f t="shared" si="2"/>
+        <v>0.2</v>
       </c>
       <c r="V11" s="32" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="12" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="158">
-        <v>20</v>
-      </c>
-      <c r="B12" s="132"/>
+        <v>131</v>
+      </c>
+    </row>
+    <row r="12" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="156">
+        <v>21</v>
+      </c>
+      <c r="B12" s="132">
+        <v>15</v>
+      </c>
       <c r="C12" s="132"/>
       <c r="D12" s="132" t="s">
         <v>80</v>
       </c>
-      <c r="E12" s="93" t="s">
+      <c r="E12" s="99" t="s">
         <v>98</v>
       </c>
       <c r="F12" s="94">
-        <v>2.87</v>
-      </c>
-      <c r="G12" s="94"/>
-      <c r="H12" s="138"/>
-      <c r="I12" s="139">
-        <f t="shared" ref="I12:I34" si="3">SUM(F12:H12)</f>
-        <v>2.87</v>
-      </c>
-      <c r="J12" s="95">
-        <v>99345.2</v>
+        <v>5.44</v>
+      </c>
+      <c r="G12" s="94">
+        <v>0.12</v>
+      </c>
+      <c r="H12" s="137"/>
+      <c r="I12" s="138">
+        <f t="shared" si="3"/>
+        <v>5.5600000000000005</v>
+      </c>
+      <c r="J12" s="100">
+        <v>267566.21000000002</v>
       </c>
       <c r="K12" s="100">
-        <f>J12</f>
-        <v>99345.2</v>
+        <v>0</v>
       </c>
       <c r="L12" s="118" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="M12" s="96">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N12" s="163">
-        <f t="shared" ref="N12:N34" si="4">IF(M12&gt;0,M12*2%,0)</f>
-        <v>0</v>
+        <v>267566.21000000002</v>
+      </c>
+      <c r="N12" s="160">
+        <f t="shared" si="4"/>
+        <v>5351.3242000000009</v>
       </c>
       <c r="O12" s="96"/>
       <c r="P12" s="97">
-        <f t="shared" ref="P12:P34" si="5">Q$2*I12/100</f>
-        <v>76881.857045000012</v>
+        <f t="shared" si="5"/>
+        <v>148941.85546000002</v>
       </c>
       <c r="Q12" s="98">
-        <f t="shared" ref="Q12:Q34" si="6">F$2*I12/100</f>
-        <v>0</v>
-      </c>
-      <c r="R12" s="98"/>
-      <c r="S12" s="160">
-        <f t="shared" ref="S12:S27" si="7">ROUND(SUM(M12:R12),0) + U12</f>
-        <v>76882.2</v>
-      </c>
-      <c r="T12" s="140">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="R12" s="159">
+        <f>K$2/18</f>
+        <v>102189.93055555556</v>
+      </c>
+      <c r="S12" s="157">
+        <f t="shared" si="7"/>
+        <v>524049.21</v>
+      </c>
+      <c r="T12" s="139">
         <f t="shared" si="1"/>
-        <v>79188.2</v>
+        <v>539770.21</v>
       </c>
       <c r="U12" s="32">
         <f t="shared" si="2"/>
-        <v>0.2</v>
-      </c>
-      <c r="V12" s="32" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="13" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="159">
-        <v>21</v>
-      </c>
-      <c r="B13" s="133">
-        <v>15</v>
-      </c>
-      <c r="C13" s="133"/>
-      <c r="D13" s="133" t="s">
+        <v>0.21</v>
+      </c>
+      <c r="V12" s="31"/>
+    </row>
+    <row r="13" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="155">
+        <v>22</v>
+      </c>
+      <c r="B13" s="131"/>
+      <c r="C13" s="131"/>
+      <c r="D13" s="131" t="s">
         <v>81</v>
       </c>
-      <c r="E13" s="99" t="s">
-        <v>99</v>
+      <c r="E13" s="93" t="s">
+        <v>97</v>
       </c>
       <c r="F13" s="94">
-        <v>5.44</v>
-      </c>
-      <c r="G13" s="94">
-        <v>0.12</v>
-      </c>
-      <c r="H13" s="138"/>
-      <c r="I13" s="139">
+        <v>2.87</v>
+      </c>
+      <c r="G13" s="94"/>
+      <c r="H13" s="137"/>
+      <c r="I13" s="138">
         <f t="shared" si="3"/>
-        <v>5.5600000000000005</v>
-      </c>
-      <c r="J13" s="100">
-        <v>208571.21</v>
-      </c>
-      <c r="K13" s="100">
-        <f>192459.4</f>
-        <v>192459.4</v>
+        <v>2.87</v>
+      </c>
+      <c r="J13" s="95">
+        <v>76882.22</v>
+      </c>
+      <c r="K13" s="193">
+        <f>J13</f>
+        <v>76882.22</v>
       </c>
       <c r="L13" s="118" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="M13" s="96">
         <f t="shared" si="0"/>
-        <v>16111.809999999998</v>
-      </c>
-      <c r="N13" s="163">
+        <v>0</v>
+      </c>
+      <c r="N13" s="160">
         <f t="shared" si="4"/>
-        <v>322.23619999999994</v>
+        <v>0</v>
       </c>
       <c r="O13" s="96"/>
       <c r="P13" s="97">
         <f t="shared" si="5"/>
-        <v>148941.85546000002</v>
+        <v>76881.857045000012</v>
       </c>
       <c r="Q13" s="98">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="R13" s="162">
-        <f>K$2/18</f>
-        <v>102189.93055555556</v>
-      </c>
-      <c r="S13" s="160">
+      <c r="R13" s="98"/>
+      <c r="S13" s="157">
         <f t="shared" si="7"/>
-        <v>267566.21000000002</v>
-      </c>
-      <c r="T13" s="140">
+        <v>76882.22</v>
+      </c>
+      <c r="T13" s="139">
         <f t="shared" si="1"/>
-        <v>275593.21000000002</v>
+        <v>79188.22</v>
       </c>
       <c r="U13" s="32">
         <f t="shared" si="2"/>
-        <v>0.21</v>
-      </c>
-      <c r="V13" s="31"/>
-    </row>
-    <row r="14" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="158">
-        <v>22</v>
-      </c>
-      <c r="B14" s="132"/>
-      <c r="C14" s="132"/>
-      <c r="D14" s="132" t="s">
+        <v>0.22</v>
+      </c>
+      <c r="V13" t="s">
+        <v>118</v>
+      </c>
+      <c r="W13" s="32"/>
+    </row>
+    <row r="14" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="155">
+        <v>23</v>
+      </c>
+      <c r="B14" s="131">
+        <v>7</v>
+      </c>
+      <c r="C14" s="131" t="s">
+        <v>74</v>
+      </c>
+      <c r="D14" s="131" t="s">
         <v>82</v>
       </c>
       <c r="E14" s="93" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F14" s="94">
-        <v>2.87</v>
-      </c>
-      <c r="G14" s="94"/>
-      <c r="H14" s="138"/>
-      <c r="I14" s="139">
+        <v>5.44</v>
+      </c>
+      <c r="G14" s="94">
+        <v>0.41</v>
+      </c>
+      <c r="H14" s="137">
+        <v>0.09</v>
+      </c>
+      <c r="I14" s="138">
         <f t="shared" si="3"/>
-        <v>2.87</v>
+        <v>5.94</v>
       </c>
       <c r="J14" s="95">
-        <v>99345.22</v>
-      </c>
-      <c r="K14" s="100">
-        <f>J14</f>
-        <v>99345.22</v>
+        <v>261311.23</v>
+      </c>
+      <c r="K14" s="193">
+        <f>19167.23+242144.23</f>
+        <v>261311.46000000002</v>
       </c>
       <c r="L14" s="118" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="M14" s="96">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N14" s="163">
+        <v>-0.23000000001047738</v>
+      </c>
+      <c r="N14" s="160">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O14" s="96"/>
       <c r="P14" s="97">
         <f t="shared" si="5"/>
-        <v>76881.857045000012</v>
+        <v>159121.33479000002</v>
       </c>
       <c r="Q14" s="98">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="R14" s="98"/>
-      <c r="S14" s="160">
+      <c r="R14" s="159">
+        <f>K$2/18</f>
+        <v>102189.93055555556</v>
+      </c>
+      <c r="S14" s="157">
         <f t="shared" si="7"/>
-        <v>76882.22</v>
-      </c>
-      <c r="T14" s="140">
+        <v>261311.23</v>
+      </c>
+      <c r="T14" s="139">
         <f t="shared" si="1"/>
-        <v>79188.22</v>
+        <v>269150.23</v>
       </c>
       <c r="U14" s="32">
         <f t="shared" si="2"/>
-        <v>0.22</v>
-      </c>
-      <c r="V14" t="s">
-        <v>123</v>
+        <v>0.23</v>
       </c>
       <c r="W14" s="32"/>
     </row>
-    <row r="15" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="158">
-        <v>23</v>
-      </c>
-      <c r="B15" s="132">
-        <v>7</v>
-      </c>
-      <c r="C15" s="132" t="s">
-        <v>75</v>
-      </c>
-      <c r="D15" s="132" t="s">
+    <row r="15" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="155">
+        <v>24</v>
+      </c>
+      <c r="B15" s="131"/>
+      <c r="C15" s="131"/>
+      <c r="D15" s="131" t="s">
         <v>83</v>
       </c>
       <c r="E15" s="93" t="s">
         <v>100</v>
       </c>
       <c r="F15" s="94">
-        <v>5.44</v>
-      </c>
-      <c r="G15" s="94">
-        <v>0.41</v>
-      </c>
-      <c r="H15" s="138">
-        <v>0.09</v>
-      </c>
-      <c r="I15" s="139">
+        <v>2.87</v>
+      </c>
+      <c r="G15" s="94"/>
+      <c r="H15" s="137"/>
+      <c r="I15" s="138">
         <f t="shared" si="3"/>
-        <v>5.94</v>
+        <v>2.87</v>
       </c>
       <c r="J15" s="95">
-        <v>221724.23</v>
-      </c>
-      <c r="K15" s="100">
-        <f>J15</f>
-        <v>221724.23</v>
+        <v>76882.240000000005</v>
+      </c>
+      <c r="K15" s="193">
+        <v>114800.24</v>
       </c>
       <c r="L15" s="118" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="M15" s="96">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N15" s="163">
+        <v>-37918</v>
+      </c>
+      <c r="N15" s="160">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O15" s="96"/>
       <c r="P15" s="97">
         <f t="shared" si="5"/>
-        <v>159121.33479000002</v>
+        <v>76881.857045000012</v>
       </c>
       <c r="Q15" s="98">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="R15" s="162">
-        <f>K$2/18</f>
-        <v>102189.93055555556</v>
-      </c>
-      <c r="S15" s="160">
+      <c r="R15" s="98"/>
+      <c r="S15" s="157">
         <f t="shared" si="7"/>
-        <v>261311.23</v>
-      </c>
-      <c r="T15" s="140">
+        <v>38964.239999999998</v>
+      </c>
+      <c r="T15" s="139">
         <f t="shared" si="1"/>
-        <v>269150.23</v>
+        <v>40133.24</v>
       </c>
       <c r="U15" s="32">
         <f t="shared" si="2"/>
-        <v>0.23</v>
-      </c>
-      <c r="W15" s="32"/>
-    </row>
-    <row r="16" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="158">
-        <v>24</v>
-      </c>
-      <c r="B16" s="132"/>
-      <c r="C16" s="132"/>
-      <c r="D16" s="132" t="s">
+        <v>0.24</v>
+      </c>
+      <c r="V15" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="16" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="155" t="s">
+        <v>71</v>
+      </c>
+      <c r="B16" s="131">
+        <v>9</v>
+      </c>
+      <c r="C16" s="131"/>
+      <c r="D16" s="131" t="s">
         <v>84</v>
       </c>
       <c r="E16" s="93" t="s">
-        <v>101</v>
-      </c>
-      <c r="F16" s="94">
-        <v>2.87</v>
-      </c>
-      <c r="G16" s="94"/>
-      <c r="H16" s="138"/>
-      <c r="I16" s="139">
+        <v>100</v>
+      </c>
+      <c r="F16" s="94"/>
+      <c r="G16" s="94">
+        <v>0.53</v>
+      </c>
+      <c r="H16" s="137"/>
+      <c r="I16" s="138">
         <f t="shared" si="3"/>
-        <v>2.87</v>
+        <v>0.53</v>
       </c>
       <c r="J16" s="95">
-        <v>99343.24</v>
-      </c>
-      <c r="K16" s="100">
+        <v>116388.24</v>
+      </c>
+      <c r="K16" s="193">
         <f>J16</f>
-        <v>99343.24</v>
+        <v>116388.24</v>
       </c>
       <c r="L16" s="118" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="M16" s="96">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N16" s="163">
+      <c r="N16" s="160">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O16" s="96"/>
       <c r="P16" s="97">
         <f t="shared" si="5"/>
-        <v>76881.857045000012</v>
+        <v>14197.694855000002</v>
       </c>
       <c r="Q16" s="98">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="R16" s="98"/>
-      <c r="S16" s="160">
+      <c r="R16" s="159">
+        <f t="shared" ref="R16:R21" si="8">K$2/18</f>
+        <v>102189.93055555556</v>
+      </c>
+      <c r="S16" s="157">
         <f t="shared" si="7"/>
-        <v>76882.240000000005</v>
-      </c>
-      <c r="T16" s="140">
+        <v>116388.24</v>
+      </c>
+      <c r="T16" s="139">
         <f t="shared" si="1"/>
-        <v>79188.240000000005</v>
+        <v>119880.24</v>
       </c>
       <c r="U16" s="32">
-        <f t="shared" si="2"/>
         <v>0.24</v>
       </c>
-      <c r="V16" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="17" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="158" t="s">
-        <v>72</v>
-      </c>
-      <c r="B17" s="132">
-        <v>9</v>
-      </c>
-      <c r="C17" s="132"/>
-      <c r="D17" s="132" t="s">
+    </row>
+    <row r="17" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="155">
+        <v>25</v>
+      </c>
+      <c r="B17" s="131">
+        <v>14</v>
+      </c>
+      <c r="C17" s="131"/>
+      <c r="D17" s="131" t="s">
         <v>85</v>
       </c>
       <c r="E17" s="93" t="s">
         <v>101</v>
       </c>
-      <c r="F17" s="94"/>
+      <c r="F17" s="94">
+        <v>5.44</v>
+      </c>
       <c r="G17" s="94">
-        <v>0.53</v>
-      </c>
-      <c r="H17" s="138"/>
-      <c r="I17" s="139">
+        <v>0.12</v>
+      </c>
+      <c r="H17" s="137"/>
+      <c r="I17" s="138">
         <f t="shared" si="3"/>
-        <v>0.53</v>
+        <v>5.5600000000000005</v>
       </c>
       <c r="J17" s="95">
-        <v>34457.24</v>
+        <v>224658.25</v>
       </c>
       <c r="K17" s="100">
-        <f>J17</f>
-        <v>34457.24</v>
+        <v>0</v>
       </c>
       <c r="L17" s="118" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="M17" s="96">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N17" s="163">
+        <v>224658.25</v>
+      </c>
+      <c r="N17" s="160">
         <f t="shared" si="4"/>
-        <v>0</v>
+        <v>4493.165</v>
       </c>
       <c r="O17" s="96"/>
       <c r="P17" s="97">
         <f t="shared" si="5"/>
-        <v>14197.694855000002</v>
+        <v>148941.85546000002</v>
       </c>
       <c r="Q17" s="98">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="R17" s="162">
-        <f t="shared" ref="R17:R22" si="8">K$2/18</f>
+      <c r="R17" s="159">
+        <f t="shared" si="8"/>
         <v>102189.93055555556</v>
       </c>
-      <c r="S17" s="160">
+      <c r="S17" s="157">
         <f t="shared" si="7"/>
-        <v>116388.24</v>
-      </c>
-      <c r="T17" s="140">
+        <v>480283.25</v>
+      </c>
+      <c r="T17" s="139">
         <f t="shared" si="1"/>
-        <v>119880.24</v>
+        <v>494691.25</v>
       </c>
       <c r="U17" s="32">
-        <v>0.24</v>
-      </c>
-    </row>
-    <row r="18" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="158">
-        <v>25</v>
-      </c>
-      <c r="B18" s="132">
-        <v>14</v>
-      </c>
-      <c r="C18" s="132"/>
-      <c r="D18" s="132" t="s">
+        <f t="shared" ref="U17:U27" si="9">A17/100</f>
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="155">
+        <f>A17+1</f>
+        <v>26</v>
+      </c>
+      <c r="B18" s="131">
+        <v>8</v>
+      </c>
+      <c r="C18" s="131"/>
+      <c r="D18" s="131" t="s">
         <v>86</v>
       </c>
       <c r="E18" s="93" t="s">
         <v>102</v>
       </c>
       <c r="F18" s="94">
-        <v>5.44</v>
+        <v>2.87</v>
       </c>
       <c r="G18" s="94">
-        <v>0.12</v>
-      </c>
-      <c r="H18" s="138"/>
-      <c r="I18" s="139">
+        <v>0.41</v>
+      </c>
+      <c r="H18" s="137"/>
+      <c r="I18" s="138">
         <f t="shared" si="3"/>
-        <v>5.5600000000000005</v>
+        <v>3.2800000000000002</v>
       </c>
       <c r="J18" s="95">
-        <v>197376.25</v>
-      </c>
-      <c r="K18" s="100">
-        <v>223850</v>
+        <v>190055.26</v>
+      </c>
+      <c r="K18" s="193">
+        <f>135644.26+54411</f>
+        <v>190055.26</v>
       </c>
       <c r="L18" s="118" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="M18" s="96">
         <f t="shared" si="0"/>
-        <v>-26473.75</v>
-      </c>
-      <c r="N18" s="163">
+        <v>0</v>
+      </c>
+      <c r="N18" s="160">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O18" s="96"/>
       <c r="P18" s="97">
         <f t="shared" si="5"/>
-        <v>148941.85546000002</v>
+        <v>87864.979480000009</v>
       </c>
       <c r="Q18" s="98">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="R18" s="162">
+      <c r="R18" s="159">
         <f t="shared" si="8"/>
         <v>102189.93055555556</v>
       </c>
-      <c r="S18" s="160">
+      <c r="S18" s="157">
         <f t="shared" si="7"/>
-        <v>224658.25</v>
-      </c>
-      <c r="T18" s="140">
+        <v>190055.26</v>
+      </c>
+      <c r="T18" s="139">
         <f t="shared" si="1"/>
-        <v>231398.25</v>
+        <v>195757.26</v>
       </c>
       <c r="U18" s="32">
-        <f t="shared" ref="U18:U28" si="9">A18/100</f>
-        <v>0.25</v>
-      </c>
-    </row>
-    <row r="19" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="158">
-        <f>A18+1</f>
-        <v>26</v>
-      </c>
-      <c r="B19" s="132">
-        <v>8</v>
-      </c>
-      <c r="C19" s="132"/>
-      <c r="D19" s="132" t="s">
+        <f t="shared" si="9"/>
+        <v>0.26</v>
+      </c>
+      <c r="V18" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="19" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="155">
+        <f t="shared" ref="A19:A27" si="10">A18+1</f>
+        <v>27</v>
+      </c>
+      <c r="B19" s="131">
+        <v>13</v>
+      </c>
+      <c r="C19" s="131"/>
+      <c r="D19" s="131" t="s">
         <v>87</v>
       </c>
       <c r="E19" s="93" t="s">
         <v>103</v>
       </c>
       <c r="F19" s="94">
-        <v>2.87</v>
+        <v>5.44</v>
       </c>
       <c r="G19" s="94">
-        <v>0.41</v>
-      </c>
-      <c r="H19" s="138"/>
-      <c r="I19" s="139">
+        <v>0.12</v>
+      </c>
+      <c r="H19" s="137"/>
+      <c r="I19" s="138">
         <f t="shared" si="3"/>
-        <v>3.2800000000000002</v>
+        <v>5.5600000000000005</v>
       </c>
       <c r="J19" s="95">
-        <v>129648.26</v>
-      </c>
-      <c r="K19" s="100">
-        <f>J19</f>
-        <v>129648.26</v>
+        <v>242587.27</v>
+      </c>
+      <c r="K19" s="193">
+        <v>218300.27</v>
       </c>
       <c r="L19" s="118" t="s">
-        <v>134</v>
+        <v>55</v>
       </c>
       <c r="M19" s="96">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N19" s="163">
-        <f t="shared" si="4"/>
+        <v>24287</v>
+      </c>
+      <c r="N19" s="160">
         <v>0</v>
       </c>
       <c r="O19" s="96"/>
       <c r="P19" s="97">
         <f t="shared" si="5"/>
-        <v>87864.979480000009</v>
+        <v>148941.85546000002</v>
       </c>
       <c r="Q19" s="98">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="R19" s="162">
+      <c r="R19" s="159">
         <f t="shared" si="8"/>
         <v>102189.93055555556</v>
       </c>
-      <c r="S19" s="160">
+      <c r="S19" s="157">
         <f t="shared" si="7"/>
-        <v>190055.26</v>
-      </c>
-      <c r="T19" s="140">
+        <v>275419.27</v>
+      </c>
+      <c r="T19" s="139">
         <f t="shared" si="1"/>
-        <v>195757.26</v>
+        <v>283682.27</v>
       </c>
       <c r="U19" s="32">
         <f t="shared" si="9"/>
-        <v>0.26</v>
-      </c>
-      <c r="V19" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="20" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="158">
-        <f t="shared" ref="A20:A28" si="10">A19+1</f>
-        <v>27</v>
-      </c>
-      <c r="B20" s="132">
-        <v>13</v>
-      </c>
-      <c r="C20" s="132"/>
-      <c r="D20" s="132" t="s">
+        <v>0.27</v>
+      </c>
+    </row>
+    <row r="20" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="155">
+        <f t="shared" si="10"/>
+        <v>28</v>
+      </c>
+      <c r="B20" s="131">
+        <v>6</v>
+      </c>
+      <c r="C20" s="131"/>
+      <c r="D20" s="131" t="s">
         <v>88</v>
       </c>
       <c r="E20" s="93" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F20" s="94">
-        <v>5.44</v>
+        <v>2.87</v>
       </c>
       <c r="G20" s="94">
-        <v>0.12</v>
-      </c>
-      <c r="H20" s="138"/>
-      <c r="I20" s="139">
+        <v>0.41</v>
+      </c>
+      <c r="H20" s="137"/>
+      <c r="I20" s="138">
         <f t="shared" si="3"/>
-        <v>5.5600000000000005</v>
+        <v>3.2800000000000002</v>
       </c>
       <c r="J20" s="95">
-        <v>200025.27</v>
-      </c>
-      <c r="K20" s="100">
-        <v>208570</v>
+        <v>190055.28</v>
+      </c>
+      <c r="K20" s="193">
+        <f>135644.28+54411</f>
+        <v>190055.28</v>
       </c>
       <c r="L20" s="118" t="s">
-        <v>55</v>
-      </c>
-      <c r="M20" s="96">
+        <v>126</v>
+      </c>
+      <c r="M20" s="124">
         <f t="shared" si="0"/>
-        <v>-8544.7300000000105</v>
-      </c>
-      <c r="N20" s="163">
+        <v>0</v>
+      </c>
+      <c r="N20" s="160">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O20" s="96"/>
       <c r="P20" s="97">
         <f t="shared" si="5"/>
-        <v>148941.85546000002</v>
+        <v>87864.979480000009</v>
       </c>
       <c r="Q20" s="98">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="R20" s="162">
+      <c r="R20" s="159">
         <f t="shared" si="8"/>
         <v>102189.93055555556</v>
       </c>
-      <c r="S20" s="160">
+      <c r="S20" s="157">
         <f t="shared" si="7"/>
-        <v>242587.27</v>
-      </c>
-      <c r="T20" s="140">
+        <v>190055.28</v>
+      </c>
+      <c r="T20" s="139">
         <f t="shared" si="1"/>
-        <v>249865.27</v>
+        <v>195757.28</v>
       </c>
       <c r="U20" s="32">
         <f t="shared" si="9"/>
-        <v>0.27</v>
-      </c>
-    </row>
-    <row r="21" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="158">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="V20" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="21" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="155">
         <f t="shared" si="10"/>
-        <v>28</v>
-      </c>
-      <c r="B21" s="132">
-        <v>6</v>
-      </c>
-      <c r="C21" s="132"/>
-      <c r="D21" s="132" t="s">
+        <v>29</v>
+      </c>
+      <c r="B21" s="131">
+        <v>11</v>
+      </c>
+      <c r="C21" s="131" t="s">
+        <v>75</v>
+      </c>
+      <c r="D21" s="131" t="s">
         <v>89</v>
       </c>
       <c r="E21" s="93" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F21" s="94">
-        <v>2.87</v>
-      </c>
-      <c r="G21" s="94">
-        <v>0.41</v>
-      </c>
-      <c r="H21" s="138"/>
-      <c r="I21" s="139">
+        <v>5.44</v>
+      </c>
+      <c r="G21" s="137">
+        <v>0.2</v>
+      </c>
+      <c r="H21" s="137">
+        <v>0.09</v>
+      </c>
+      <c r="I21" s="138">
         <f t="shared" si="3"/>
-        <v>3.2800000000000002</v>
+        <v>5.73</v>
       </c>
       <c r="J21" s="95">
-        <v>129648.28</v>
-      </c>
-      <c r="K21" s="118">
-        <f>J21</f>
-        <v>129648.28</v>
+        <v>255686.29</v>
+      </c>
+      <c r="K21" s="193">
+        <v>233644.29</v>
       </c>
       <c r="L21" s="118" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="M21" s="124">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N21" s="163">
-        <f t="shared" si="4"/>
+        <v>22042</v>
+      </c>
+      <c r="N21" s="160">
         <v>0</v>
       </c>
       <c r="O21" s="96"/>
       <c r="P21" s="97">
         <f t="shared" si="5"/>
-        <v>87864.979480000009</v>
+        <v>153495.83305500002</v>
       </c>
       <c r="Q21" s="98">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="R21" s="162">
+      <c r="R21" s="159">
         <f t="shared" si="8"/>
         <v>102189.93055555556</v>
       </c>
-      <c r="S21" s="160">
+      <c r="S21" s="157">
         <f t="shared" si="7"/>
-        <v>190055.28</v>
-      </c>
-      <c r="T21" s="140">
+        <v>277728.28999999998</v>
+      </c>
+      <c r="T21" s="139">
         <f t="shared" si="1"/>
-        <v>195757.28</v>
+        <v>286060.28999999998</v>
       </c>
       <c r="U21" s="32">
         <f t="shared" si="9"/>
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="V21" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="22" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="158">
+        <v>0.28999999999999998</v>
+      </c>
+    </row>
+    <row r="22" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A22" s="155">
         <f t="shared" si="10"/>
-        <v>29</v>
-      </c>
-      <c r="B22" s="132">
-        <v>11</v>
-      </c>
-      <c r="C22" s="132" t="s">
-        <v>76</v>
-      </c>
-      <c r="D22" s="132" t="s">
+        <v>30</v>
+      </c>
+      <c r="B22" s="131"/>
+      <c r="C22" s="131"/>
+      <c r="D22" s="131" t="s">
         <v>90</v>
       </c>
       <c r="E22" s="93" t="s">
         <v>105</v>
       </c>
       <c r="F22" s="94">
-        <v>5.44</v>
-      </c>
-      <c r="G22" s="138">
-        <v>0.2</v>
-      </c>
-      <c r="H22" s="138">
-        <v>0.09</v>
-      </c>
-      <c r="I22" s="139">
+        <v>2.87</v>
+      </c>
+      <c r="G22" s="94"/>
+      <c r="H22" s="137"/>
+      <c r="I22" s="138">
         <f t="shared" si="3"/>
-        <v>5.73</v>
+        <v>2.87</v>
       </c>
       <c r="J22" s="95">
-        <v>214455.29</v>
-      </c>
-      <c r="K22" s="100">
-        <f>J22</f>
-        <v>214455.29</v>
+        <v>76637.3</v>
+      </c>
+      <c r="K22" s="193">
+        <v>76700</v>
       </c>
       <c r="L22" s="118" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="M22" s="124">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N22" s="163">
+        <v>-62.69999999999709</v>
+      </c>
+      <c r="N22" s="160">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O22" s="96"/>
       <c r="P22" s="97">
         <f t="shared" si="5"/>
-        <v>153495.83305500002</v>
+        <v>76881.857045000012</v>
       </c>
       <c r="Q22" s="98">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="R22" s="162">
-        <f t="shared" si="8"/>
-        <v>102189.93055555556</v>
-      </c>
-      <c r="S22" s="160">
+      <c r="R22" s="98"/>
+      <c r="S22" s="157">
         <f t="shared" si="7"/>
-        <v>255686.29</v>
-      </c>
-      <c r="T22" s="140">
+        <v>76819.3</v>
+      </c>
+      <c r="T22" s="139">
         <f t="shared" si="1"/>
-        <v>263357.29000000004</v>
+        <v>79124.3</v>
       </c>
       <c r="U22" s="32">
         <f t="shared" si="9"/>
-        <v>0.28999999999999998</v>
-      </c>
-    </row>
-    <row r="23" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="158">
+        <v>0.3</v>
+      </c>
+      <c r="V22" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="23" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="155">
         <f t="shared" si="10"/>
-        <v>30</v>
-      </c>
-      <c r="B23" s="132"/>
-      <c r="C23" s="132"/>
-      <c r="D23" s="132" t="s">
+        <v>31</v>
+      </c>
+      <c r="B23" s="131">
+        <v>1</v>
+      </c>
+      <c r="C23" s="131" t="s">
+        <v>73</v>
+      </c>
+      <c r="D23" s="131" t="s">
         <v>91</v>
       </c>
       <c r="E23" s="93" t="s">
         <v>106</v>
       </c>
       <c r="F23" s="94">
-        <v>2.87</v>
-      </c>
-      <c r="G23" s="94"/>
-      <c r="H23" s="138"/>
-      <c r="I23" s="139">
+        <v>5.44</v>
+      </c>
+      <c r="G23" s="94">
+        <v>0.48</v>
+      </c>
+      <c r="H23" s="137">
+        <v>0.09</v>
+      </c>
+      <c r="I23" s="138">
         <f t="shared" si="3"/>
-        <v>2.87</v>
+        <v>6.01</v>
       </c>
       <c r="J23" s="95">
-        <v>99255.3</v>
-      </c>
-      <c r="K23" s="100">
-        <v>99500</v>
+        <v>263186.31</v>
+      </c>
+      <c r="K23" s="193">
+        <v>244944.31</v>
       </c>
       <c r="L23" s="118" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="M23" s="124">
         <f t="shared" si="0"/>
-        <v>-244.69999999999709</v>
-      </c>
-      <c r="N23" s="163">
-        <f t="shared" si="4"/>
+        <v>18242</v>
+      </c>
+      <c r="N23" s="160">
         <v>0</v>
       </c>
       <c r="O23" s="96"/>
       <c r="P23" s="97">
         <f t="shared" si="5"/>
-        <v>76881.857045000012</v>
+        <v>160996.50203500001</v>
       </c>
       <c r="Q23" s="98">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="R23" s="98"/>
-      <c r="S23" s="160">
+      <c r="R23" s="159">
+        <f>K$2/18</f>
+        <v>102189.93055555556</v>
+      </c>
+      <c r="S23" s="157">
         <f t="shared" si="7"/>
-        <v>76637.3</v>
-      </c>
-      <c r="T23" s="140">
+        <v>281428.31</v>
+      </c>
+      <c r="T23" s="139">
         <f t="shared" si="1"/>
-        <v>78936.3</v>
+        <v>289871.31</v>
       </c>
       <c r="U23" s="32">
         <f t="shared" si="9"/>
-        <v>0.3</v>
-      </c>
-      <c r="V23" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="24" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="158">
+        <v>0.31</v>
+      </c>
+    </row>
+    <row r="24" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="155">
         <f t="shared" si="10"/>
-        <v>31</v>
-      </c>
-      <c r="B24" s="132">
-        <v>1</v>
-      </c>
-      <c r="C24" s="132" t="s">
-        <v>74</v>
-      </c>
+        <v>32</v>
+      </c>
+      <c r="B24" s="132"/>
+      <c r="C24" s="132"/>
       <c r="D24" s="132" t="s">
         <v>92</v>
       </c>
-      <c r="E24" s="93" t="s">
+      <c r="E24" s="99" t="s">
         <v>107</v>
       </c>
       <c r="F24" s="94">
-        <v>5.44</v>
-      </c>
-      <c r="G24" s="94">
-        <v>0.48</v>
-      </c>
-      <c r="H24" s="138">
-        <v>0.09</v>
-      </c>
-      <c r="I24" s="139">
+        <v>2.87</v>
+      </c>
+      <c r="G24" s="133"/>
+      <c r="H24" s="137"/>
+      <c r="I24" s="138">
         <f t="shared" si="3"/>
-        <v>6.01</v>
-      </c>
-      <c r="J24" s="95">
-        <v>224147.31</v>
-      </c>
-      <c r="K24" s="100">
+        <v>2.87</v>
+      </c>
+      <c r="J24" s="100">
+        <v>79187.320000000007</v>
+      </c>
+      <c r="K24" s="193">
         <f>J24</f>
-        <v>224147.31</v>
+        <v>79187.320000000007</v>
       </c>
       <c r="L24" s="118" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="M24" s="124">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N24" s="163">
+      <c r="N24" s="160">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O24" s="96"/>
       <c r="P24" s="97">
         <f t="shared" si="5"/>
-        <v>160996.50203500001</v>
+        <v>76881.857045000012</v>
       </c>
       <c r="Q24" s="98">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="R24" s="162">
-        <f>K$2/18</f>
-        <v>102189.93055555556</v>
-      </c>
-      <c r="S24" s="160">
+      <c r="R24" s="98"/>
+      <c r="S24" s="157">
         <f t="shared" si="7"/>
-        <v>263186.31</v>
-      </c>
-      <c r="T24" s="140">
+        <v>76882.320000000007</v>
+      </c>
+      <c r="T24" s="139">
         <f t="shared" si="1"/>
-        <v>271082.31</v>
+        <v>79188.320000000007</v>
       </c>
       <c r="U24" s="32">
         <f t="shared" si="9"/>
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="25" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="158">
+        <v>0.32</v>
+      </c>
+      <c r="V24" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="25" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="155">
         <f t="shared" si="10"/>
-        <v>32</v>
-      </c>
-      <c r="B25" s="133"/>
-      <c r="C25" s="133"/>
-      <c r="D25" s="133" t="s">
+        <v>33</v>
+      </c>
+      <c r="B25" s="131">
+        <v>10</v>
+      </c>
+      <c r="C25" s="131"/>
+      <c r="D25" s="131" t="s">
         <v>93</v>
       </c>
-      <c r="E25" s="99" t="s">
+      <c r="E25" s="93" t="s">
         <v>108</v>
       </c>
       <c r="F25" s="94">
-        <v>2.87</v>
-      </c>
-      <c r="G25" s="134"/>
-      <c r="H25" s="138"/>
-      <c r="I25" s="139">
+        <v>5.44</v>
+      </c>
+      <c r="G25" s="94">
+        <v>0.45</v>
+      </c>
+      <c r="H25" s="137"/>
+      <c r="I25" s="138">
         <f t="shared" si="3"/>
-        <v>2.87</v>
-      </c>
-      <c r="J25" s="100">
-        <v>99344.320000000007</v>
-      </c>
-      <c r="K25" s="100">
-        <f>99345</f>
-        <v>99345</v>
+        <v>5.8900000000000006</v>
+      </c>
+      <c r="J25" s="95">
+        <v>259972.33</v>
+      </c>
+      <c r="K25" s="193">
+        <f>J25</f>
+        <v>259972.33</v>
       </c>
       <c r="L25" s="118" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="M25" s="124">
         <f t="shared" si="0"/>
-        <v>-0.67999999999301508</v>
-      </c>
-      <c r="N25" s="163">
+        <v>0</v>
+      </c>
+      <c r="N25" s="160">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O25" s="96"/>
       <c r="P25" s="97">
         <f t="shared" si="5"/>
-        <v>76881.857045000012</v>
+        <v>157781.92961500003</v>
       </c>
       <c r="Q25" s="98">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="R25" s="98"/>
-      <c r="S25" s="160">
+      <c r="R25" s="159">
+        <f>K$2/18</f>
+        <v>102189.93055555556</v>
+      </c>
+      <c r="S25" s="157">
         <f t="shared" si="7"/>
-        <v>76881.320000000007</v>
-      </c>
-      <c r="T25" s="140">
+        <v>259972.33</v>
+      </c>
+      <c r="T25" s="139">
         <f t="shared" si="1"/>
-        <v>79187.320000000007</v>
+        <v>267771.32999999996</v>
       </c>
       <c r="U25" s="32">
         <f t="shared" si="9"/>
-        <v>0.32</v>
-      </c>
-      <c r="V25" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="26" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="158">
+        <v>0.33</v>
+      </c>
+    </row>
+    <row r="26" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="155">
         <f t="shared" si="10"/>
-        <v>33</v>
-      </c>
-      <c r="B26" s="132">
-        <v>10</v>
-      </c>
-      <c r="C26" s="132"/>
-      <c r="D26" s="132" t="s">
+        <v>34</v>
+      </c>
+      <c r="B26" s="131"/>
+      <c r="C26" s="131"/>
+      <c r="D26" s="131" t="s">
         <v>94</v>
       </c>
       <c r="E26" s="93" t="s">
         <v>109</v>
       </c>
       <c r="F26" s="94">
-        <v>5.44</v>
-      </c>
-      <c r="G26" s="94">
-        <v>0.45</v>
-      </c>
-      <c r="H26" s="138"/>
-      <c r="I26" s="139">
+        <v>2.87</v>
+      </c>
+      <c r="G26" s="94"/>
+      <c r="H26" s="137"/>
+      <c r="I26" s="138">
         <f t="shared" si="3"/>
-        <v>5.8900000000000006</v>
-      </c>
-      <c r="J26" s="95">
-        <v>219993.33</v>
-      </c>
-      <c r="K26" s="100">
-        <f>J26</f>
-        <v>219993.33</v>
+        <v>2.87</v>
+      </c>
+      <c r="J26" s="100">
+        <v>76882.34</v>
+      </c>
+      <c r="K26" s="193">
+        <v>99345.34</v>
       </c>
       <c r="L26" s="118" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="M26" s="124">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N26" s="163">
+        <v>-22463</v>
+      </c>
+      <c r="N26" s="160">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O26" s="96"/>
       <c r="P26" s="97">
         <f t="shared" si="5"/>
-        <v>157781.92961500003</v>
+        <v>76881.857045000012</v>
       </c>
       <c r="Q26" s="98">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="R26" s="162">
-        <f>K$2/18</f>
-        <v>102189.93055555556</v>
-      </c>
-      <c r="S26" s="160">
+      <c r="R26" s="98"/>
+      <c r="S26" s="157">
         <f t="shared" si="7"/>
-        <v>259972.33</v>
-      </c>
-      <c r="T26" s="140">
+        <v>54419.34</v>
+      </c>
+      <c r="T26" s="139">
         <f t="shared" si="1"/>
-        <v>267771.32999999996</v>
+        <v>56052.34</v>
       </c>
       <c r="U26" s="32">
         <f t="shared" si="9"/>
-        <v>0.33</v>
-      </c>
-    </row>
-    <row r="27" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="158">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="27" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="155">
         <f t="shared" si="10"/>
-        <v>34</v>
-      </c>
-      <c r="B27" s="132"/>
-      <c r="C27" s="132"/>
-      <c r="D27" s="132" t="s">
-        <v>95</v>
-      </c>
-      <c r="E27" s="93" t="s">
+        <v>35</v>
+      </c>
+      <c r="B27" s="131">
+        <v>4</v>
+      </c>
+      <c r="C27" s="131" t="s">
+        <v>55</v>
+      </c>
+      <c r="D27" s="232">
+        <v>9</v>
+      </c>
+      <c r="E27" s="232" t="s">
         <v>110</v>
       </c>
-      <c r="F27" s="94">
-        <v>2.87</v>
-      </c>
-      <c r="G27" s="94"/>
-      <c r="H27" s="138"/>
-      <c r="I27" s="139">
+      <c r="F27" s="136">
+        <f>7.73/2</f>
+        <v>3.8650000000000002</v>
+      </c>
+      <c r="G27" s="151">
+        <v>0.41</v>
+      </c>
+      <c r="H27" s="137">
+        <v>0.09</v>
+      </c>
+      <c r="I27" s="138">
         <f t="shared" si="3"/>
-        <v>2.87</v>
-      </c>
-      <c r="J27" s="100">
-        <v>99345.34</v>
-      </c>
-      <c r="K27" s="100">
+        <v>4.3650000000000002</v>
+      </c>
+      <c r="J27" s="95">
+        <v>447977.35</v>
+      </c>
+      <c r="K27" s="194">
         <f>J27</f>
-        <v>99345.34</v>
+        <v>447977.35</v>
       </c>
       <c r="L27" s="118" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="M27" s="124">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N27" s="163">
+      <c r="N27" s="160">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O27" s="96"/>
       <c r="P27" s="97">
         <f t="shared" si="5"/>
-        <v>76881.857045000012</v>
+        <v>116930.07177750001</v>
       </c>
       <c r="Q27" s="98">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="R27" s="98"/>
-      <c r="S27" s="160">
-        <f t="shared" si="7"/>
-        <v>76882.34</v>
-      </c>
-      <c r="T27" s="140">
+      <c r="R27" s="159">
+        <f t="shared" ref="R27:R33" si="11">K$2/18</f>
+        <v>102189.93055555556</v>
+      </c>
+      <c r="S27" s="139">
+        <f>ROUND(SUM(M27:R27)+P28+Q28+R28,0) + U27</f>
+        <v>435829.35</v>
+      </c>
+      <c r="T27" s="139">
         <f t="shared" si="1"/>
-        <v>79188.34</v>
+        <v>448904.35</v>
       </c>
       <c r="U27" s="32">
         <f t="shared" si="9"/>
-        <v>0.34</v>
-      </c>
-    </row>
-    <row r="28" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="158">
-        <f t="shared" si="10"/>
-        <v>35</v>
-      </c>
-      <c r="B28" s="132">
-        <v>4</v>
-      </c>
-      <c r="C28" s="132" t="s">
-        <v>55</v>
-      </c>
-      <c r="D28" s="225">
-        <v>9</v>
-      </c>
-      <c r="E28" s="225" t="s">
-        <v>111</v>
-      </c>
-      <c r="F28" s="137">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="28" spans="1:22" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="155" t="s">
+        <v>71</v>
+      </c>
+      <c r="B28" s="131">
+        <v>5</v>
+      </c>
+      <c r="C28" s="134"/>
+      <c r="D28" s="233"/>
+      <c r="E28" s="233"/>
+      <c r="F28" s="136">
         <f>7.73/2</f>
         <v>3.8650000000000002</v>
       </c>
-      <c r="G28" s="154">
+      <c r="G28" s="151">
         <v>0.41</v>
       </c>
-      <c r="H28" s="138">
-        <v>0.09</v>
-      </c>
-      <c r="I28" s="139">
+      <c r="H28" s="137"/>
+      <c r="I28" s="138">
         <f t="shared" si="3"/>
-        <v>4.3650000000000002</v>
+        <v>4.2750000000000004</v>
       </c>
       <c r="J28" s="95">
-        <v>337100.35</v>
-      </c>
-      <c r="K28" s="118">
-        <v>338000</v>
+        <v>0</v>
+      </c>
+      <c r="K28" s="100">
+        <f>J28</f>
+        <v>0</v>
       </c>
       <c r="L28" s="118" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="M28" s="124">
         <f t="shared" si="0"/>
-        <v>-899.65000000002328</v>
-      </c>
-      <c r="N28" s="163">
+        <v>0</v>
+      </c>
+      <c r="N28" s="160">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O28" s="96"/>
       <c r="P28" s="97">
         <f t="shared" si="5"/>
-        <v>116930.07177750001</v>
+        <v>114519.14246250002</v>
       </c>
       <c r="Q28" s="98">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="R28" s="162">
-        <f t="shared" ref="R28:R34" si="11">K$2/18</f>
+      <c r="R28" s="159">
+        <f t="shared" si="11"/>
         <v>102189.93055555556</v>
       </c>
-      <c r="S28" s="140">
-        <f>ROUND(SUM(M28:R28)+P29+Q29+R29,0) + U28</f>
-        <v>434929.35</v>
-      </c>
-      <c r="T28" s="140">
+      <c r="S28" s="139">
+        <v>0</v>
+      </c>
+      <c r="T28" s="139">
         <f t="shared" si="1"/>
-        <v>447977.35</v>
-      </c>
-      <c r="U28" s="32">
-        <f t="shared" si="9"/>
-        <v>0.35</v>
-      </c>
-    </row>
-    <row r="29" spans="1:22" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="158" t="s">
-        <v>72</v>
-      </c>
-      <c r="B29" s="132">
-        <v>5</v>
-      </c>
-      <c r="C29" s="135"/>
-      <c r="D29" s="226"/>
-      <c r="E29" s="226"/>
-      <c r="F29" s="137">
+        <v>0</v>
+      </c>
+      <c r="U28" s="32"/>
+    </row>
+    <row r="29" spans="1:22" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A29" s="155">
+        <v>36</v>
+      </c>
+      <c r="B29" s="131">
+        <v>2</v>
+      </c>
+      <c r="C29" s="134" t="s">
+        <v>45</v>
+      </c>
+      <c r="D29" s="232">
+        <v>10</v>
+      </c>
+      <c r="E29" s="235" t="s">
+        <v>111</v>
+      </c>
+      <c r="F29" s="136">
         <f>7.73/2</f>
         <v>3.8650000000000002</v>
       </c>
-      <c r="G29" s="154">
-        <v>0.41</v>
-      </c>
-      <c r="H29" s="138"/>
-      <c r="I29" s="139">
+      <c r="G29" s="153">
+        <v>0.45</v>
+      </c>
+      <c r="H29" s="137">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="I29" s="138">
         <f t="shared" si="3"/>
-        <v>4.2750000000000004</v>
-      </c>
-      <c r="J29" s="95"/>
-      <c r="K29" s="100">
-        <f>J29</f>
-        <v>0</v>
+        <v>4.3850000000000007</v>
+      </c>
+      <c r="J29" s="101">
+        <v>428596.36</v>
+      </c>
+      <c r="K29" s="194">
+        <f>84907.36+343689.36</f>
+        <v>428596.72</v>
       </c>
       <c r="L29" s="118" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="M29" s="124">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N29" s="163">
+        <v>-0.35999999998603016</v>
+      </c>
+      <c r="N29" s="160">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O29" s="96"/>
       <c r="P29" s="97">
         <f t="shared" si="5"/>
-        <v>114519.14246250002</v>
+        <v>117465.83384750003</v>
       </c>
       <c r="Q29" s="98">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="R29" s="162">
+      <c r="R29" s="159">
         <f t="shared" si="11"/>
         <v>102189.93055555556</v>
       </c>
-      <c r="S29" s="140">
-        <v>0</v>
-      </c>
-      <c r="T29" s="140">
+      <c r="S29" s="139">
+        <f>ROUND(SUM(M29:R29)+P30+Q30+R30,0) + U29</f>
+        <v>428596.36</v>
+      </c>
+      <c r="T29" s="139">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="U29" s="32"/>
-    </row>
-    <row r="30" spans="1:22" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="158">
-        <v>36</v>
-      </c>
-      <c r="B30" s="132">
-        <v>2</v>
-      </c>
-      <c r="C30" s="135" t="s">
-        <v>45</v>
-      </c>
-      <c r="D30" s="225">
-        <v>10</v>
-      </c>
-      <c r="E30" s="228" t="s">
-        <v>112</v>
-      </c>
-      <c r="F30" s="137">
+        <v>441454.36</v>
+      </c>
+      <c r="U29" s="32">
+        <f>A29/100</f>
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="30" spans="1:22" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="155" t="s">
+        <v>71</v>
+      </c>
+      <c r="B30" s="131">
+        <v>18</v>
+      </c>
+      <c r="C30" s="134"/>
+      <c r="D30" s="233"/>
+      <c r="E30" s="236"/>
+      <c r="F30" s="136">
         <f>7.73/2</f>
         <v>3.8650000000000002</v>
       </c>
-      <c r="G30" s="156">
-        <v>0.45</v>
-      </c>
-      <c r="H30" s="138">
-        <v>7.0000000000000007E-2</v>
-      </c>
-      <c r="I30" s="139">
+      <c r="G30" s="154">
+        <v>0.12</v>
+      </c>
+      <c r="H30" s="137"/>
+      <c r="I30" s="138">
         <f t="shared" si="3"/>
-        <v>4.3850000000000007</v>
+        <v>3.9850000000000003</v>
       </c>
       <c r="J30" s="101">
-        <v>321950.36</v>
+        <v>0</v>
       </c>
       <c r="K30" s="118">
         <f>J30</f>
-        <v>321950.36</v>
+        <v>0</v>
       </c>
       <c r="L30" s="118" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="M30" s="124">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N30" s="163">
+      <c r="N30" s="160">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O30" s="96"/>
       <c r="P30" s="97">
         <f t="shared" si="5"/>
-        <v>117465.83384750003</v>
+        <v>106750.59244750001</v>
       </c>
       <c r="Q30" s="98">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="R30" s="162">
+      <c r="R30" s="159">
         <f t="shared" si="11"/>
         <v>102189.93055555556</v>
       </c>
-      <c r="S30" s="140">
-        <f>ROUND(SUM(M30:R30)+P31+Q31+R31,0) + U30</f>
-        <v>428596.36</v>
-      </c>
-      <c r="T30" s="140">
+      <c r="S30" s="139">
+        <v>0</v>
+      </c>
+      <c r="T30" s="139">
         <f t="shared" si="1"/>
-        <v>441454.36</v>
-      </c>
-      <c r="U30" s="32">
-        <f>A30/100</f>
-        <v>0.36</v>
-      </c>
-    </row>
-    <row r="31" spans="1:22" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="158" t="s">
-        <v>72</v>
-      </c>
-      <c r="B31" s="132">
-        <v>18</v>
-      </c>
-      <c r="C31" s="135"/>
-      <c r="D31" s="226"/>
-      <c r="E31" s="229"/>
-      <c r="F31" s="137">
-        <f>7.73/2</f>
-        <v>3.8650000000000002</v>
-      </c>
-      <c r="G31" s="157">
+        <v>0</v>
+      </c>
+      <c r="U30" s="32"/>
+    </row>
+    <row r="31" spans="1:22" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="155">
+        <v>37</v>
+      </c>
+      <c r="B31" s="131">
+        <v>12</v>
+      </c>
+      <c r="C31" s="134" t="s">
+        <v>76</v>
+      </c>
+      <c r="D31" s="232" t="s">
+        <v>95</v>
+      </c>
+      <c r="E31" s="232" t="s">
+        <v>112</v>
+      </c>
+      <c r="F31" s="136">
+        <f>12.13/3</f>
+        <v>4.0433333333333339</v>
+      </c>
+      <c r="G31" s="131">
         <v>0.12</v>
       </c>
-      <c r="H31" s="138"/>
-      <c r="I31" s="139">
+      <c r="H31" s="137">
+        <v>0.09</v>
+      </c>
+      <c r="I31" s="138">
         <f t="shared" si="3"/>
-        <v>3.9850000000000003</v>
-      </c>
-      <c r="J31" s="101"/>
-      <c r="K31" s="118">
-        <f>J31</f>
-        <v>0</v>
+        <v>4.2533333333333339</v>
+      </c>
+      <c r="J31" s="101">
+        <v>651333.37</v>
+      </c>
+      <c r="K31" s="194">
+        <v>528133.37</v>
       </c>
       <c r="L31" s="118" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="M31" s="124">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N31" s="163">
-        <f t="shared" si="4"/>
+        <v>123200</v>
+      </c>
+      <c r="N31" s="160">
         <v>0</v>
       </c>
       <c r="O31" s="96"/>
       <c r="P31" s="97">
         <f t="shared" si="5"/>
-        <v>106750.59244750001</v>
+        <v>113938.73355333335</v>
       </c>
       <c r="Q31" s="98">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="R31" s="162">
+      <c r="R31" s="159">
         <f t="shared" si="11"/>
         <v>102189.93055555556</v>
       </c>
-      <c r="S31" s="140">
-        <v>0</v>
-      </c>
-      <c r="T31" s="140">
+      <c r="S31" s="139">
+        <f>ROUND(SUM(M31:R31)+P32+P33+Q32+Q33+R32+R33,0) + U31</f>
+        <v>774533.37</v>
+      </c>
+      <c r="T31" s="139">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="U31" s="32"/>
-    </row>
-    <row r="32" spans="1:22" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="158">
-        <v>37</v>
-      </c>
-      <c r="B32" s="132">
-        <v>12</v>
-      </c>
-      <c r="C32" s="135" t="s">
-        <v>77</v>
-      </c>
-      <c r="D32" s="225" t="s">
-        <v>96</v>
-      </c>
-      <c r="E32" s="225" t="s">
-        <v>113</v>
-      </c>
-      <c r="F32" s="137">
+        <v>797769.37</v>
+      </c>
+      <c r="U31" s="32">
+        <f>A31/100</f>
+        <v>0.37</v>
+      </c>
+    </row>
+    <row r="32" spans="1:22" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="155" t="s">
+        <v>71</v>
+      </c>
+      <c r="B32" s="131">
+        <v>3</v>
+      </c>
+      <c r="C32" s="135"/>
+      <c r="D32" s="234"/>
+      <c r="E32" s="234"/>
+      <c r="F32" s="136">
         <f>12.13/3</f>
         <v>4.0433333333333339</v>
       </c>
-      <c r="G32" s="132">
-        <v>0.12</v>
-      </c>
-      <c r="H32" s="138">
-        <v>0.09</v>
-      </c>
-      <c r="I32" s="139">
+      <c r="G32" s="131">
+        <v>0.41</v>
+      </c>
+      <c r="H32" s="137"/>
+      <c r="I32" s="138">
         <f t="shared" si="3"/>
-        <v>4.2533333333333339</v>
+        <v>4.453333333333334</v>
       </c>
       <c r="J32" s="101">
-        <v>493828.37</v>
-      </c>
-      <c r="K32" s="118">
-        <f t="shared" ref="K32" si="12">J32</f>
-        <v>493828.37</v>
-      </c>
-      <c r="L32" s="118" t="s">
-        <v>134</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K32" s="118"/>
+      <c r="L32" s="118"/>
       <c r="M32" s="124">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N32" s="163">
+      <c r="N32" s="160">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
       <c r="O32" s="96"/>
       <c r="P32" s="97">
         <f t="shared" si="5"/>
-        <v>113938.73355333335</v>
+        <v>119296.35425333335</v>
       </c>
       <c r="Q32" s="98">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="R32" s="162">
+      <c r="R32" s="159">
         <f t="shared" si="11"/>
         <v>102189.93055555556</v>
       </c>
-      <c r="S32" s="140">
-        <f>ROUND(SUM(M32:R32)+P33+P34+Q33+Q34+R33+R34,0) + U32</f>
-        <v>651333.37</v>
-      </c>
-      <c r="T32" s="140">
+      <c r="S32" s="139">
+        <v>0</v>
+      </c>
+      <c r="T32" s="139">
         <f t="shared" si="1"/>
-        <v>670873.37</v>
-      </c>
-      <c r="U32" s="32">
-        <f>A32/100</f>
-        <v>0.37</v>
-      </c>
-    </row>
-    <row r="33" spans="1:21" ht="14.7" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="158" t="s">
-        <v>72</v>
-      </c>
-      <c r="B33" s="132">
-        <v>3</v>
-      </c>
-      <c r="C33" s="136"/>
-      <c r="D33" s="227"/>
-      <c r="E33" s="227"/>
-      <c r="F33" s="137">
+        <v>0</v>
+      </c>
+      <c r="U32" s="32"/>
+    </row>
+    <row r="33" spans="1:21" ht="14.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="171" t="s">
+        <v>71</v>
+      </c>
+      <c r="B33" s="151">
+        <v>16</v>
+      </c>
+      <c r="C33" s="135"/>
+      <c r="D33" s="234"/>
+      <c r="E33" s="234"/>
+      <c r="F33" s="136">
         <f>12.13/3</f>
         <v>4.0433333333333339</v>
       </c>
-      <c r="G33" s="132">
-        <v>0.41</v>
-      </c>
-      <c r="H33" s="138"/>
-      <c r="I33" s="139">
+      <c r="G33" s="151">
+        <v>0.12</v>
+      </c>
+      <c r="H33" s="172"/>
+      <c r="I33" s="173">
         <f t="shared" si="3"/>
-        <v>4.453333333333334</v>
-      </c>
-      <c r="J33" s="101"/>
+        <v>4.163333333333334</v>
+      </c>
+      <c r="J33" s="101">
+        <v>0</v>
+      </c>
       <c r="K33" s="118"/>
       <c r="L33" s="118"/>
-      <c r="M33" s="124">
+      <c r="M33" s="174">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N33" s="163">
+      <c r="N33" s="175">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O33" s="96"/>
-      <c r="P33" s="97">
+      <c r="O33" s="176"/>
+      <c r="P33" s="177">
         <f t="shared" si="5"/>
-        <v>119296.35425333335</v>
-      </c>
-      <c r="Q33" s="98">
+        <v>111527.80423833335</v>
+      </c>
+      <c r="Q33" s="178">
         <f t="shared" si="6"/>
         <v>0</v>
       </c>
-      <c r="R33" s="162">
+      <c r="R33" s="185">
         <f t="shared" si="11"/>
         <v>102189.93055555556</v>
       </c>
-      <c r="S33" s="140">
-        <v>0</v>
-      </c>
-      <c r="T33" s="140">
+      <c r="S33" s="179">
+        <v>0</v>
+      </c>
+      <c r="T33" s="179">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
       <c r="U33" s="32"/>
     </row>
-    <row r="34" spans="1:21" ht="14.7" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A34" s="176" t="s">
-        <v>72</v>
-      </c>
-      <c r="B34" s="154">
-        <v>16</v>
-      </c>
-      <c r="C34" s="136"/>
-      <c r="D34" s="227"/>
-      <c r="E34" s="227"/>
-      <c r="F34" s="137">
-        <f>12.13/3</f>
-        <v>4.0433333333333339</v>
-      </c>
-      <c r="G34" s="154">
-        <v>0.12</v>
-      </c>
-      <c r="H34" s="177"/>
-      <c r="I34" s="178">
-        <f t="shared" si="3"/>
-        <v>4.163333333333334</v>
-      </c>
-      <c r="J34" s="101"/>
-      <c r="K34" s="118"/>
-      <c r="L34" s="118"/>
-      <c r="M34" s="179">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="N34" s="180">
-        <f t="shared" si="4"/>
-        <v>0</v>
-      </c>
-      <c r="O34" s="181"/>
-      <c r="P34" s="182">
-        <f t="shared" si="5"/>
-        <v>111527.80423833335</v>
-      </c>
-      <c r="Q34" s="183">
-        <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="R34" s="190">
-        <f t="shared" si="11"/>
-        <v>102189.93055555556</v>
-      </c>
-      <c r="S34" s="184">
-        <v>0</v>
-      </c>
-      <c r="T34" s="184">
-        <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="U34" s="32"/>
-    </row>
-    <row r="35" spans="1:21" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A35" s="222" t="s">
+    <row r="34" spans="1:21" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="229" t="s">
         <v>44</v>
       </c>
-      <c r="B35" s="223"/>
-      <c r="C35" s="223"/>
-      <c r="D35" s="223"/>
-      <c r="E35" s="224"/>
-      <c r="F35" s="185"/>
-      <c r="G35" s="185"/>
-      <c r="H35" s="186">
-        <f t="shared" ref="H35:N35" si="13">SUM(H11:H34)</f>
+      <c r="B34" s="230"/>
+      <c r="C34" s="230"/>
+      <c r="D34" s="230"/>
+      <c r="E34" s="231"/>
+      <c r="F34" s="180"/>
+      <c r="G34" s="180"/>
+      <c r="H34" s="181">
+        <f t="shared" ref="H34:N34" si="12">SUM(H10:H33)</f>
         <v>0.52</v>
       </c>
-      <c r="I35" s="186">
-        <f t="shared" si="13"/>
+      <c r="I34" s="181">
+        <f t="shared" si="12"/>
         <v>100</v>
       </c>
-      <c r="J35" s="187">
-        <f t="shared" si="13"/>
-        <v>3737475.5599999996</v>
-      </c>
-      <c r="K35" s="187">
-        <f>SUM(K11:K34)</f>
-        <v>3757527.26</v>
-      </c>
-      <c r="L35" s="187"/>
-      <c r="M35" s="187">
-        <f t="shared" si="13"/>
-        <v>-20051.700000000026</v>
-      </c>
-      <c r="N35" s="187">
-        <f t="shared" si="13"/>
-        <v>322.23619999999994</v>
-      </c>
-      <c r="O35" s="188"/>
-      <c r="P35" s="188">
-        <f>SUM(P11:P34)</f>
+      <c r="J34" s="182">
+        <f t="shared" si="12"/>
+        <v>4513859.5599999996</v>
+      </c>
+      <c r="K34" s="182">
+        <f>SUM(K10:K33)</f>
+        <v>3916821.1900000004</v>
+      </c>
+      <c r="L34" s="182"/>
+      <c r="M34" s="182">
+        <f t="shared" si="12"/>
+        <v>597038.37000000011</v>
+      </c>
+      <c r="N34" s="182">
+        <f t="shared" si="12"/>
+        <v>9844.4892</v>
+      </c>
+      <c r="O34" s="183"/>
+      <c r="P34" s="183">
+        <f>SUM(P10:P33)</f>
         <v>2678810.35</v>
       </c>
-      <c r="Q35" s="189">
-        <f>SUM(Q11:Q34)</f>
-        <v>0</v>
-      </c>
-      <c r="R35" s="191">
-        <f>SUM(R11:R34)</f>
+      <c r="Q34" s="184">
+        <f>SUM(Q10:Q33)</f>
+        <v>0</v>
+      </c>
+      <c r="R34" s="186">
+        <f>SUM(R10:R33)</f>
         <v>1839418.7499999995</v>
       </c>
-      <c r="S35" s="187">
-        <f>SUM(S11:S32)</f>
-        <v>4498505.5599999996</v>
-      </c>
-      <c r="T35" s="187">
-        <f>SUM(T11:T32)</f>
-        <v>4633460.5599999996</v>
-      </c>
-    </row>
-    <row r="36" spans="1:21" ht="22.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="E36" s="38"/>
-      <c r="F36" s="38"/>
-      <c r="G36" s="38"/>
+      <c r="S34" s="182">
+        <f>SUM(S10:S31)</f>
+        <v>5125118.5599999996</v>
+      </c>
+      <c r="T34" s="182">
+        <f>SUM(T10:T31)</f>
+        <v>5278872.5599999996</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E35" s="38"/>
+      <c r="F35" s="38"/>
+      <c r="G35" s="38"/>
+      <c r="K35" s="103" t="s">
+        <v>127</v>
+      </c>
+      <c r="L35" s="103">
+        <f>SUMIF(L10:L33,"B",K10:K33)</f>
+        <v>3698520.92</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A36" s="239"/>
+      <c r="B36" s="239"/>
+      <c r="C36" s="129"/>
+      <c r="D36" s="129"/>
+      <c r="H36" s="240"/>
+      <c r="I36" s="130"/>
+      <c r="J36" s="241"/>
       <c r="K36" s="103" t="s">
-        <v>135</v>
+        <v>117</v>
       </c>
       <c r="L36" s="103">
-        <f>SUMIF(L11:L34,"B",K11:K34)</f>
-        <v>3548957.26</v>
-      </c>
-    </row>
-    <row r="37" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A37" s="232"/>
-      <c r="B37" s="232"/>
+        <f>SUMIF(L10:L33,"E",K10:K33)</f>
+        <v>218300.27</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="A37" s="239"/>
+      <c r="B37" s="239"/>
       <c r="C37" s="129"/>
       <c r="D37" s="129"/>
-      <c r="H37" s="233"/>
+      <c r="H37" s="240"/>
       <c r="I37" s="130"/>
-      <c r="J37" s="234"/>
-      <c r="K37" s="103" t="s">
-        <v>120</v>
-      </c>
-      <c r="L37" s="103">
-        <f>SUMIF(L11:L34,"E",K11:K34)</f>
-        <v>208570</v>
-      </c>
-    </row>
-    <row r="38" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A38" s="232"/>
-      <c r="B38" s="232"/>
-      <c r="C38" s="129"/>
-      <c r="D38" s="129"/>
-      <c r="H38" s="233"/>
-      <c r="I38" s="130"/>
-      <c r="J38" s="234"/>
-      <c r="K38" s="104"/>
-      <c r="L38" s="104"/>
-    </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="J49">
-        <f>SUM(H47:H48)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="J37" s="241"/>
+      <c r="K37" s="104"/>
+      <c r="L37" s="104"/>
+    </row>
+    <row r="48" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="J48">
+        <f>SUM(H46:H47)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A52" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="J53">
-        <f>SUM(H51:H52)</f>
+    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J52">
+        <f>SUM(H50:H51)</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="R9:R10"/>
-    <mergeCell ref="L9:L10"/>
-    <mergeCell ref="A37:B38"/>
-    <mergeCell ref="H37:H38"/>
-    <mergeCell ref="J37:J38"/>
+    <mergeCell ref="R8:R9"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="A36:B37"/>
+    <mergeCell ref="H36:H37"/>
+    <mergeCell ref="J36:J37"/>
     <mergeCell ref="K2:M2"/>
-    <mergeCell ref="A35:E35"/>
-    <mergeCell ref="O9:O10"/>
-    <mergeCell ref="G9:G10"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="D28:D29"/>
-    <mergeCell ref="D30:D31"/>
-    <mergeCell ref="D32:D34"/>
-    <mergeCell ref="E32:E34"/>
-    <mergeCell ref="E30:E31"/>
-    <mergeCell ref="E28:E29"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="D31:D33"/>
+    <mergeCell ref="E31:E33"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="E27:E28"/>
     <mergeCell ref="F2:G2"/>
     <mergeCell ref="H1:S1"/>
-    <mergeCell ref="N9:N10"/>
-    <mergeCell ref="J9:J10"/>
-    <mergeCell ref="K9:K10"/>
-    <mergeCell ref="M9:M10"/>
-    <mergeCell ref="P9:P10"/>
-    <mergeCell ref="Q9:Q10"/>
-    <mergeCell ref="A4:T8"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="E9:E10"/>
-    <mergeCell ref="H9:H10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="T9:T10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="D9:D10"/>
+    <mergeCell ref="N8:N9"/>
+    <mergeCell ref="J8:J9"/>
+    <mergeCell ref="K8:K9"/>
+    <mergeCell ref="M8:M9"/>
+    <mergeCell ref="P8:P9"/>
+    <mergeCell ref="Q8:Q9"/>
+    <mergeCell ref="A4:T7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="H8:H9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="T8:T9"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="D8:D9"/>
     <mergeCell ref="Q2:S2"/>
   </mergeCells>
   <phoneticPr fontId="21" type="noConversion"/>
@@ -5323,9 +5286,15 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D7123E2-E76E-40B2-9631-974509386176}">
-  <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <sheetData/>
+  <dimension ref="C3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="3" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C3" t="s">
+        <v>162</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/2026/BRIN 2970/Agosto/Agosto-BRIN2970.xlsx
+++ b/2026/BRIN 2970/Agosto/Agosto-BRIN2970.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\BRIN 2970\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A5D96D9F-0880-4A4B-BC09-0D7DCEE0A61C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FB03BC1-DC23-44BE-8CE1-FC4AFBDBC610}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="850" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -536,7 +536,7 @@
     <numFmt numFmtId="167" formatCode="_-[$$-2C0A]\ * #,##0.00_-;\-[$$-2C0A]\ * #,##0.00_-;_-[$$-2C0A]\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="168" formatCode="0.000"/>
   </numFmts>
-  <fonts count="25" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -719,13 +719,6 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
   <fills count="12">
     <fill>
@@ -1245,7 +1238,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="242">
+  <cellXfs count="236">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1254,7 +1247,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="12" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="10" fontId="2" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1546,20 +1538,42 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="8" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="8" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="24" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="24" fillId="2" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="24" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1572,57 +1586,72 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1653,50 +1682,8 @@
     <xf numFmtId="0" fontId="15" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2112,143 +2099,148 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="14"/>
-      <c r="B1" s="207" t="s">
+      <c r="A1" s="13"/>
+      <c r="B1" s="192" t="s">
         <v>138</v>
       </c>
-      <c r="C1" s="207"/>
-      <c r="D1" s="207"/>
-      <c r="E1" s="47"/>
+      <c r="C1" s="192"/>
+      <c r="D1" s="192"/>
+      <c r="E1" s="46"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="15"/>
-      <c r="B2" s="48" t="s">
+      <c r="A2" s="14"/>
+      <c r="B2" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="C2" s="48"/>
-      <c r="D2" s="48"/>
-      <c r="E2" s="49"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="48"/>
     </row>
     <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="15"/>
-      <c r="B3" s="208" t="s">
+      <c r="A3" s="14"/>
+      <c r="B3" s="195" t="s">
         <v>139</v>
       </c>
-      <c r="C3" s="208"/>
-      <c r="D3" s="208"/>
-      <c r="E3" s="209"/>
+      <c r="C3" s="195"/>
+      <c r="D3" s="195"/>
+      <c r="E3" s="196"/>
     </row>
     <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="18" t="s">
-        <v>0</v>
-      </c>
-      <c r="B4" s="50" t="s">
+      <c r="A4" s="17" t="s">
+        <v>0</v>
+      </c>
+      <c r="B4" s="49" t="s">
         <v>29</v>
       </c>
-      <c r="C4" s="19"/>
-      <c r="D4" s="19"/>
-      <c r="E4" s="20"/>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="19"/>
     </row>
     <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="B5" s="19" t="s">
+      <c r="B5" s="18" t="s">
         <v>141</v>
       </c>
-      <c r="C5" s="16"/>
-      <c r="D5" s="48" t="s">
+      <c r="C5" s="15"/>
+      <c r="D5" s="47" t="s">
         <v>21</v>
       </c>
-      <c r="E5" s="17"/>
+      <c r="E5" s="16"/>
     </row>
     <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="18" t="s">
+      <c r="A6" s="17" t="s">
         <v>60</v>
       </c>
-      <c r="B6" s="19"/>
-      <c r="C6" s="19"/>
-      <c r="D6" s="19" t="s">
+      <c r="B6" s="18"/>
+      <c r="C6" s="18"/>
+      <c r="D6" s="18" t="s">
         <v>41</v>
       </c>
-      <c r="E6" s="20"/>
+      <c r="E6" s="19"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="211" t="s">
+      <c r="B8" s="198" t="s">
         <v>140</v>
       </c>
-      <c r="C8" s="211"/>
+      <c r="C8" s="198"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="211"/>
-      <c r="C9" s="211"/>
+      <c r="B9" s="198"/>
+      <c r="C9" s="198"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="211"/>
-      <c r="C10" s="211"/>
+      <c r="B10" s="198"/>
+      <c r="C10" s="198"/>
     </row>
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="210" t="s">
+      <c r="A13" s="197" t="s">
         <v>46</v>
       </c>
-      <c r="B13" s="210"/>
-      <c r="C13" s="210"/>
-      <c r="D13" s="210"/>
-      <c r="E13" s="210"/>
+      <c r="B13" s="197"/>
+      <c r="C13" s="197"/>
+      <c r="D13" s="197"/>
+      <c r="E13" s="197"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="210"/>
-      <c r="B14" s="210"/>
-      <c r="C14" s="210"/>
-      <c r="D14" s="210"/>
-      <c r="E14" s="210"/>
+      <c r="A14" s="197"/>
+      <c r="B14" s="197"/>
+      <c r="C14" s="197"/>
+      <c r="D14" s="197"/>
+      <c r="E14" s="197"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="210"/>
-      <c r="B15" s="210"/>
-      <c r="C15" s="210"/>
-      <c r="D15" s="210"/>
-      <c r="E15" s="210"/>
+      <c r="A15" s="197"/>
+      <c r="B15" s="197"/>
+      <c r="C15" s="197"/>
+      <c r="D15" s="197"/>
+      <c r="E15" s="197"/>
     </row>
     <row r="16" spans="1:5" ht="127.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="210"/>
-      <c r="B16" s="210"/>
-      <c r="C16" s="210"/>
-      <c r="D16" s="210"/>
-      <c r="E16" s="210"/>
-    </row>
-    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
+      <c r="A16" s="197"/>
+      <c r="B16" s="197"/>
+      <c r="C16" s="197"/>
+      <c r="D16" s="197"/>
+      <c r="E16" s="197"/>
+    </row>
+    <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D17" s="62"/>
+    </row>
     <row r="18" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
-    </row>
-    <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
+      <c r="D18" s="62"/>
+    </row>
+    <row r="19" spans="1:7" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D19" s="62"/>
+    </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="10" t="s">
+      <c r="A20" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="B20" s="11"/>
-      <c r="C20" s="12"/>
-      <c r="D20" s="8"/>
-      <c r="E20" s="13"/>
+      <c r="B20" s="10"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="66"/>
+      <c r="E20" s="12"/>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="26" t="s">
+      <c r="A21" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="B21" s="26"/>
-      <c r="C21" s="26"/>
-      <c r="D21" s="25"/>
-      <c r="E21" s="25"/>
+      <c r="B21" s="25"/>
+      <c r="C21" s="25"/>
+      <c r="D21" s="24"/>
+      <c r="E21" s="24"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="53" t="s">
+      <c r="A22" s="52" t="s">
         <v>62</v>
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
-      <c r="D22" s="108">
-        <v>920874.33</v>
+      <c r="D22" s="107">
+        <v>1025699.49</v>
       </c>
       <c r="E22" s="5"/>
     </row>
@@ -2258,8 +2250,8 @@
       </c>
       <c r="B23" s="5"/>
       <c r="C23" s="5"/>
-      <c r="D23" s="108">
-        <v>-227916.33</v>
+      <c r="D23" s="107">
+        <v>-253860.49</v>
       </c>
       <c r="E23" s="5"/>
     </row>
@@ -2269,23 +2261,23 @@
       </c>
       <c r="B24" s="5"/>
       <c r="C24" s="5"/>
-      <c r="D24" s="108">
+      <c r="D24" s="107">
         <v>0</v>
       </c>
       <c r="E24" s="5"/>
     </row>
     <row r="25" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="43" t="s">
+      <c r="A25" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="B25" s="43"/>
-      <c r="C25" s="43"/>
-      <c r="D25" s="109">
+      <c r="B25" s="42"/>
+      <c r="C25" s="42"/>
+      <c r="D25" s="108">
         <f>SUM(D22:D24)</f>
-        <v>692958</v>
-      </c>
-      <c r="E25" s="80"/>
-      <c r="G25" s="21"/>
+        <v>771839</v>
+      </c>
+      <c r="E25" s="79"/>
+      <c r="G25" s="20"/>
     </row>
     <row r="26" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
@@ -2293,155 +2285,155 @@
       </c>
       <c r="B26" s="5"/>
       <c r="C26" s="5"/>
-      <c r="D26" s="108"/>
+      <c r="D26" s="107"/>
       <c r="E26" s="5"/>
     </row>
     <row r="27" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="22"/>
+      <c r="A27" s="21"/>
       <c r="B27" s="5"/>
       <c r="C27" s="5"/>
-      <c r="D27" s="108"/>
+      <c r="D27" s="107"/>
       <c r="E27" s="5"/>
     </row>
     <row r="28" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="5"/>
       <c r="B28" s="5"/>
       <c r="C28" s="5"/>
-      <c r="D28" s="108"/>
+      <c r="D28" s="107"/>
       <c r="E28" s="5"/>
     </row>
     <row r="29" spans="1:7" ht="0.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="5"/>
       <c r="B29" s="5"/>
       <c r="C29" s="5"/>
-      <c r="D29" s="125"/>
+      <c r="D29" s="124"/>
       <c r="E29" s="5"/>
     </row>
     <row r="30" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="43" t="s">
+      <c r="A30" s="42" t="s">
         <v>26</v>
       </c>
-      <c r="B30" s="43"/>
-      <c r="C30" s="43"/>
-      <c r="D30" s="110">
+      <c r="B30" s="42"/>
+      <c r="C30" s="42"/>
+      <c r="D30" s="109">
         <f>SUM(D26:D29)</f>
         <v>0</v>
       </c>
-      <c r="E30" s="80"/>
+      <c r="E30" s="79"/>
     </row>
     <row r="31" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="23" t="s">
+      <c r="A31" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="B31" s="23"/>
-      <c r="C31" s="23"/>
-      <c r="D31" s="111"/>
-      <c r="E31" s="81">
+      <c r="B31" s="22"/>
+      <c r="C31" s="22"/>
+      <c r="D31" s="110"/>
+      <c r="E31" s="80">
         <f>D25+D30</f>
-        <v>692958</v>
-      </c>
-      <c r="F31" s="21"/>
+        <v>771839</v>
+      </c>
+      <c r="F31" s="20"/>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="26" t="s">
+      <c r="A32" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="B32" s="26"/>
-      <c r="C32" s="26"/>
-      <c r="D32" s="112"/>
-      <c r="E32" s="82"/>
+      <c r="B32" s="25"/>
+      <c r="C32" s="25"/>
+      <c r="D32" s="111"/>
+      <c r="E32" s="81"/>
     </row>
     <row r="33" spans="1:7" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="200" t="s">
+      <c r="A33" s="193" t="s">
         <v>161</v>
       </c>
-      <c r="B33" s="201"/>
-      <c r="C33" s="40"/>
-      <c r="D33" s="189">
+      <c r="B33" s="194"/>
+      <c r="C33" s="39"/>
+      <c r="D33" s="107">
         <v>100000</v>
       </c>
-      <c r="E33" s="83" t="s">
+      <c r="E33" s="82" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="200" t="s">
+      <c r="A34" s="193" t="s">
         <v>63</v>
       </c>
-      <c r="B34" s="201"/>
-      <c r="C34" s="40"/>
-      <c r="D34" s="126">
-        <v>0</v>
-      </c>
-      <c r="E34" s="83"/>
+      <c r="B34" s="194"/>
+      <c r="C34" s="39"/>
+      <c r="D34" s="125">
+        <v>0</v>
+      </c>
+      <c r="E34" s="82"/>
     </row>
     <row r="35" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="23" t="s">
+      <c r="A35" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="B35" s="23"/>
-      <c r="C35" s="23"/>
-      <c r="D35" s="119"/>
-      <c r="E35" s="84">
+      <c r="B35" s="22"/>
+      <c r="C35" s="22"/>
+      <c r="D35" s="118"/>
+      <c r="E35" s="83">
         <f>SUM(D33:D34)</f>
         <v>100000</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="26" t="s">
+      <c r="A36" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="B36" s="23"/>
-      <c r="C36" s="23"/>
-      <c r="D36" s="120"/>
-      <c r="E36" s="85"/>
-    </row>
-    <row r="37" spans="1:7" s="29" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="206" t="s">
+      <c r="B36" s="22"/>
+      <c r="C36" s="22"/>
+      <c r="D36" s="119"/>
+      <c r="E36" s="84"/>
+    </row>
+    <row r="37" spans="1:7" s="28" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A37" s="191" t="s">
         <v>64</v>
       </c>
-      <c r="B37" s="206"/>
-      <c r="C37" s="41"/>
-      <c r="D37" s="191">
+      <c r="B37" s="191"/>
+      <c r="C37" s="40"/>
+      <c r="D37" s="235">
         <v>44249</v>
       </c>
-      <c r="E37" s="141" t="s">
+      <c r="E37" s="140" t="s">
         <v>147</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="142" t="s">
+      <c r="A38" s="141" t="s">
         <v>65</v>
       </c>
-      <c r="B38" s="143"/>
-      <c r="C38" s="41"/>
-      <c r="D38" s="191">
+      <c r="B38" s="142"/>
+      <c r="C38" s="40"/>
+      <c r="D38" s="235">
         <v>4406</v>
       </c>
-      <c r="E38" s="147" t="s">
+      <c r="E38" s="146" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="144" t="s">
+      <c r="A39" s="143" t="s">
         <v>2</v>
       </c>
-      <c r="B39" s="144"/>
-      <c r="C39" s="23"/>
-      <c r="D39" s="119"/>
-      <c r="E39" s="54">
+      <c r="B39" s="143"/>
+      <c r="C39" s="22"/>
+      <c r="D39" s="118"/>
+      <c r="E39" s="53">
         <f>SUM(D37:D38)</f>
         <v>48655</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="26" t="s">
+      <c r="A40" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="B40" s="86"/>
-      <c r="C40" s="86"/>
-      <c r="D40" s="121"/>
-      <c r="E40" s="114"/>
+      <c r="B40" s="85"/>
+      <c r="C40" s="85"/>
+      <c r="D40" s="120"/>
+      <c r="E40" s="113"/>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
@@ -2450,14 +2442,14 @@
       <c r="B41" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="C41" s="40"/>
-      <c r="D41" s="188">
+      <c r="C41" s="39"/>
+      <c r="D41" s="112">
         <v>839936.9</v>
       </c>
-      <c r="E41" s="89" t="s">
+      <c r="E41" s="88" t="s">
         <v>152</v>
       </c>
-      <c r="G41" s="71"/>
+      <c r="G41" s="70"/>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
@@ -2466,14 +2458,14 @@
       <c r="B42" s="5" t="s">
         <v>156</v>
       </c>
-      <c r="C42" s="40"/>
-      <c r="D42" s="188">
+      <c r="C42" s="39"/>
+      <c r="D42" s="112">
         <v>518193.32</v>
       </c>
-      <c r="E42" s="89" t="s">
+      <c r="E42" s="88" t="s">
         <v>152</v>
       </c>
-      <c r="G42" s="71"/>
+      <c r="G42" s="70"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
@@ -2483,10 +2475,10 @@
         <v>53</v>
       </c>
       <c r="C43" s="5"/>
-      <c r="D43" s="188">
+      <c r="D43" s="112">
         <v>84552.82</v>
       </c>
-      <c r="E43" s="89" t="s">
+      <c r="E43" s="88" t="s">
         <v>155</v>
       </c>
     </row>
@@ -2499,10 +2491,10 @@
         <v>52</v>
       </c>
       <c r="C44" s="5"/>
-      <c r="D44" s="188">
+      <c r="D44" s="112">
         <v>41439.33</v>
       </c>
-      <c r="E44" s="90" t="str">
+      <c r="E44" s="89" t="str">
         <f>E43</f>
         <v>Debito 12/08</v>
       </c>
@@ -2516,174 +2508,174 @@
         <v>51</v>
       </c>
       <c r="C45" s="5"/>
-      <c r="D45" s="188">
+      <c r="D45" s="112">
         <v>4604.37</v>
       </c>
-      <c r="E45" s="91" t="str">
+      <c r="E45" s="90" t="str">
         <f>E44</f>
         <v>Debito 12/08</v>
       </c>
     </row>
     <row r="46" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="23" t="s">
+      <c r="A46" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="B46" s="86"/>
-      <c r="C46" s="86"/>
-      <c r="D46" s="122"/>
-      <c r="E46" s="54">
+      <c r="B46" s="85"/>
+      <c r="C46" s="85"/>
+      <c r="D46" s="121"/>
+      <c r="E46" s="53">
         <f>SUM(D41:D45)</f>
         <v>1488726.7400000002</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="26" t="s">
+      <c r="A47" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="B47" s="86"/>
-      <c r="C47" s="86"/>
-      <c r="D47" s="121"/>
-      <c r="E47" s="114"/>
+      <c r="B47" s="85"/>
+      <c r="C47" s="85"/>
+      <c r="D47" s="120"/>
+      <c r="E47" s="113"/>
     </row>
     <row r="48" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="53" t="s">
+      <c r="A48" s="52" t="s">
         <v>68</v>
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
-      <c r="D48" s="188">
+      <c r="D48" s="112">
         <v>334964.3</v>
       </c>
-      <c r="E48" s="89" t="s">
+      <c r="E48" s="88" t="s">
         <v>144</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="145" t="s">
+      <c r="A49" s="144" t="s">
         <v>70</v>
       </c>
-      <c r="B49" s="102"/>
+      <c r="B49" s="101"/>
       <c r="C49" s="5"/>
-      <c r="D49" s="188">
-        <v>0</v>
-      </c>
-      <c r="E49" s="89"/>
+      <c r="D49" s="112">
+        <v>0</v>
+      </c>
+      <c r="E49" s="88"/>
     </row>
     <row r="50" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="145" t="s">
+      <c r="A50" s="144" t="s">
         <v>67</v>
       </c>
-      <c r="B50" s="102"/>
+      <c r="B50" s="101"/>
       <c r="C50" s="5"/>
-      <c r="D50" s="188">
+      <c r="D50" s="112">
         <v>783602.88</v>
       </c>
-      <c r="E50" s="105" t="s">
+      <c r="E50" s="104" t="s">
         <v>146</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="23" t="s">
+      <c r="A51" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="B51" s="23"/>
-      <c r="C51" s="23"/>
-      <c r="D51" s="123"/>
-      <c r="E51" s="54">
+      <c r="B51" s="22"/>
+      <c r="C51" s="22"/>
+      <c r="D51" s="122"/>
+      <c r="E51" s="53">
         <f>SUM(D48:D50)</f>
         <v>1118567.18</v>
       </c>
     </row>
     <row r="52" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="26"/>
-      <c r="B52" s="23"/>
-      <c r="C52" s="23"/>
-      <c r="D52" s="119"/>
-      <c r="E52" s="115"/>
+      <c r="A52" s="25"/>
+      <c r="B52" s="22"/>
+      <c r="C52" s="22"/>
+      <c r="D52" s="118"/>
+      <c r="E52" s="114"/>
     </row>
     <row r="53" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="140" t="s">
+      <c r="A53" s="139" t="s">
         <v>66</v>
       </c>
-      <c r="B53" s="146"/>
+      <c r="B53" s="145"/>
       <c r="C53" s="5"/>
-      <c r="D53" s="113">
-        <v>0</v>
-      </c>
-      <c r="E53" s="89"/>
+      <c r="D53" s="112">
+        <v>0</v>
+      </c>
+      <c r="E53" s="88"/>
     </row>
     <row r="54" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="140" t="s">
+      <c r="A54" s="139" t="s">
         <v>69</v>
       </c>
-      <c r="B54" s="190"/>
+      <c r="B54" s="187"/>
       <c r="C54" s="5"/>
-      <c r="D54" s="188">
+      <c r="D54" s="112">
         <v>48746</v>
       </c>
-      <c r="E54" s="105" t="s">
+      <c r="E54" s="104" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="204" t="s">
+      <c r="A55" s="189" t="s">
         <v>149</v>
       </c>
-      <c r="B55" s="205"/>
+      <c r="B55" s="190"/>
       <c r="C55" s="5"/>
-      <c r="D55" s="188">
+      <c r="D55" s="112">
         <v>330000</v>
       </c>
-      <c r="E55" s="105" t="s">
+      <c r="E55" s="104" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="56" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="140" t="s">
+      <c r="A56" s="139" t="s">
         <v>151</v>
       </c>
-      <c r="B56" s="146"/>
+      <c r="B56" s="145"/>
       <c r="C56" s="5"/>
-      <c r="D56" s="188">
+      <c r="D56" s="112">
         <v>81000</v>
       </c>
-      <c r="E56" s="105" t="s">
+      <c r="E56" s="104" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="57" spans="1:5" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="204" t="s">
+      <c r="A57" s="189" t="s">
         <v>150</v>
       </c>
-      <c r="B57" s="205"/>
+      <c r="B57" s="190"/>
       <c r="C57" s="5"/>
-      <c r="D57" s="188">
+      <c r="D57" s="112">
         <v>95700</v>
       </c>
-      <c r="E57" s="105" t="s">
+      <c r="E57" s="104" t="s">
         <v>143</v>
       </c>
     </row>
     <row r="58" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="23" t="s">
+      <c r="A58" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="B58" s="26"/>
-      <c r="C58" s="26"/>
-      <c r="D58" s="25"/>
-      <c r="E58" s="116">
+      <c r="B58" s="25"/>
+      <c r="C58" s="25"/>
+      <c r="D58" s="24"/>
+      <c r="E58" s="115">
         <f>SUM(D53:D57)</f>
         <v>555446</v>
       </c>
     </row>
     <row r="59" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="26" t="s">
+      <c r="A59" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="B59" s="45"/>
-      <c r="C59" s="23"/>
-      <c r="D59" s="111"/>
-      <c r="E59" s="87"/>
+      <c r="B59" s="44"/>
+      <c r="C59" s="22"/>
+      <c r="D59" s="110"/>
+      <c r="E59" s="86"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="5" t="s">
@@ -2691,10 +2683,10 @@
       </c>
       <c r="B60" s="5"/>
       <c r="C60" s="5"/>
-      <c r="D60" s="113">
-        <v>0</v>
-      </c>
-      <c r="E60" s="88"/>
+      <c r="D60" s="112">
+        <v>0</v>
+      </c>
+      <c r="E60" s="87"/>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
@@ -2702,20 +2694,20 @@
       </c>
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
-      <c r="D61" s="188">
+      <c r="D61" s="112">
         <f>6403.5+74344.13</f>
         <v>80747.63</v>
       </c>
-      <c r="E61" s="30"/>
+      <c r="E61" s="29"/>
     </row>
     <row r="62" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="39" t="s">
+      <c r="A62" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="B62" s="39"/>
-      <c r="C62" s="39"/>
-      <c r="D62" s="59"/>
-      <c r="E62" s="54">
+      <c r="B62" s="38"/>
+      <c r="C62" s="38"/>
+      <c r="D62" s="58"/>
+      <c r="E62" s="53">
         <f>SUM(D60:D61)</f>
         <v>80747.63</v>
       </c>
@@ -2724,475 +2716,482 @@
       <c r="A63" s="5"/>
       <c r="B63" s="5"/>
       <c r="C63" s="5"/>
-      <c r="D63" s="53"/>
-      <c r="E63" s="60"/>
+      <c r="D63" s="52"/>
+      <c r="E63" s="59"/>
     </row>
     <row r="64" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="24" t="s">
+      <c r="A64" s="23" t="s">
         <v>58</v>
       </c>
-      <c r="B64" s="24"/>
-      <c r="C64" s="24"/>
-      <c r="D64" s="61"/>
-      <c r="E64" s="62">
+      <c r="B64" s="23"/>
+      <c r="C64" s="23"/>
+      <c r="D64" s="60"/>
+      <c r="E64" s="61">
         <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="1"/>
-      <c r="D65" s="63"/>
-      <c r="E65" s="64"/>
-      <c r="F65" s="32"/>
+      <c r="D65" s="62"/>
+      <c r="E65" s="63"/>
+      <c r="F65" s="31"/>
     </row>
     <row r="66" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B66" s="9"/>
+      <c r="B66" s="8"/>
       <c r="C66" s="4"/>
-      <c r="D66" s="65"/>
-      <c r="E66" s="66">
+      <c r="D66" s="64"/>
+      <c r="E66" s="65">
         <f>(SUM(E28:E64))</f>
-        <v>4085100.55</v>
-      </c>
-      <c r="F66" s="79"/>
-      <c r="G66" s="32"/>
-      <c r="H66" s="71"/>
-      <c r="I66" s="71"/>
-      <c r="J66" s="71"/>
-      <c r="K66" s="71"/>
-      <c r="L66" s="71"/>
+        <v>4163981.55</v>
+      </c>
+      <c r="F66" s="78"/>
+      <c r="G66" s="31"/>
+      <c r="H66" s="70"/>
+      <c r="I66" s="70"/>
+      <c r="J66" s="70"/>
+      <c r="K66" s="70"/>
+      <c r="L66" s="70"/>
     </row>
     <row r="67" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D67" s="63"/>
-      <c r="E67" s="63"/>
-      <c r="H67" s="71"/>
-      <c r="I67" s="71"/>
-      <c r="J67" s="71"/>
-      <c r="K67" s="71"/>
-      <c r="L67" s="71"/>
+      <c r="D67" s="62"/>
+      <c r="E67" s="62"/>
+      <c r="H67" s="70"/>
+      <c r="I67" s="70"/>
+      <c r="J67" s="70"/>
+      <c r="K67" s="70"/>
+      <c r="L67" s="70"/>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A68" s="10" t="s">
+      <c r="A68" s="9" t="s">
         <v>133</v>
       </c>
-      <c r="B68" s="11"/>
-      <c r="C68" s="12"/>
-      <c r="D68" s="67"/>
-      <c r="E68" s="68"/>
-      <c r="H68" s="71"/>
-      <c r="I68" s="71"/>
-      <c r="J68" s="71"/>
-      <c r="K68" s="71"/>
-      <c r="L68" s="71"/>
+      <c r="B68" s="10"/>
+      <c r="C68" s="11"/>
+      <c r="D68" s="66"/>
+      <c r="E68" s="67"/>
+      <c r="H68" s="70"/>
+      <c r="I68" s="70"/>
+      <c r="J68" s="70"/>
+      <c r="K68" s="70"/>
+      <c r="L68" s="70"/>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A69" s="202"/>
-      <c r="B69" s="203"/>
+      <c r="A69" s="203"/>
+      <c r="B69" s="204"/>
       <c r="C69" s="5"/>
-      <c r="D69" s="113"/>
-      <c r="E69" s="105"/>
-      <c r="H69" s="71"/>
-      <c r="I69" s="71"/>
-      <c r="J69" s="71"/>
-      <c r="K69" s="71"/>
-      <c r="L69" s="71"/>
+      <c r="D69" s="112"/>
+      <c r="E69" s="104"/>
+      <c r="H69" s="70"/>
+      <c r="I69" s="70"/>
+      <c r="J69" s="70"/>
+      <c r="K69" s="70"/>
+      <c r="L69" s="70"/>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A70" s="202"/>
-      <c r="B70" s="203"/>
+      <c r="A70" s="203"/>
+      <c r="B70" s="204"/>
       <c r="C70" s="5"/>
-      <c r="D70" s="113"/>
-      <c r="E70" s="55"/>
-      <c r="H70" s="71"/>
-      <c r="I70" s="71"/>
-      <c r="J70" s="71"/>
-      <c r="K70" s="71"/>
-      <c r="L70" s="71"/>
+      <c r="D70" s="112"/>
+      <c r="E70" s="54"/>
+      <c r="H70" s="70"/>
+      <c r="I70" s="70"/>
+      <c r="J70" s="70"/>
+      <c r="K70" s="70"/>
+      <c r="L70" s="70"/>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A71" s="56"/>
-      <c r="B71" s="58"/>
+      <c r="A71" s="55"/>
+      <c r="B71" s="57"/>
       <c r="C71" s="5"/>
-      <c r="D71" s="57"/>
-      <c r="E71" s="55"/>
-      <c r="H71" s="71"/>
-      <c r="I71" s="71"/>
-      <c r="J71" s="71"/>
-      <c r="K71" s="71"/>
-      <c r="L71" s="71"/>
+      <c r="D71" s="56"/>
+      <c r="E71" s="54"/>
+      <c r="H71" s="70"/>
+      <c r="I71" s="70"/>
+      <c r="J71" s="70"/>
+      <c r="K71" s="70"/>
+      <c r="L71" s="70"/>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A72" s="37"/>
-      <c r="B72" s="36"/>
-      <c r="C72" s="36"/>
-      <c r="D72" s="127"/>
-      <c r="E72" s="170">
+      <c r="A72" s="36"/>
+      <c r="B72" s="35"/>
+      <c r="C72" s="35"/>
+      <c r="D72" s="126"/>
+      <c r="E72" s="169">
         <f>SUM(D69:D71)</f>
         <v>0</v>
       </c>
-      <c r="H72" s="71"/>
-      <c r="I72" s="71"/>
-      <c r="J72" s="71"/>
-      <c r="K72" s="71"/>
-      <c r="L72" s="71"/>
+      <c r="H72" s="70"/>
+      <c r="I72" s="70"/>
+      <c r="J72" s="70"/>
+      <c r="K72" s="70"/>
+      <c r="L72" s="70"/>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="D73" s="63"/>
-      <c r="E73" s="63"/>
-      <c r="H73" s="71"/>
-      <c r="I73" s="71"/>
-      <c r="J73" s="71"/>
-      <c r="K73" s="71"/>
-      <c r="L73" s="71"/>
+      <c r="D73" s="62"/>
+      <c r="E73" s="62"/>
+      <c r="H73" s="70"/>
+      <c r="I73" s="70"/>
+      <c r="J73" s="70"/>
+      <c r="K73" s="70"/>
+      <c r="L73" s="70"/>
     </row>
     <row r="74" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D74" s="63"/>
-      <c r="E74" s="63"/>
-      <c r="H74" s="92"/>
+      <c r="D74" s="62"/>
+      <c r="E74" s="62"/>
+      <c r="H74" s="91"/>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A75" s="10" t="s">
+      <c r="A75" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="B75" s="11"/>
-      <c r="C75" s="12"/>
-      <c r="D75" s="67"/>
-      <c r="E75" s="68"/>
+      <c r="B75" s="10"/>
+      <c r="C75" s="11"/>
+      <c r="D75" s="66"/>
+      <c r="E75" s="67"/>
     </row>
     <row r="76" spans="1:12" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="198" t="s">
+      <c r="A76" s="201" t="s">
         <v>153</v>
       </c>
-      <c r="B76" s="199"/>
+      <c r="B76" s="202"/>
       <c r="C76" s="5"/>
-      <c r="D76" s="188">
+      <c r="D76" s="112">
         <v>3320350</v>
       </c>
-      <c r="E76" s="105" t="s">
+      <c r="E76" s="104" t="s">
         <v>152</v>
       </c>
     </row>
     <row r="77" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="200"/>
-      <c r="B77" s="201"/>
+      <c r="A77" s="193"/>
+      <c r="B77" s="194"/>
       <c r="C77" s="5"/>
-      <c r="D77" s="57"/>
-      <c r="E77" s="55"/>
+      <c r="D77" s="56"/>
+      <c r="E77" s="54"/>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A78" s="56"/>
-      <c r="B78" s="58"/>
+      <c r="A78" s="55"/>
+      <c r="B78" s="57"/>
       <c r="C78" s="5"/>
-      <c r="D78" s="57"/>
-      <c r="E78" s="55"/>
+      <c r="D78" s="56"/>
+      <c r="E78" s="54"/>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A79" s="37"/>
-      <c r="B79" s="36"/>
-      <c r="C79" s="36"/>
-      <c r="D79" s="127"/>
-      <c r="E79" s="170">
+      <c r="A79" s="36"/>
+      <c r="B79" s="35"/>
+      <c r="C79" s="35"/>
+      <c r="D79" s="126"/>
+      <c r="E79" s="169">
         <f>SUM(D76:D78)</f>
         <v>3320350</v>
       </c>
     </row>
     <row r="80" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D80" s="63"/>
+      <c r="D80" s="62"/>
     </row>
     <row r="81" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D81" s="63"/>
+      <c r="D81" s="62"/>
     </row>
     <row r="82" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="106" t="s">
+      <c r="A82" s="105" t="s">
         <v>57</v>
       </c>
-      <c r="B82" s="107"/>
-      <c r="C82" s="107"/>
-      <c r="D82" s="128"/>
-      <c r="E82" s="117">
+      <c r="B82" s="106"/>
+      <c r="C82" s="106"/>
+      <c r="D82" s="127"/>
+      <c r="E82" s="116">
         <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D83" s="63"/>
+      <c r="D83" s="62"/>
     </row>
     <row r="84" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A84" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B84" s="9"/>
+      <c r="B84" s="8"/>
       <c r="C84" s="4"/>
-      <c r="D84" s="65"/>
-      <c r="E84" s="46">
+      <c r="D84" s="64"/>
+      <c r="E84" s="45">
         <f>E79+E82</f>
         <v>3320350</v>
       </c>
     </row>
     <row r="85" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D85" s="63"/>
+      <c r="D85" s="62"/>
     </row>
     <row r="86" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="51" t="s">
+      <c r="A86" s="50" t="s">
         <v>12</v>
       </c>
-      <c r="B86" s="52">
+      <c r="B86" s="51">
         <f>E66</f>
-        <v>4085100.55</v>
-      </c>
-      <c r="D86" s="63"/>
+        <v>4163981.55</v>
+      </c>
+      <c r="D86" s="62"/>
     </row>
     <row r="87" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A87" s="51" t="s">
+      <c r="A87" s="50" t="s">
         <v>13</v>
       </c>
-      <c r="B87" s="52">
+      <c r="B87" s="51">
         <f>E66-E64</f>
-        <v>4085100.55</v>
-      </c>
-      <c r="D87" s="63"/>
+        <v>4163981.55</v>
+      </c>
+      <c r="D87" s="62"/>
     </row>
     <row r="88" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A88" s="51" t="s">
+      <c r="A88" s="50" t="s">
         <v>19</v>
       </c>
-      <c r="B88" s="52">
+      <c r="B88" s="51">
         <f>E84-E82</f>
         <v>3320350</v>
       </c>
-      <c r="D88" s="63"/>
+      <c r="D88" s="62"/>
     </row>
     <row r="89" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A89" s="51" t="s">
+      <c r="A89" s="50" t="s">
         <v>30</v>
       </c>
-      <c r="B89" s="52">
+      <c r="B89" s="51">
         <f>E84</f>
         <v>3320350</v>
       </c>
-      <c r="D89" s="63"/>
+      <c r="D89" s="62"/>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D90" s="63"/>
+      <c r="D90" s="62"/>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D91" s="63"/>
-    </row>
-    <row r="92" spans="1:5" s="29" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="D91" s="62"/>
+    </row>
+    <row r="92" spans="1:5" s="28" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A92"/>
-      <c r="B92" s="31"/>
-      <c r="C92" s="28"/>
+      <c r="B92" s="30"/>
+      <c r="C92" s="27"/>
       <c r="D92"/>
     </row>
-    <row r="93" spans="1:5" s="29" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="72" t="s">
+    <row r="93" spans="1:5" s="28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A93" s="71" t="s">
         <v>132</v>
       </c>
-      <c r="B93" s="73">
+      <c r="B93" s="72">
         <v>7227046.5299999993</v>
       </c>
-      <c r="C93" s="28"/>
-      <c r="D93" s="35"/>
+      <c r="C93" s="27"/>
+      <c r="D93" s="34"/>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A94" s="41" t="s">
+      <c r="A94" s="40" t="s">
         <v>36</v>
       </c>
-      <c r="B94" s="77">
+      <c r="B94" s="76">
         <f>-B87</f>
-        <v>-4085100.55</v>
-      </c>
-      <c r="E94" s="32"/>
+        <v>-4163981.55</v>
+      </c>
+      <c r="E94" s="31"/>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A95" s="41" t="s">
+      <c r="A95" s="40" t="s">
         <v>37</v>
       </c>
-      <c r="B95" s="77">
+      <c r="B95" s="76">
         <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A96" s="41" t="s">
+      <c r="A96" s="40" t="s">
         <v>134</v>
       </c>
-      <c r="B96" s="77">
+      <c r="B96" s="76">
         <f>-E72</f>
         <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A97" s="41" t="s">
+      <c r="A97" s="40" t="s">
         <v>158</v>
       </c>
-      <c r="B97" s="148">
+      <c r="B97" s="147">
         <v>-3000000</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A98" s="41" t="s">
+      <c r="A98" s="40" t="s">
         <v>38</v>
       </c>
-      <c r="B98" s="77">
+      <c r="B98" s="76">
         <f>B116</f>
         <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A99" s="41" t="s">
+      <c r="A99" s="40" t="s">
         <v>128</v>
       </c>
-      <c r="B99" s="78">
+      <c r="B99" s="77">
         <f>PRORRATEO!L35</f>
-        <v>3698520.92</v>
+        <v>3923179.17</v>
       </c>
     </row>
     <row r="100" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="75" t="s">
+      <c r="A100" s="74" t="s">
         <v>34</v>
       </c>
-      <c r="B100" s="76">
+      <c r="B100" s="75">
         <f>SUM(B93:C99)</f>
-        <v>3840466.8999999994</v>
-      </c>
-      <c r="D100" s="31"/>
-      <c r="E100" s="32"/>
+        <v>3986244.1499999994</v>
+      </c>
+      <c r="D100" s="30"/>
+      <c r="E100" s="31"/>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A101" s="74"/>
-      <c r="B101" s="74"/>
+      <c r="A101" s="73"/>
+      <c r="B101" s="73"/>
+      <c r="D101" s="31"/>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A102" s="72" t="s">
+      <c r="A102" s="71" t="s">
         <v>129</v>
       </c>
-      <c r="B102" s="73">
+      <c r="B102" s="72">
         <v>198159.40000000002</v>
       </c>
     </row>
     <row r="103" spans="1:5" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="41" t="s">
+      <c r="A103" s="40" t="s">
         <v>157</v>
       </c>
-      <c r="B103" s="148">
+      <c r="B103" s="147">
         <v>-75000</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A104" s="41" t="s">
+      <c r="A104" s="40" t="s">
         <v>159</v>
       </c>
-      <c r="B104" s="192">
+      <c r="B104" s="188">
         <v>3000000</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A105" s="41" t="s">
+      <c r="A105" s="40" t="s">
         <v>37</v>
       </c>
-      <c r="B105" s="148">
+      <c r="B105" s="147">
         <f>-B88</f>
         <v>-3320350</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A106" s="41" t="s">
+      <c r="A106" s="40" t="s">
         <v>130</v>
       </c>
-      <c r="B106" s="78">
+      <c r="B106" s="77">
         <f>PRORRATEO!L36</f>
         <v>218300.27</v>
       </c>
     </row>
     <row r="107" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="75" t="s">
+      <c r="A107" s="74" t="s">
         <v>34</v>
       </c>
-      <c r="B107" s="76">
+      <c r="B107" s="75">
         <f>SUM(B102:C106)</f>
         <v>21109.669999999896</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A108" s="74"/>
-      <c r="B108" s="74"/>
+      <c r="A108" s="73"/>
+      <c r="B108" s="73"/>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A109" s="74"/>
-      <c r="B109" s="74"/>
+      <c r="A109" s="73"/>
+      <c r="B109" s="73"/>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A110" s="74"/>
-      <c r="B110" s="74"/>
+      <c r="A110" s="73"/>
+      <c r="B110" s="73"/>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A111" s="74"/>
-      <c r="B111" s="74"/>
+      <c r="A111" s="73"/>
+      <c r="B111" s="73"/>
     </row>
     <row r="112" spans="1:5" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="113" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A113" s="197" t="s">
+      <c r="A113" s="200" t="s">
         <v>24</v>
       </c>
-      <c r="B113" s="197"/>
-      <c r="C113" s="197"/>
+      <c r="B113" s="200"/>
+      <c r="C113" s="200"/>
     </row>
     <row r="114" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A114" s="197"/>
-      <c r="B114" s="197"/>
-      <c r="C114" s="197"/>
+      <c r="A114" s="200"/>
+      <c r="B114" s="200"/>
+      <c r="C114" s="200"/>
     </row>
     <row r="115" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="69"/>
-      <c r="B115" s="27"/>
-      <c r="C115" s="27">
+      <c r="A115" s="68"/>
+      <c r="B115" s="26"/>
+      <c r="C115" s="26">
         <v>40000</v>
       </c>
-      <c r="E115" s="79"/>
+      <c r="E115" s="78"/>
     </row>
     <row r="116" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A116" s="33" t="s">
+      <c r="A116" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="B116" s="70">
+      <c r="B116" s="69">
         <f>SUM(B115:B115)</f>
         <v>0</v>
       </c>
-      <c r="C116" s="34"/>
+      <c r="C116" s="33"/>
     </row>
     <row r="117" spans="1:13" x14ac:dyDescent="0.25">
       <c r="M117" s="7"/>
     </row>
     <row r="118" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="196"/>
-      <c r="B118" s="196"/>
-      <c r="C118" s="196"/>
-      <c r="D118" s="196"/>
-      <c r="E118" s="196"/>
+      <c r="A118" s="199"/>
+      <c r="B118" s="199"/>
+      <c r="C118" s="199"/>
+      <c r="D118" s="199"/>
+      <c r="E118" s="199"/>
     </row>
     <row r="119" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A119" s="196"/>
-      <c r="B119" s="196"/>
-      <c r="C119" s="196"/>
-      <c r="D119" s="196"/>
-      <c r="E119" s="196"/>
+      <c r="A119" s="199"/>
+      <c r="B119" s="199"/>
+      <c r="C119" s="199"/>
+      <c r="D119" s="199"/>
+      <c r="E119" s="199"/>
     </row>
     <row r="120" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A120" s="196"/>
-      <c r="B120" s="196"/>
-      <c r="C120" s="196"/>
-      <c r="D120" s="196"/>
-      <c r="E120" s="196"/>
+      <c r="A120" s="199"/>
+      <c r="B120" s="199"/>
+      <c r="C120" s="199"/>
+      <c r="D120" s="199"/>
+      <c r="E120" s="199"/>
     </row>
     <row r="121" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A121" s="196"/>
-      <c r="B121" s="196"/>
-      <c r="C121" s="196"/>
-      <c r="D121" s="196"/>
-      <c r="E121" s="196"/>
+      <c r="A121" s="199"/>
+      <c r="B121" s="199"/>
+      <c r="C121" s="199"/>
+      <c r="D121" s="199"/>
+      <c r="E121" s="199"/>
     </row>
   </sheetData>
   <mergeCells count="15">
+    <mergeCell ref="A118:E121"/>
+    <mergeCell ref="A113:C114"/>
+    <mergeCell ref="A76:B76"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="A69:B69"/>
+    <mergeCell ref="A70:B70"/>
     <mergeCell ref="A55:B55"/>
     <mergeCell ref="A57:B57"/>
     <mergeCell ref="A37:B37"/>
@@ -3202,12 +3201,6 @@
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="A13:E16"/>
     <mergeCell ref="B8:C10"/>
-    <mergeCell ref="A118:E121"/>
-    <mergeCell ref="A113:C114"/>
-    <mergeCell ref="A76:B76"/>
-    <mergeCell ref="A77:B77"/>
-    <mergeCell ref="A69:B69"/>
-    <mergeCell ref="A70:B70"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3248,18 +3241,18 @@
       <c r="E1" s="6"/>
       <c r="F1" s="6"/>
       <c r="G1" s="6"/>
-      <c r="H1" s="212"/>
-      <c r="I1" s="212"/>
-      <c r="J1" s="212"/>
-      <c r="K1" s="212"/>
-      <c r="L1" s="212"/>
-      <c r="M1" s="212"/>
-      <c r="N1" s="212"/>
-      <c r="O1" s="212"/>
-      <c r="P1" s="212"/>
-      <c r="Q1" s="212"/>
-      <c r="R1" s="212"/>
-      <c r="S1" s="212"/>
+      <c r="H1" s="224"/>
+      <c r="I1" s="224"/>
+      <c r="J1" s="224"/>
+      <c r="K1" s="224"/>
+      <c r="L1" s="224"/>
+      <c r="M1" s="224"/>
+      <c r="N1" s="224"/>
+      <c r="O1" s="224"/>
+      <c r="P1" s="224"/>
+      <c r="Q1" s="224"/>
+      <c r="R1" s="224"/>
+      <c r="S1" s="224"/>
       <c r="T1" s="6"/>
     </row>
     <row r="2" spans="1:23" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3267,37 +3260,39 @@
       <c r="B2" s="6"/>
       <c r="C2" s="6"/>
       <c r="D2" s="6"/>
-      <c r="E2" s="16" t="s">
+      <c r="E2" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="F2" s="227">
-        <v>0</v>
-      </c>
-      <c r="G2" s="227"/>
-      <c r="H2" s="169"/>
-      <c r="I2" s="169"/>
-      <c r="J2" s="16" t="s">
+      <c r="F2" s="223">
+        <f>V3</f>
+        <v>3320350</v>
+      </c>
+      <c r="G2" s="223"/>
+      <c r="H2" s="168"/>
+      <c r="I2" s="168"/>
+      <c r="J2" s="15" t="s">
         <v>135</v>
       </c>
-      <c r="K2" s="228">
-        <v>1839418.75</v>
-      </c>
-      <c r="L2" s="228"/>
-      <c r="M2" s="228"/>
-      <c r="N2" s="16"/>
-      <c r="O2" s="16"/>
-      <c r="P2" s="16" t="s">
+      <c r="K2" s="212">
+        <v>0</v>
+      </c>
+      <c r="L2" s="212"/>
+      <c r="M2" s="212"/>
+      <c r="N2" s="15"/>
+      <c r="O2" s="15"/>
+      <c r="P2" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="Q2" s="227">
-        <v>2678810.35</v>
-      </c>
-      <c r="R2" s="227"/>
-      <c r="S2" s="227"/>
-      <c r="T2" s="42"/>
-      <c r="U2" s="21"/>
+      <c r="Q2" s="223">
+        <f>V2</f>
+        <v>4163981.55</v>
+      </c>
+      <c r="R2" s="223"/>
+      <c r="S2" s="223"/>
+      <c r="T2" s="41"/>
+      <c r="U2" s="20"/>
       <c r="V2">
-        <v>4095718.96</v>
+        <v>4163981.55</v>
       </c>
     </row>
     <row r="3" spans="1:23" ht="13.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -3319,590 +3314,593 @@
       <c r="P3" s="6"/>
       <c r="Q3" s="6"/>
       <c r="R3" s="6"/>
-      <c r="S3" s="44"/>
-      <c r="T3" s="44"/>
+      <c r="S3" s="43"/>
+      <c r="T3" s="43"/>
+      <c r="V3">
+        <v>3320350</v>
+      </c>
     </row>
     <row r="4" spans="1:23" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="219" t="s">
+      <c r="A4" s="227" t="s">
         <v>160</v>
       </c>
-      <c r="B4" s="220"/>
-      <c r="C4" s="220"/>
-      <c r="D4" s="220"/>
-      <c r="E4" s="220"/>
-      <c r="F4" s="220"/>
-      <c r="G4" s="220"/>
-      <c r="H4" s="220"/>
-      <c r="I4" s="220"/>
-      <c r="J4" s="220"/>
-      <c r="K4" s="220"/>
-      <c r="L4" s="220"/>
-      <c r="M4" s="220"/>
-      <c r="N4" s="220"/>
-      <c r="O4" s="220"/>
-      <c r="P4" s="220"/>
-      <c r="Q4" s="220"/>
-      <c r="R4" s="220"/>
-      <c r="S4" s="220"/>
-      <c r="T4" s="221"/>
+      <c r="B4" s="228"/>
+      <c r="C4" s="228"/>
+      <c r="D4" s="228"/>
+      <c r="E4" s="228"/>
+      <c r="F4" s="228"/>
+      <c r="G4" s="228"/>
+      <c r="H4" s="228"/>
+      <c r="I4" s="228"/>
+      <c r="J4" s="228"/>
+      <c r="K4" s="228"/>
+      <c r="L4" s="228"/>
+      <c r="M4" s="228"/>
+      <c r="N4" s="228"/>
+      <c r="O4" s="228"/>
+      <c r="P4" s="228"/>
+      <c r="Q4" s="228"/>
+      <c r="R4" s="228"/>
+      <c r="S4" s="228"/>
+      <c r="T4" s="229"/>
     </row>
     <row r="5" spans="1:23" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="222"/>
-      <c r="B5" s="223"/>
-      <c r="C5" s="223"/>
-      <c r="D5" s="223"/>
-      <c r="E5" s="223"/>
-      <c r="F5" s="223"/>
-      <c r="G5" s="223"/>
-      <c r="H5" s="223"/>
-      <c r="I5" s="223"/>
-      <c r="J5" s="223"/>
-      <c r="K5" s="223"/>
-      <c r="L5" s="223"/>
-      <c r="M5" s="223"/>
-      <c r="N5" s="223"/>
-      <c r="O5" s="223"/>
-      <c r="P5" s="223"/>
-      <c r="Q5" s="223"/>
-      <c r="R5" s="223"/>
-      <c r="S5" s="223"/>
-      <c r="T5" s="224"/>
+      <c r="A5" s="230"/>
+      <c r="B5" s="231"/>
+      <c r="C5" s="231"/>
+      <c r="D5" s="231"/>
+      <c r="E5" s="231"/>
+      <c r="F5" s="231"/>
+      <c r="G5" s="231"/>
+      <c r="H5" s="231"/>
+      <c r="I5" s="231"/>
+      <c r="J5" s="231"/>
+      <c r="K5" s="231"/>
+      <c r="L5" s="231"/>
+      <c r="M5" s="231"/>
+      <c r="N5" s="231"/>
+      <c r="O5" s="231"/>
+      <c r="P5" s="231"/>
+      <c r="Q5" s="231"/>
+      <c r="R5" s="231"/>
+      <c r="S5" s="231"/>
+      <c r="T5" s="232"/>
     </row>
     <row r="6" spans="1:23" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="222"/>
-      <c r="B6" s="223"/>
-      <c r="C6" s="223"/>
-      <c r="D6" s="223"/>
-      <c r="E6" s="223"/>
-      <c r="F6" s="223"/>
-      <c r="G6" s="223"/>
-      <c r="H6" s="223"/>
-      <c r="I6" s="223"/>
-      <c r="J6" s="223"/>
-      <c r="K6" s="223"/>
-      <c r="L6" s="223"/>
-      <c r="M6" s="223"/>
-      <c r="N6" s="223"/>
-      <c r="O6" s="223"/>
-      <c r="P6" s="223"/>
-      <c r="Q6" s="223"/>
-      <c r="R6" s="223"/>
-      <c r="S6" s="223"/>
-      <c r="T6" s="224"/>
+      <c r="A6" s="230"/>
+      <c r="B6" s="231"/>
+      <c r="C6" s="231"/>
+      <c r="D6" s="231"/>
+      <c r="E6" s="231"/>
+      <c r="F6" s="231"/>
+      <c r="G6" s="231"/>
+      <c r="H6" s="231"/>
+      <c r="I6" s="231"/>
+      <c r="J6" s="231"/>
+      <c r="K6" s="231"/>
+      <c r="L6" s="231"/>
+      <c r="M6" s="231"/>
+      <c r="N6" s="231"/>
+      <c r="O6" s="231"/>
+      <c r="P6" s="231"/>
+      <c r="Q6" s="231"/>
+      <c r="R6" s="231"/>
+      <c r="S6" s="231"/>
+      <c r="T6" s="232"/>
     </row>
     <row r="7" spans="1:23" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="222"/>
-      <c r="B7" s="223"/>
-      <c r="C7" s="223"/>
-      <c r="D7" s="223"/>
-      <c r="E7" s="223"/>
-      <c r="F7" s="223"/>
-      <c r="G7" s="223"/>
-      <c r="H7" s="223"/>
-      <c r="I7" s="223"/>
-      <c r="J7" s="223"/>
-      <c r="K7" s="223"/>
-      <c r="L7" s="223"/>
-      <c r="M7" s="223"/>
-      <c r="N7" s="223"/>
-      <c r="O7" s="223"/>
-      <c r="P7" s="223"/>
-      <c r="Q7" s="223"/>
-      <c r="R7" s="223"/>
-      <c r="S7" s="223"/>
-      <c r="T7" s="224"/>
+      <c r="A7" s="230"/>
+      <c r="B7" s="231"/>
+      <c r="C7" s="231"/>
+      <c r="D7" s="231"/>
+      <c r="E7" s="231"/>
+      <c r="F7" s="231"/>
+      <c r="G7" s="231"/>
+      <c r="H7" s="231"/>
+      <c r="I7" s="231"/>
+      <c r="J7" s="231"/>
+      <c r="K7" s="231"/>
+      <c r="L7" s="231"/>
+      <c r="M7" s="231"/>
+      <c r="N7" s="231"/>
+      <c r="O7" s="231"/>
+      <c r="P7" s="231"/>
+      <c r="Q7" s="231"/>
+      <c r="R7" s="231"/>
+      <c r="S7" s="231"/>
+      <c r="T7" s="232"/>
     </row>
     <row r="8" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="213" t="s">
+      <c r="A8" s="216" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="215" t="s">
+      <c r="B8" s="207" t="s">
         <v>72</v>
       </c>
-      <c r="C8" s="215" t="s">
+      <c r="C8" s="207" t="s">
         <v>73</v>
       </c>
-      <c r="D8" s="215" t="s">
+      <c r="D8" s="207" t="s">
         <v>77</v>
       </c>
-      <c r="E8" s="215" t="s">
+      <c r="E8" s="207" t="s">
         <v>6</v>
       </c>
-      <c r="F8" s="215" t="s">
+      <c r="F8" s="207" t="s">
         <v>115</v>
       </c>
-      <c r="G8" s="215" t="s">
+      <c r="G8" s="207" t="s">
         <v>116</v>
       </c>
-      <c r="H8" s="213" t="s">
+      <c r="H8" s="216" t="s">
         <v>114</v>
       </c>
-      <c r="I8" s="149" t="s">
+      <c r="I8" s="148" t="s">
         <v>14</v>
       </c>
-      <c r="J8" s="213" t="s">
+      <c r="J8" s="216" t="s">
         <v>35</v>
       </c>
-      <c r="K8" s="215" t="s">
+      <c r="K8" s="207" t="s">
         <v>7</v>
       </c>
-      <c r="L8" s="215" t="s">
+      <c r="L8" s="207" t="s">
         <v>125</v>
       </c>
-      <c r="M8" s="217" t="s">
+      <c r="M8" s="225" t="s">
         <v>22</v>
       </c>
-      <c r="N8" s="213" t="s">
+      <c r="N8" s="216" t="s">
         <v>137</v>
       </c>
-      <c r="O8" s="213" t="s">
+      <c r="O8" s="216" t="s">
         <v>56</v>
       </c>
-      <c r="P8" s="213" t="s">
+      <c r="P8" s="216" t="s">
         <v>20</v>
       </c>
-      <c r="Q8" s="213" t="s">
+      <c r="Q8" s="216" t="s">
         <v>43</v>
       </c>
-      <c r="R8" s="237" t="s">
+      <c r="R8" s="205" t="s">
         <v>136</v>
       </c>
-      <c r="S8" s="150" t="s">
+      <c r="S8" s="149" t="s">
         <v>28</v>
       </c>
-      <c r="T8" s="225" t="s">
+      <c r="T8" s="233" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="214"/>
-      <c r="B9" s="216"/>
-      <c r="C9" s="216"/>
-      <c r="D9" s="216"/>
-      <c r="E9" s="216"/>
-      <c r="F9" s="216"/>
-      <c r="G9" s="216"/>
-      <c r="H9" s="214"/>
-      <c r="I9" s="162" t="s">
+      <c r="A9" s="217"/>
+      <c r="B9" s="208"/>
+      <c r="C9" s="208"/>
+      <c r="D9" s="208"/>
+      <c r="E9" s="208"/>
+      <c r="F9" s="208"/>
+      <c r="G9" s="208"/>
+      <c r="H9" s="217"/>
+      <c r="I9" s="161" t="s">
         <v>113</v>
       </c>
-      <c r="J9" s="214"/>
-      <c r="K9" s="216"/>
-      <c r="L9" s="216"/>
-      <c r="M9" s="218"/>
-      <c r="N9" s="214"/>
-      <c r="O9" s="214"/>
-      <c r="P9" s="214"/>
-      <c r="Q9" s="214"/>
-      <c r="R9" s="238"/>
-      <c r="S9" s="187" t="str">
+      <c r="J9" s="217"/>
+      <c r="K9" s="208"/>
+      <c r="L9" s="208"/>
+      <c r="M9" s="226"/>
+      <c r="N9" s="217"/>
+      <c r="O9" s="217"/>
+      <c r="P9" s="217"/>
+      <c r="Q9" s="217"/>
+      <c r="R9" s="206"/>
+      <c r="S9" s="186" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 17/09</v>
       </c>
-      <c r="T9" s="226"/>
+      <c r="T9" s="234"/>
     </row>
     <row r="10" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="167">
+      <c r="A10" s="166">
         <v>19</v>
       </c>
-      <c r="B10" s="152">
+      <c r="B10" s="151">
         <v>17</v>
       </c>
-      <c r="C10" s="152"/>
-      <c r="D10" s="152" t="s">
+      <c r="C10" s="151"/>
+      <c r="D10" s="151" t="s">
         <v>78</v>
       </c>
-      <c r="E10" s="164" t="s">
+      <c r="E10" s="163" t="s">
         <v>96</v>
       </c>
-      <c r="F10" s="165">
+      <c r="F10" s="164">
         <v>5.44</v>
       </c>
-      <c r="G10" s="165">
+      <c r="G10" s="164">
         <v>0.12</v>
       </c>
-      <c r="H10" s="166"/>
-      <c r="I10" s="168">
+      <c r="H10" s="165"/>
+      <c r="I10" s="167">
         <f>SUM(F10:H10)</f>
         <v>5.5600000000000005</v>
       </c>
-      <c r="J10" s="163">
+      <c r="J10" s="162">
         <v>251132.19</v>
       </c>
-      <c r="K10" s="195">
+      <c r="K10" s="160">
         <f>J10</f>
         <v>251132.19</v>
       </c>
-      <c r="L10" s="161" t="s">
+      <c r="L10" s="160" t="s">
         <v>126</v>
       </c>
-      <c r="M10" s="160">
+      <c r="M10" s="159">
         <f t="shared" ref="M10:M33" si="0">J10-K10</f>
         <v>0</v>
       </c>
-      <c r="N10" s="160">
+      <c r="N10" s="159">
         <f>IF(M10&gt;0,M10*2%,0)</f>
         <v>0</v>
       </c>
-      <c r="O10" s="160"/>
-      <c r="P10" s="158">
+      <c r="O10" s="159"/>
+      <c r="P10" s="157">
         <f>Q$2*I10/100</f>
-        <v>148941.85546000002</v>
-      </c>
-      <c r="Q10" s="159">
+        <v>231517.37418000001</v>
+      </c>
+      <c r="Q10" s="158">
         <f>F$2*I10/100</f>
-        <v>0</v>
-      </c>
-      <c r="R10" s="159">
+        <v>184611.46</v>
+      </c>
+      <c r="R10" s="158">
         <f>K$2/18</f>
-        <v>102189.93055555556</v>
-      </c>
-      <c r="S10" s="157">
+        <v>0</v>
+      </c>
+      <c r="S10" s="156">
         <f>ROUND(SUM(M10:R10),0) + U10</f>
-        <v>251132.19</v>
-      </c>
-      <c r="T10" s="157">
+        <v>416129.19</v>
+      </c>
+      <c r="T10" s="156">
         <f t="shared" ref="T10:T33" si="1">ROUND(S10*3%,0) + S10</f>
-        <v>258666.19</v>
-      </c>
-      <c r="U10" s="32">
+        <v>428613.19</v>
+      </c>
+      <c r="U10" s="31">
         <f t="shared" ref="U10:U15" si="2">A10/100</f>
         <v>0.19</v>
       </c>
-      <c r="V10" s="32" t="s">
+      <c r="V10" s="31" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="11" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="155">
+      <c r="A11" s="154">
         <v>20</v>
       </c>
-      <c r="B11" s="131"/>
-      <c r="C11" s="131"/>
-      <c r="D11" s="131" t="s">
+      <c r="B11" s="130"/>
+      <c r="C11" s="130"/>
+      <c r="D11" s="130" t="s">
         <v>79</v>
       </c>
-      <c r="E11" s="93" t="s">
+      <c r="E11" s="92" t="s">
         <v>97</v>
       </c>
-      <c r="F11" s="94">
+      <c r="F11" s="93">
         <v>2.87</v>
       </c>
-      <c r="G11" s="94"/>
-      <c r="H11" s="137"/>
-      <c r="I11" s="138">
+      <c r="G11" s="93"/>
+      <c r="H11" s="136"/>
+      <c r="I11" s="137">
         <f t="shared" ref="I11:I33" si="3">SUM(F11:H11)</f>
         <v>2.87</v>
       </c>
-      <c r="J11" s="95">
+      <c r="J11" s="94">
         <v>76882.2</v>
       </c>
-      <c r="K11" s="193">
+      <c r="K11" s="99">
         <v>99395</v>
       </c>
-      <c r="L11" s="118" t="s">
+      <c r="L11" s="117" t="s">
         <v>126</v>
       </c>
-      <c r="M11" s="96">
+      <c r="M11" s="95">
         <f t="shared" si="0"/>
         <v>-22512.800000000003</v>
       </c>
-      <c r="N11" s="160">
+      <c r="N11" s="159">
         <f t="shared" ref="N11:N33" si="4">IF(M11&gt;0,M11*2%,0)</f>
         <v>0</v>
       </c>
-      <c r="O11" s="96"/>
-      <c r="P11" s="97">
+      <c r="O11" s="95"/>
+      <c r="P11" s="96">
         <f t="shared" ref="P11:P33" si="5">Q$2*I11/100</f>
-        <v>76881.857045000012</v>
-      </c>
-      <c r="Q11" s="98">
+        <v>119506.270485</v>
+      </c>
+      <c r="Q11" s="97">
         <f t="shared" ref="Q11:Q33" si="6">F$2*I11/100</f>
-        <v>0</v>
-      </c>
-      <c r="R11" s="98"/>
-      <c r="S11" s="157">
+        <v>95294.044999999998</v>
+      </c>
+      <c r="R11" s="97"/>
+      <c r="S11" s="156">
         <f t="shared" ref="S11:S26" si="7">ROUND(SUM(M11:R11),0) + U11</f>
-        <v>54369.2</v>
-      </c>
-      <c r="T11" s="139">
+        <v>192288.2</v>
+      </c>
+      <c r="T11" s="138">
         <f t="shared" si="1"/>
-        <v>56000.2</v>
-      </c>
-      <c r="U11" s="32">
+        <v>198057.2</v>
+      </c>
+      <c r="U11" s="31">
         <f t="shared" si="2"/>
         <v>0.2</v>
       </c>
-      <c r="V11" s="32" t="s">
+      <c r="V11" s="31" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="12" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="156">
+      <c r="A12" s="155">
         <v>21</v>
       </c>
-      <c r="B12" s="132">
+      <c r="B12" s="131">
         <v>15</v>
       </c>
-      <c r="C12" s="132"/>
-      <c r="D12" s="132" t="s">
+      <c r="C12" s="131"/>
+      <c r="D12" s="131" t="s">
         <v>80</v>
       </c>
-      <c r="E12" s="99" t="s">
+      <c r="E12" s="98" t="s">
         <v>98</v>
       </c>
-      <c r="F12" s="94">
+      <c r="F12" s="93">
         <v>5.44</v>
       </c>
-      <c r="G12" s="94">
+      <c r="G12" s="93">
         <v>0.12</v>
       </c>
-      <c r="H12" s="137"/>
-      <c r="I12" s="138">
+      <c r="H12" s="136"/>
+      <c r="I12" s="137">
         <f t="shared" si="3"/>
         <v>5.5600000000000005</v>
       </c>
-      <c r="J12" s="100">
+      <c r="J12" s="99">
         <v>267566.21000000002</v>
       </c>
-      <c r="K12" s="100">
-        <v>0</v>
-      </c>
-      <c r="L12" s="118" t="s">
+      <c r="K12" s="99">
+        <v>0</v>
+      </c>
+      <c r="L12" s="117" t="s">
         <v>126</v>
       </c>
-      <c r="M12" s="96">
+      <c r="M12" s="95">
         <f t="shared" si="0"/>
         <v>267566.21000000002</v>
       </c>
-      <c r="N12" s="160">
+      <c r="N12" s="159">
         <f t="shared" si="4"/>
         <v>5351.3242000000009</v>
       </c>
-      <c r="O12" s="96"/>
-      <c r="P12" s="97">
+      <c r="O12" s="95"/>
+      <c r="P12" s="96">
         <f t="shared" si="5"/>
-        <v>148941.85546000002</v>
-      </c>
-      <c r="Q12" s="98">
+        <v>231517.37418000001</v>
+      </c>
+      <c r="Q12" s="97">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="R12" s="159">
+        <v>184611.46</v>
+      </c>
+      <c r="R12" s="158">
         <f>K$2/18</f>
-        <v>102189.93055555556</v>
-      </c>
-      <c r="S12" s="157">
+        <v>0</v>
+      </c>
+      <c r="S12" s="156">
         <f t="shared" si="7"/>
-        <v>524049.21</v>
-      </c>
-      <c r="T12" s="139">
+        <v>689046.21</v>
+      </c>
+      <c r="T12" s="138">
         <f t="shared" si="1"/>
-        <v>539770.21</v>
-      </c>
-      <c r="U12" s="32">
+        <v>709717.21</v>
+      </c>
+      <c r="U12" s="31">
         <f t="shared" si="2"/>
         <v>0.21</v>
       </c>
-      <c r="V12" s="31"/>
+      <c r="V12" s="30"/>
     </row>
     <row r="13" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="155">
+      <c r="A13" s="154">
         <v>22</v>
       </c>
-      <c r="B13" s="131"/>
-      <c r="C13" s="131"/>
-      <c r="D13" s="131" t="s">
+      <c r="B13" s="130"/>
+      <c r="C13" s="130"/>
+      <c r="D13" s="130" t="s">
         <v>81</v>
       </c>
-      <c r="E13" s="93" t="s">
+      <c r="E13" s="92" t="s">
         <v>97</v>
       </c>
-      <c r="F13" s="94">
+      <c r="F13" s="93">
         <v>2.87</v>
       </c>
-      <c r="G13" s="94"/>
-      <c r="H13" s="137"/>
-      <c r="I13" s="138">
+      <c r="G13" s="93"/>
+      <c r="H13" s="136"/>
+      <c r="I13" s="137">
         <f t="shared" si="3"/>
         <v>2.87</v>
       </c>
-      <c r="J13" s="95">
+      <c r="J13" s="94">
         <v>76882.22</v>
       </c>
-      <c r="K13" s="193">
+      <c r="K13" s="99">
         <f>J13</f>
         <v>76882.22</v>
       </c>
-      <c r="L13" s="118" t="s">
+      <c r="L13" s="117" t="s">
         <v>126</v>
       </c>
-      <c r="M13" s="96">
+      <c r="M13" s="95">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N13" s="160">
+      <c r="N13" s="159">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O13" s="96"/>
-      <c r="P13" s="97">
+      <c r="O13" s="95"/>
+      <c r="P13" s="96">
         <f t="shared" si="5"/>
-        <v>76881.857045000012</v>
-      </c>
-      <c r="Q13" s="98">
+        <v>119506.270485</v>
+      </c>
+      <c r="Q13" s="97">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="R13" s="98"/>
-      <c r="S13" s="157">
+        <v>95294.044999999998</v>
+      </c>
+      <c r="R13" s="97"/>
+      <c r="S13" s="156">
         <f t="shared" si="7"/>
-        <v>76882.22</v>
-      </c>
-      <c r="T13" s="139">
+        <v>214800.22</v>
+      </c>
+      <c r="T13" s="138">
         <f t="shared" si="1"/>
-        <v>79188.22</v>
-      </c>
-      <c r="U13" s="32">
+        <v>221244.22</v>
+      </c>
+      <c r="U13" s="31">
         <f t="shared" si="2"/>
         <v>0.22</v>
       </c>
       <c r="V13" t="s">
         <v>118</v>
       </c>
-      <c r="W13" s="32"/>
+      <c r="W13" s="31"/>
     </row>
     <row r="14" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="155">
+      <c r="A14" s="154">
         <v>23</v>
       </c>
-      <c r="B14" s="131">
+      <c r="B14" s="130">
         <v>7</v>
       </c>
-      <c r="C14" s="131" t="s">
+      <c r="C14" s="130" t="s">
         <v>74</v>
       </c>
-      <c r="D14" s="131" t="s">
+      <c r="D14" s="130" t="s">
         <v>82</v>
       </c>
-      <c r="E14" s="93" t="s">
+      <c r="E14" s="92" t="s">
         <v>99</v>
       </c>
-      <c r="F14" s="94">
+      <c r="F14" s="93">
         <v>5.44</v>
       </c>
-      <c r="G14" s="94">
+      <c r="G14" s="93">
         <v>0.41</v>
       </c>
-      <c r="H14" s="137">
+      <c r="H14" s="136">
         <v>0.09</v>
       </c>
-      <c r="I14" s="138">
+      <c r="I14" s="137">
         <f t="shared" si="3"/>
         <v>5.94</v>
       </c>
-      <c r="J14" s="95">
+      <c r="J14" s="94">
         <v>261311.23</v>
       </c>
-      <c r="K14" s="193">
+      <c r="K14" s="99">
         <f>19167.23+242144.23</f>
         <v>261311.46000000002</v>
       </c>
-      <c r="L14" s="118" t="s">
+      <c r="L14" s="117" t="s">
         <v>126</v>
       </c>
-      <c r="M14" s="96">
+      <c r="M14" s="95">
         <f t="shared" si="0"/>
         <v>-0.23000000001047738</v>
       </c>
-      <c r="N14" s="160">
+      <c r="N14" s="159">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O14" s="96"/>
-      <c r="P14" s="97">
+      <c r="O14" s="95"/>
+      <c r="P14" s="96">
         <f t="shared" si="5"/>
-        <v>159121.33479000002</v>
-      </c>
-      <c r="Q14" s="98">
+        <v>247340.50407000002</v>
+      </c>
+      <c r="Q14" s="97">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="R14" s="159">
+        <v>197228.79</v>
+      </c>
+      <c r="R14" s="158">
         <f>K$2/18</f>
-        <v>102189.93055555556</v>
-      </c>
-      <c r="S14" s="157">
+        <v>0</v>
+      </c>
+      <c r="S14" s="156">
         <f t="shared" si="7"/>
-        <v>261311.23</v>
-      </c>
-      <c r="T14" s="139">
+        <v>444569.23</v>
+      </c>
+      <c r="T14" s="138">
         <f t="shared" si="1"/>
-        <v>269150.23</v>
-      </c>
-      <c r="U14" s="32">
+        <v>457906.23</v>
+      </c>
+      <c r="U14" s="31">
         <f t="shared" si="2"/>
         <v>0.23</v>
       </c>
-      <c r="W14" s="32"/>
+      <c r="W14" s="31"/>
     </row>
     <row r="15" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="155">
+      <c r="A15" s="154">
         <v>24</v>
       </c>
-      <c r="B15" s="131"/>
-      <c r="C15" s="131"/>
-      <c r="D15" s="131" t="s">
+      <c r="B15" s="130"/>
+      <c r="C15" s="130"/>
+      <c r="D15" s="130" t="s">
         <v>83</v>
       </c>
-      <c r="E15" s="93" t="s">
+      <c r="E15" s="92" t="s">
         <v>100</v>
       </c>
-      <c r="F15" s="94">
+      <c r="F15" s="93">
         <v>2.87</v>
       </c>
-      <c r="G15" s="94"/>
-      <c r="H15" s="137"/>
-      <c r="I15" s="138">
+      <c r="G15" s="93"/>
+      <c r="H15" s="136"/>
+      <c r="I15" s="137">
         <f t="shared" si="3"/>
         <v>2.87</v>
       </c>
-      <c r="J15" s="95">
+      <c r="J15" s="94">
         <v>76882.240000000005</v>
       </c>
-      <c r="K15" s="193">
+      <c r="K15" s="99">
         <v>114800.24</v>
       </c>
-      <c r="L15" s="118" t="s">
+      <c r="L15" s="117" t="s">
         <v>126</v>
       </c>
-      <c r="M15" s="96">
+      <c r="M15" s="95">
         <f t="shared" si="0"/>
         <v>-37918</v>
       </c>
-      <c r="N15" s="160">
+      <c r="N15" s="159">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O15" s="96"/>
-      <c r="P15" s="97">
+      <c r="O15" s="95"/>
+      <c r="P15" s="96">
         <f t="shared" si="5"/>
-        <v>76881.857045000012</v>
-      </c>
-      <c r="Q15" s="98">
+        <v>119506.270485</v>
+      </c>
+      <c r="Q15" s="97">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="R15" s="98"/>
-      <c r="S15" s="157">
+        <v>95294.044999999998</v>
+      </c>
+      <c r="R15" s="97"/>
+      <c r="S15" s="156">
         <f t="shared" si="7"/>
-        <v>38964.239999999998</v>
-      </c>
-      <c r="T15" s="139">
+        <v>176882.24</v>
+      </c>
+      <c r="T15" s="138">
         <f t="shared" si="1"/>
-        <v>40133.24</v>
-      </c>
-      <c r="U15" s="32">
+        <v>182188.24</v>
+      </c>
+      <c r="U15" s="31">
         <f t="shared" si="2"/>
         <v>0.24</v>
       </c>
@@ -3911,205 +3909,206 @@
       </c>
     </row>
     <row r="16" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="155" t="s">
+      <c r="A16" s="154" t="s">
         <v>71</v>
       </c>
-      <c r="B16" s="131">
+      <c r="B16" s="130">
         <v>9</v>
       </c>
-      <c r="C16" s="131"/>
-      <c r="D16" s="131" t="s">
+      <c r="C16" s="130"/>
+      <c r="D16" s="130" t="s">
         <v>84</v>
       </c>
-      <c r="E16" s="93" t="s">
+      <c r="E16" s="92" t="s">
         <v>100</v>
       </c>
-      <c r="F16" s="94"/>
-      <c r="G16" s="94">
+      <c r="F16" s="93"/>
+      <c r="G16" s="93">
         <v>0.53</v>
       </c>
-      <c r="H16" s="137"/>
-      <c r="I16" s="138">
+      <c r="H16" s="136"/>
+      <c r="I16" s="137">
         <f t="shared" si="3"/>
         <v>0.53</v>
       </c>
-      <c r="J16" s="95">
+      <c r="J16" s="94">
         <v>116388.24</v>
       </c>
-      <c r="K16" s="193">
+      <c r="K16" s="99">
         <f>J16</f>
         <v>116388.24</v>
       </c>
-      <c r="L16" s="118" t="s">
+      <c r="L16" s="117" t="s">
         <v>126</v>
       </c>
-      <c r="M16" s="96">
+      <c r="M16" s="95">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N16" s="160">
+      <c r="N16" s="159">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O16" s="96"/>
-      <c r="P16" s="97">
+      <c r="O16" s="95"/>
+      <c r="P16" s="96">
         <f t="shared" si="5"/>
-        <v>14197.694855000002</v>
-      </c>
-      <c r="Q16" s="98">
+        <v>22069.102214999999</v>
+      </c>
+      <c r="Q16" s="97">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="R16" s="159">
+        <v>17597.855</v>
+      </c>
+      <c r="R16" s="158">
         <f t="shared" ref="R16:R21" si="8">K$2/18</f>
-        <v>102189.93055555556</v>
-      </c>
-      <c r="S16" s="157">
+        <v>0</v>
+      </c>
+      <c r="S16" s="156">
         <f t="shared" si="7"/>
-        <v>116388.24</v>
-      </c>
-      <c r="T16" s="139">
+        <v>39667.24</v>
+      </c>
+      <c r="T16" s="138">
         <f t="shared" si="1"/>
-        <v>119880.24</v>
-      </c>
-      <c r="U16" s="32">
+        <v>40857.24</v>
+      </c>
+      <c r="U16" s="31">
         <v>0.24</v>
       </c>
     </row>
     <row r="17" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="155">
+      <c r="A17" s="154">
         <v>25</v>
       </c>
-      <c r="B17" s="131">
+      <c r="B17" s="130">
         <v>14</v>
       </c>
-      <c r="C17" s="131"/>
-      <c r="D17" s="131" t="s">
+      <c r="C17" s="130"/>
+      <c r="D17" s="130" t="s">
         <v>85</v>
       </c>
-      <c r="E17" s="93" t="s">
+      <c r="E17" s="92" t="s">
         <v>101</v>
       </c>
-      <c r="F17" s="94">
+      <c r="F17" s="93">
         <v>5.44</v>
       </c>
-      <c r="G17" s="94">
+      <c r="G17" s="93">
         <v>0.12</v>
       </c>
-      <c r="H17" s="137"/>
-      <c r="I17" s="138">
+      <c r="H17" s="136"/>
+      <c r="I17" s="137">
         <f t="shared" si="3"/>
         <v>5.5600000000000005</v>
       </c>
-      <c r="J17" s="95">
+      <c r="J17" s="94">
         <v>224658.25</v>
       </c>
-      <c r="K17" s="100">
-        <v>0</v>
-      </c>
-      <c r="L17" s="118" t="s">
+      <c r="K17" s="99">
+        <f>191500+33158.25</f>
+        <v>224658.25</v>
+      </c>
+      <c r="L17" s="117" t="s">
         <v>126</v>
       </c>
-      <c r="M17" s="96">
+      <c r="M17" s="95">
         <f t="shared" si="0"/>
-        <v>224658.25</v>
-      </c>
-      <c r="N17" s="160">
+        <v>0</v>
+      </c>
+      <c r="N17" s="159">
         <f t="shared" si="4"/>
-        <v>4493.165</v>
-      </c>
-      <c r="O17" s="96"/>
-      <c r="P17" s="97">
+        <v>0</v>
+      </c>
+      <c r="O17" s="95"/>
+      <c r="P17" s="96">
         <f t="shared" si="5"/>
-        <v>148941.85546000002</v>
-      </c>
-      <c r="Q17" s="98">
+        <v>231517.37418000001</v>
+      </c>
+      <c r="Q17" s="97">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="R17" s="159">
+        <v>184611.46</v>
+      </c>
+      <c r="R17" s="158">
         <f t="shared" si="8"/>
-        <v>102189.93055555556</v>
-      </c>
-      <c r="S17" s="157">
+        <v>0</v>
+      </c>
+      <c r="S17" s="156">
         <f t="shared" si="7"/>
-        <v>480283.25</v>
-      </c>
-      <c r="T17" s="139">
+        <v>416129.25</v>
+      </c>
+      <c r="T17" s="138">
         <f t="shared" si="1"/>
-        <v>494691.25</v>
-      </c>
-      <c r="U17" s="32">
+        <v>428613.25</v>
+      </c>
+      <c r="U17" s="31">
         <f t="shared" ref="U17:U27" si="9">A17/100</f>
         <v>0.25</v>
       </c>
     </row>
     <row r="18" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="155">
+      <c r="A18" s="154">
         <f>A17+1</f>
         <v>26</v>
       </c>
-      <c r="B18" s="131">
+      <c r="B18" s="130">
         <v>8</v>
       </c>
-      <c r="C18" s="131"/>
-      <c r="D18" s="131" t="s">
+      <c r="C18" s="130"/>
+      <c r="D18" s="130" t="s">
         <v>86</v>
       </c>
-      <c r="E18" s="93" t="s">
+      <c r="E18" s="92" t="s">
         <v>102</v>
       </c>
-      <c r="F18" s="94">
+      <c r="F18" s="93">
         <v>2.87</v>
       </c>
-      <c r="G18" s="94">
+      <c r="G18" s="93">
         <v>0.41</v>
       </c>
-      <c r="H18" s="137"/>
-      <c r="I18" s="138">
+      <c r="H18" s="136"/>
+      <c r="I18" s="137">
         <f t="shared" si="3"/>
         <v>3.2800000000000002</v>
       </c>
-      <c r="J18" s="95">
+      <c r="J18" s="94">
         <v>190055.26</v>
       </c>
-      <c r="K18" s="193">
+      <c r="K18" s="99">
         <f>135644.26+54411</f>
         <v>190055.26</v>
       </c>
-      <c r="L18" s="118" t="s">
+      <c r="L18" s="117" t="s">
         <v>126</v>
       </c>
-      <c r="M18" s="96">
+      <c r="M18" s="95">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N18" s="160">
+      <c r="N18" s="159">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O18" s="96"/>
-      <c r="P18" s="97">
+      <c r="O18" s="95"/>
+      <c r="P18" s="96">
         <f t="shared" si="5"/>
-        <v>87864.979480000009</v>
-      </c>
-      <c r="Q18" s="98">
+        <v>136578.59484000001</v>
+      </c>
+      <c r="Q18" s="97">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="R18" s="159">
+        <v>108907.48</v>
+      </c>
+      <c r="R18" s="158">
         <f t="shared" si="8"/>
-        <v>102189.93055555556</v>
-      </c>
-      <c r="S18" s="157">
+        <v>0</v>
+      </c>
+      <c r="S18" s="156">
         <f t="shared" si="7"/>
-        <v>190055.26</v>
-      </c>
-      <c r="T18" s="139">
+        <v>245486.26</v>
+      </c>
+      <c r="T18" s="138">
         <f t="shared" si="1"/>
-        <v>195757.26</v>
-      </c>
-      <c r="U18" s="32">
+        <v>252851.26</v>
+      </c>
+      <c r="U18" s="31">
         <f t="shared" si="9"/>
         <v>0.26</v>
       </c>
@@ -4118,139 +4117,139 @@
       </c>
     </row>
     <row r="19" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="155">
+      <c r="A19" s="154">
         <f t="shared" ref="A19:A27" si="10">A18+1</f>
         <v>27</v>
       </c>
-      <c r="B19" s="131">
+      <c r="B19" s="130">
         <v>13</v>
       </c>
-      <c r="C19" s="131"/>
-      <c r="D19" s="131" t="s">
+      <c r="C19" s="130"/>
+      <c r="D19" s="130" t="s">
         <v>87</v>
       </c>
-      <c r="E19" s="93" t="s">
+      <c r="E19" s="92" t="s">
         <v>103</v>
       </c>
-      <c r="F19" s="94">
+      <c r="F19" s="93">
         <v>5.44</v>
       </c>
-      <c r="G19" s="94">
+      <c r="G19" s="93">
         <v>0.12</v>
       </c>
-      <c r="H19" s="137"/>
-      <c r="I19" s="138">
+      <c r="H19" s="136"/>
+      <c r="I19" s="137">
         <f t="shared" si="3"/>
         <v>5.5600000000000005</v>
       </c>
-      <c r="J19" s="95">
+      <c r="J19" s="94">
         <v>242587.27</v>
       </c>
-      <c r="K19" s="193">
+      <c r="K19" s="99">
         <v>218300.27</v>
       </c>
-      <c r="L19" s="118" t="s">
+      <c r="L19" s="117" t="s">
         <v>55</v>
       </c>
-      <c r="M19" s="96">
+      <c r="M19" s="95">
         <f t="shared" si="0"/>
         <v>24287</v>
       </c>
-      <c r="N19" s="160">
-        <v>0</v>
-      </c>
-      <c r="O19" s="96"/>
-      <c r="P19" s="97">
+      <c r="N19" s="159">
+        <v>0</v>
+      </c>
+      <c r="O19" s="95"/>
+      <c r="P19" s="96">
         <f t="shared" si="5"/>
-        <v>148941.85546000002</v>
-      </c>
-      <c r="Q19" s="98">
+        <v>231517.37418000001</v>
+      </c>
+      <c r="Q19" s="97">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="R19" s="159">
+        <v>184611.46</v>
+      </c>
+      <c r="R19" s="158">
         <f t="shared" si="8"/>
-        <v>102189.93055555556</v>
-      </c>
-      <c r="S19" s="157">
+        <v>0</v>
+      </c>
+      <c r="S19" s="156">
         <f t="shared" si="7"/>
-        <v>275419.27</v>
-      </c>
-      <c r="T19" s="139">
+        <v>440416.27</v>
+      </c>
+      <c r="T19" s="138">
         <f t="shared" si="1"/>
-        <v>283682.27</v>
-      </c>
-      <c r="U19" s="32">
+        <v>453628.27</v>
+      </c>
+      <c r="U19" s="31">
         <f t="shared" si="9"/>
         <v>0.27</v>
       </c>
     </row>
     <row r="20" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="155">
+      <c r="A20" s="154">
         <f t="shared" si="10"/>
         <v>28</v>
       </c>
-      <c r="B20" s="131">
+      <c r="B20" s="130">
         <v>6</v>
       </c>
-      <c r="C20" s="131"/>
-      <c r="D20" s="131" t="s">
+      <c r="C20" s="130"/>
+      <c r="D20" s="130" t="s">
         <v>88</v>
       </c>
-      <c r="E20" s="93" t="s">
+      <c r="E20" s="92" t="s">
         <v>102</v>
       </c>
-      <c r="F20" s="94">
+      <c r="F20" s="93">
         <v>2.87</v>
       </c>
-      <c r="G20" s="94">
+      <c r="G20" s="93">
         <v>0.41</v>
       </c>
-      <c r="H20" s="137"/>
-      <c r="I20" s="138">
+      <c r="H20" s="136"/>
+      <c r="I20" s="137">
         <f t="shared" si="3"/>
         <v>3.2800000000000002</v>
       </c>
-      <c r="J20" s="95">
+      <c r="J20" s="94">
         <v>190055.28</v>
       </c>
-      <c r="K20" s="193">
+      <c r="K20" s="99">
         <f>135644.28+54411</f>
         <v>190055.28</v>
       </c>
-      <c r="L20" s="118" t="s">
+      <c r="L20" s="117" t="s">
         <v>126</v>
       </c>
-      <c r="M20" s="124">
+      <c r="M20" s="123">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N20" s="160">
+      <c r="N20" s="159">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O20" s="96"/>
-      <c r="P20" s="97">
+      <c r="O20" s="95"/>
+      <c r="P20" s="96">
         <f t="shared" si="5"/>
-        <v>87864.979480000009</v>
-      </c>
-      <c r="Q20" s="98">
+        <v>136578.59484000001</v>
+      </c>
+      <c r="Q20" s="97">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="R20" s="159">
+        <v>108907.48</v>
+      </c>
+      <c r="R20" s="158">
         <f t="shared" si="8"/>
-        <v>102189.93055555556</v>
-      </c>
-      <c r="S20" s="157">
+        <v>0</v>
+      </c>
+      <c r="S20" s="156">
         <f t="shared" si="7"/>
-        <v>190055.28</v>
-      </c>
-      <c r="T20" s="139">
+        <v>245486.28</v>
+      </c>
+      <c r="T20" s="138">
         <f t="shared" si="1"/>
-        <v>195757.28</v>
-      </c>
-      <c r="U20" s="32">
+        <v>252851.28</v>
+      </c>
+      <c r="U20" s="31">
         <f t="shared" si="9"/>
         <v>0.28000000000000003</v>
       </c>
@@ -4259,135 +4258,135 @@
       </c>
     </row>
     <row r="21" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="155">
+      <c r="A21" s="154">
         <f t="shared" si="10"/>
         <v>29</v>
       </c>
-      <c r="B21" s="131">
+      <c r="B21" s="130">
         <v>11</v>
       </c>
-      <c r="C21" s="131" t="s">
+      <c r="C21" s="130" t="s">
         <v>75</v>
       </c>
-      <c r="D21" s="131" t="s">
+      <c r="D21" s="130" t="s">
         <v>89</v>
       </c>
-      <c r="E21" s="93" t="s">
+      <c r="E21" s="92" t="s">
         <v>104</v>
       </c>
-      <c r="F21" s="94">
+      <c r="F21" s="93">
         <v>5.44</v>
       </c>
-      <c r="G21" s="137">
+      <c r="G21" s="136">
         <v>0.2</v>
       </c>
-      <c r="H21" s="137">
+      <c r="H21" s="136">
         <v>0.09</v>
       </c>
-      <c r="I21" s="138">
+      <c r="I21" s="137">
         <f t="shared" si="3"/>
         <v>5.73</v>
       </c>
-      <c r="J21" s="95">
+      <c r="J21" s="94">
         <v>255686.29</v>
       </c>
-      <c r="K21" s="193">
+      <c r="K21" s="99">
         <v>233644.29</v>
       </c>
-      <c r="L21" s="118" t="s">
+      <c r="L21" s="117" t="s">
         <v>126</v>
       </c>
-      <c r="M21" s="124">
+      <c r="M21" s="123">
         <f t="shared" si="0"/>
         <v>22042</v>
       </c>
-      <c r="N21" s="160">
-        <v>0</v>
-      </c>
-      <c r="O21" s="96"/>
-      <c r="P21" s="97">
+      <c r="N21" s="159">
+        <v>0</v>
+      </c>
+      <c r="O21" s="95"/>
+      <c r="P21" s="96">
         <f t="shared" si="5"/>
-        <v>153495.83305500002</v>
-      </c>
-      <c r="Q21" s="98">
+        <v>238596.142815</v>
+      </c>
+      <c r="Q21" s="97">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="R21" s="159">
+        <v>190256.05499999999</v>
+      </c>
+      <c r="R21" s="158">
         <f t="shared" si="8"/>
-        <v>102189.93055555556</v>
-      </c>
-      <c r="S21" s="157">
+        <v>0</v>
+      </c>
+      <c r="S21" s="156">
         <f t="shared" si="7"/>
-        <v>277728.28999999998</v>
-      </c>
-      <c r="T21" s="139">
+        <v>450894.29</v>
+      </c>
+      <c r="T21" s="138">
         <f t="shared" si="1"/>
-        <v>286060.28999999998</v>
-      </c>
-      <c r="U21" s="32">
+        <v>464421.29</v>
+      </c>
+      <c r="U21" s="31">
         <f t="shared" si="9"/>
         <v>0.28999999999999998</v>
       </c>
     </row>
     <row r="22" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="155">
+      <c r="A22" s="154">
         <f t="shared" si="10"/>
         <v>30</v>
       </c>
-      <c r="B22" s="131"/>
-      <c r="C22" s="131"/>
-      <c r="D22" s="131" t="s">
+      <c r="B22" s="130"/>
+      <c r="C22" s="130"/>
+      <c r="D22" s="130" t="s">
         <v>90</v>
       </c>
-      <c r="E22" s="93" t="s">
+      <c r="E22" s="92" t="s">
         <v>105</v>
       </c>
-      <c r="F22" s="94">
+      <c r="F22" s="93">
         <v>2.87</v>
       </c>
-      <c r="G22" s="94"/>
-      <c r="H22" s="137"/>
-      <c r="I22" s="138">
+      <c r="G22" s="93"/>
+      <c r="H22" s="136"/>
+      <c r="I22" s="137">
         <f t="shared" si="3"/>
         <v>2.87</v>
       </c>
-      <c r="J22" s="95">
+      <c r="J22" s="94">
         <v>76637.3</v>
       </c>
-      <c r="K22" s="193">
+      <c r="K22" s="99">
         <v>76700</v>
       </c>
-      <c r="L22" s="118" t="s">
+      <c r="L22" s="117" t="s">
         <v>126</v>
       </c>
-      <c r="M22" s="124">
+      <c r="M22" s="123">
         <f t="shared" si="0"/>
         <v>-62.69999999999709</v>
       </c>
-      <c r="N22" s="160">
+      <c r="N22" s="159">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O22" s="96"/>
-      <c r="P22" s="97">
+      <c r="O22" s="95"/>
+      <c r="P22" s="96">
         <f t="shared" si="5"/>
-        <v>76881.857045000012</v>
-      </c>
-      <c r="Q22" s="98">
+        <v>119506.270485</v>
+      </c>
+      <c r="Q22" s="97">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="R22" s="98"/>
-      <c r="S22" s="157">
+        <v>95294.044999999998</v>
+      </c>
+      <c r="R22" s="97"/>
+      <c r="S22" s="156">
         <f t="shared" si="7"/>
-        <v>76819.3</v>
-      </c>
-      <c r="T22" s="139">
+        <v>214738.3</v>
+      </c>
+      <c r="T22" s="138">
         <f t="shared" si="1"/>
-        <v>79124.3</v>
-      </c>
-      <c r="U22" s="32">
+        <v>221180.3</v>
+      </c>
+      <c r="U22" s="31">
         <f t="shared" si="9"/>
         <v>0.3</v>
       </c>
@@ -4396,136 +4395,136 @@
       </c>
     </row>
     <row r="23" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="155">
+      <c r="A23" s="154">
         <f t="shared" si="10"/>
         <v>31</v>
       </c>
-      <c r="B23" s="131">
+      <c r="B23" s="130">
         <v>1</v>
       </c>
-      <c r="C23" s="131" t="s">
+      <c r="C23" s="130" t="s">
         <v>73</v>
       </c>
-      <c r="D23" s="131" t="s">
+      <c r="D23" s="130" t="s">
         <v>91</v>
       </c>
-      <c r="E23" s="93" t="s">
+      <c r="E23" s="92" t="s">
         <v>106</v>
       </c>
-      <c r="F23" s="94">
+      <c r="F23" s="93">
         <v>5.44</v>
       </c>
-      <c r="G23" s="94">
+      <c r="G23" s="93">
         <v>0.48</v>
       </c>
-      <c r="H23" s="137">
+      <c r="H23" s="136">
         <v>0.09</v>
       </c>
-      <c r="I23" s="138">
+      <c r="I23" s="137">
         <f t="shared" si="3"/>
         <v>6.01</v>
       </c>
-      <c r="J23" s="95">
+      <c r="J23" s="94">
         <v>263186.31</v>
       </c>
-      <c r="K23" s="193">
+      <c r="K23" s="99">
         <v>244944.31</v>
       </c>
-      <c r="L23" s="118" t="s">
+      <c r="L23" s="117" t="s">
         <v>126</v>
       </c>
-      <c r="M23" s="124">
+      <c r="M23" s="123">
         <f t="shared" si="0"/>
         <v>18242</v>
       </c>
-      <c r="N23" s="160">
-        <v>0</v>
-      </c>
-      <c r="O23" s="96"/>
-      <c r="P23" s="97">
+      <c r="N23" s="159">
+        <v>0</v>
+      </c>
+      <c r="O23" s="95"/>
+      <c r="P23" s="96">
         <f t="shared" si="5"/>
-        <v>160996.50203500001</v>
-      </c>
-      <c r="Q23" s="98">
+        <v>250255.29115499998</v>
+      </c>
+      <c r="Q23" s="97">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="R23" s="159">
+        <v>199553.035</v>
+      </c>
+      <c r="R23" s="158">
         <f>K$2/18</f>
-        <v>102189.93055555556</v>
-      </c>
-      <c r="S23" s="157">
+        <v>0</v>
+      </c>
+      <c r="S23" s="156">
         <f t="shared" si="7"/>
-        <v>281428.31</v>
-      </c>
-      <c r="T23" s="139">
+        <v>468050.31</v>
+      </c>
+      <c r="T23" s="138">
         <f t="shared" si="1"/>
-        <v>289871.31</v>
-      </c>
-      <c r="U23" s="32">
+        <v>482092.31</v>
+      </c>
+      <c r="U23" s="31">
         <f t="shared" si="9"/>
         <v>0.31</v>
       </c>
     </row>
     <row r="24" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="155">
+      <c r="A24" s="154">
         <f t="shared" si="10"/>
         <v>32</v>
       </c>
-      <c r="B24" s="132"/>
-      <c r="C24" s="132"/>
-      <c r="D24" s="132" t="s">
+      <c r="B24" s="131"/>
+      <c r="C24" s="131"/>
+      <c r="D24" s="131" t="s">
         <v>92</v>
       </c>
-      <c r="E24" s="99" t="s">
+      <c r="E24" s="98" t="s">
         <v>107</v>
       </c>
-      <c r="F24" s="94">
+      <c r="F24" s="93">
         <v>2.87</v>
       </c>
-      <c r="G24" s="133"/>
-      <c r="H24" s="137"/>
-      <c r="I24" s="138">
+      <c r="G24" s="132"/>
+      <c r="H24" s="136"/>
+      <c r="I24" s="137">
         <f t="shared" si="3"/>
         <v>2.87</v>
       </c>
-      <c r="J24" s="100">
+      <c r="J24" s="99">
         <v>79187.320000000007</v>
       </c>
-      <c r="K24" s="193">
+      <c r="K24" s="99">
         <f>J24</f>
         <v>79187.320000000007</v>
       </c>
-      <c r="L24" s="118" t="s">
+      <c r="L24" s="117" t="s">
         <v>126</v>
       </c>
-      <c r="M24" s="124">
+      <c r="M24" s="123">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N24" s="160">
+      <c r="N24" s="159">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O24" s="96"/>
-      <c r="P24" s="97">
+      <c r="O24" s="95"/>
+      <c r="P24" s="96">
         <f t="shared" si="5"/>
-        <v>76881.857045000012</v>
-      </c>
-      <c r="Q24" s="98">
+        <v>119506.270485</v>
+      </c>
+      <c r="Q24" s="97">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="R24" s="98"/>
-      <c r="S24" s="157">
+        <v>95294.044999999998</v>
+      </c>
+      <c r="R24" s="97"/>
+      <c r="S24" s="156">
         <f t="shared" si="7"/>
-        <v>76882.320000000007</v>
-      </c>
-      <c r="T24" s="139">
+        <v>214800.32</v>
+      </c>
+      <c r="T24" s="138">
         <f t="shared" si="1"/>
-        <v>79188.320000000007</v>
-      </c>
-      <c r="U24" s="32">
+        <v>221244.32</v>
+      </c>
+      <c r="U24" s="31">
         <f t="shared" si="9"/>
         <v>0.32</v>
       </c>
@@ -4534,691 +4533,691 @@
       </c>
     </row>
     <row r="25" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="155">
+      <c r="A25" s="154">
         <f t="shared" si="10"/>
         <v>33</v>
       </c>
-      <c r="B25" s="131">
+      <c r="B25" s="130">
         <v>10</v>
       </c>
-      <c r="C25" s="131"/>
-      <c r="D25" s="131" t="s">
+      <c r="C25" s="130"/>
+      <c r="D25" s="130" t="s">
         <v>93</v>
       </c>
-      <c r="E25" s="93" t="s">
+      <c r="E25" s="92" t="s">
         <v>108</v>
       </c>
-      <c r="F25" s="94">
+      <c r="F25" s="93">
         <v>5.44</v>
       </c>
-      <c r="G25" s="94">
+      <c r="G25" s="93">
         <v>0.45</v>
       </c>
-      <c r="H25" s="137"/>
-      <c r="I25" s="138">
+      <c r="H25" s="136"/>
+      <c r="I25" s="137">
         <f t="shared" si="3"/>
         <v>5.8900000000000006</v>
       </c>
-      <c r="J25" s="95">
+      <c r="J25" s="94">
         <v>259972.33</v>
       </c>
-      <c r="K25" s="193">
+      <c r="K25" s="99">
         <f>J25</f>
         <v>259972.33</v>
       </c>
-      <c r="L25" s="118" t="s">
+      <c r="L25" s="117" t="s">
         <v>126</v>
       </c>
-      <c r="M25" s="124">
+      <c r="M25" s="123">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N25" s="160">
+      <c r="N25" s="159">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O25" s="96"/>
-      <c r="P25" s="97">
+      <c r="O25" s="95"/>
+      <c r="P25" s="96">
         <f t="shared" si="5"/>
-        <v>157781.92961500003</v>
-      </c>
-      <c r="Q25" s="98">
+        <v>245258.51329500001</v>
+      </c>
+      <c r="Q25" s="97">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="R25" s="159">
+        <v>195568.61500000005</v>
+      </c>
+      <c r="R25" s="158">
         <f>K$2/18</f>
-        <v>102189.93055555556</v>
-      </c>
-      <c r="S25" s="157">
+        <v>0</v>
+      </c>
+      <c r="S25" s="156">
         <f t="shared" si="7"/>
-        <v>259972.33</v>
-      </c>
-      <c r="T25" s="139">
+        <v>440827.33</v>
+      </c>
+      <c r="T25" s="138">
         <f t="shared" si="1"/>
-        <v>267771.32999999996</v>
-      </c>
-      <c r="U25" s="32">
+        <v>454052.33</v>
+      </c>
+      <c r="U25" s="31">
         <f t="shared" si="9"/>
         <v>0.33</v>
       </c>
     </row>
     <row r="26" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="155">
+      <c r="A26" s="154">
         <f t="shared" si="10"/>
         <v>34</v>
       </c>
-      <c r="B26" s="131"/>
-      <c r="C26" s="131"/>
-      <c r="D26" s="131" t="s">
+      <c r="B26" s="130"/>
+      <c r="C26" s="130"/>
+      <c r="D26" s="130" t="s">
         <v>94</v>
       </c>
-      <c r="E26" s="93" t="s">
+      <c r="E26" s="92" t="s">
         <v>109</v>
       </c>
-      <c r="F26" s="94">
+      <c r="F26" s="93">
         <v>2.87</v>
       </c>
-      <c r="G26" s="94"/>
-      <c r="H26" s="137"/>
-      <c r="I26" s="138">
+      <c r="G26" s="93"/>
+      <c r="H26" s="136"/>
+      <c r="I26" s="137">
         <f t="shared" si="3"/>
         <v>2.87</v>
       </c>
-      <c r="J26" s="100">
+      <c r="J26" s="99">
         <v>76882.34</v>
       </c>
-      <c r="K26" s="193">
+      <c r="K26" s="99">
         <v>99345.34</v>
       </c>
-      <c r="L26" s="118" t="s">
+      <c r="L26" s="117" t="s">
         <v>126</v>
       </c>
-      <c r="M26" s="124">
+      <c r="M26" s="123">
         <f t="shared" si="0"/>
         <v>-22463</v>
       </c>
-      <c r="N26" s="160">
+      <c r="N26" s="159">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O26" s="96"/>
-      <c r="P26" s="97">
+      <c r="O26" s="95"/>
+      <c r="P26" s="96">
         <f t="shared" si="5"/>
-        <v>76881.857045000012</v>
-      </c>
-      <c r="Q26" s="98">
+        <v>119506.270485</v>
+      </c>
+      <c r="Q26" s="97">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="R26" s="98"/>
-      <c r="S26" s="157">
+        <v>95294.044999999998</v>
+      </c>
+      <c r="R26" s="97"/>
+      <c r="S26" s="156">
         <f t="shared" si="7"/>
-        <v>54419.34</v>
-      </c>
-      <c r="T26" s="139">
+        <v>192337.34</v>
+      </c>
+      <c r="T26" s="138">
         <f t="shared" si="1"/>
-        <v>56052.34</v>
-      </c>
-      <c r="U26" s="32">
+        <v>198107.34</v>
+      </c>
+      <c r="U26" s="31">
         <f t="shared" si="9"/>
         <v>0.34</v>
       </c>
     </row>
     <row r="27" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="155">
+      <c r="A27" s="154">
         <f t="shared" si="10"/>
         <v>35</v>
       </c>
-      <c r="B27" s="131">
+      <c r="B27" s="130">
         <v>4</v>
       </c>
-      <c r="C27" s="131" t="s">
+      <c r="C27" s="130" t="s">
         <v>55</v>
       </c>
-      <c r="D27" s="232">
+      <c r="D27" s="218">
         <v>9</v>
       </c>
-      <c r="E27" s="232" t="s">
+      <c r="E27" s="218" t="s">
         <v>110</v>
       </c>
-      <c r="F27" s="136">
+      <c r="F27" s="135">
         <f>7.73/2</f>
         <v>3.8650000000000002</v>
       </c>
-      <c r="G27" s="151">
+      <c r="G27" s="150">
         <v>0.41</v>
       </c>
-      <c r="H27" s="137">
+      <c r="H27" s="136">
         <v>0.09</v>
       </c>
-      <c r="I27" s="138">
+      <c r="I27" s="137">
         <f t="shared" si="3"/>
         <v>4.3650000000000002</v>
       </c>
-      <c r="J27" s="95">
+      <c r="J27" s="94">
         <v>447977.35</v>
       </c>
-      <c r="K27" s="194">
+      <c r="K27" s="117">
         <f>J27</f>
         <v>447977.35</v>
       </c>
-      <c r="L27" s="118" t="s">
+      <c r="L27" s="117" t="s">
         <v>126</v>
       </c>
-      <c r="M27" s="124">
+      <c r="M27" s="123">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N27" s="160">
+      <c r="N27" s="159">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O27" s="96"/>
-      <c r="P27" s="97">
+      <c r="O27" s="95"/>
+      <c r="P27" s="96">
         <f t="shared" si="5"/>
-        <v>116930.07177750001</v>
-      </c>
-      <c r="Q27" s="98">
+        <v>181757.79465750002</v>
+      </c>
+      <c r="Q27" s="97">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="R27" s="159">
+        <v>144933.2775</v>
+      </c>
+      <c r="R27" s="158">
         <f t="shared" ref="R27:R33" si="11">K$2/18</f>
-        <v>102189.93055555556</v>
-      </c>
-      <c r="S27" s="139">
+        <v>0</v>
+      </c>
+      <c r="S27" s="138">
         <f>ROUND(SUM(M27:R27)+P28+Q28+R28,0) + U27</f>
-        <v>435829.35</v>
-      </c>
-      <c r="T27" s="139">
+        <v>646646.35</v>
+      </c>
+      <c r="T27" s="138">
         <f t="shared" si="1"/>
-        <v>448904.35</v>
-      </c>
-      <c r="U27" s="32">
+        <v>666045.35</v>
+      </c>
+      <c r="U27" s="31">
         <f t="shared" si="9"/>
         <v>0.35</v>
       </c>
     </row>
     <row r="28" spans="1:22" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="155" t="s">
+      <c r="A28" s="154" t="s">
         <v>71</v>
       </c>
-      <c r="B28" s="131">
+      <c r="B28" s="130">
         <v>5</v>
       </c>
-      <c r="C28" s="134"/>
-      <c r="D28" s="233"/>
-      <c r="E28" s="233"/>
-      <c r="F28" s="136">
+      <c r="C28" s="133"/>
+      <c r="D28" s="219"/>
+      <c r="E28" s="219"/>
+      <c r="F28" s="135">
         <f>7.73/2</f>
         <v>3.8650000000000002</v>
       </c>
-      <c r="G28" s="151">
+      <c r="G28" s="150">
         <v>0.41</v>
       </c>
-      <c r="H28" s="137"/>
-      <c r="I28" s="138">
+      <c r="H28" s="136"/>
+      <c r="I28" s="137">
         <f t="shared" si="3"/>
         <v>4.2750000000000004</v>
       </c>
-      <c r="J28" s="95">
-        <v>0</v>
-      </c>
-      <c r="K28" s="100">
+      <c r="J28" s="94">
+        <v>0</v>
+      </c>
+      <c r="K28" s="99">
         <f>J28</f>
         <v>0</v>
       </c>
-      <c r="L28" s="118" t="s">
+      <c r="L28" s="117" t="s">
         <v>126</v>
       </c>
-      <c r="M28" s="124">
+      <c r="M28" s="123">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N28" s="160">
+      <c r="N28" s="159">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O28" s="96"/>
-      <c r="P28" s="97">
+      <c r="O28" s="95"/>
+      <c r="P28" s="96">
         <f t="shared" si="5"/>
-        <v>114519.14246250002</v>
-      </c>
-      <c r="Q28" s="98">
+        <v>178010.21126250003</v>
+      </c>
+      <c r="Q28" s="97">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="R28" s="159">
+        <v>141944.96250000002</v>
+      </c>
+      <c r="R28" s="158">
         <f t="shared" si="11"/>
-        <v>102189.93055555556</v>
-      </c>
-      <c r="S28" s="139">
-        <v>0</v>
-      </c>
-      <c r="T28" s="139">
+        <v>0</v>
+      </c>
+      <c r="S28" s="138">
+        <v>0</v>
+      </c>
+      <c r="T28" s="138">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="U28" s="32"/>
+      <c r="U28" s="31"/>
     </row>
     <row r="29" spans="1:22" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="155">
+      <c r="A29" s="154">
         <v>36</v>
       </c>
-      <c r="B29" s="131">
+      <c r="B29" s="130">
         <v>2</v>
       </c>
-      <c r="C29" s="134" t="s">
+      <c r="C29" s="133" t="s">
         <v>45</v>
       </c>
-      <c r="D29" s="232">
+      <c r="D29" s="218">
         <v>10</v>
       </c>
-      <c r="E29" s="235" t="s">
+      <c r="E29" s="221" t="s">
         <v>111</v>
       </c>
-      <c r="F29" s="136">
+      <c r="F29" s="135">
         <f>7.73/2</f>
         <v>3.8650000000000002</v>
       </c>
-      <c r="G29" s="153">
+      <c r="G29" s="152">
         <v>0.45</v>
       </c>
-      <c r="H29" s="137">
+      <c r="H29" s="136">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="I29" s="138">
+      <c r="I29" s="137">
         <f t="shared" si="3"/>
         <v>4.3850000000000007</v>
       </c>
-      <c r="J29" s="101">
+      <c r="J29" s="100">
         <v>428596.36</v>
       </c>
-      <c r="K29" s="194">
+      <c r="K29" s="117">
         <f>84907.36+343689.36</f>
         <v>428596.72</v>
       </c>
-      <c r="L29" s="118" t="s">
+      <c r="L29" s="117" t="s">
         <v>126</v>
       </c>
-      <c r="M29" s="124">
+      <c r="M29" s="123">
         <f t="shared" si="0"/>
         <v>-0.35999999998603016</v>
       </c>
-      <c r="N29" s="160">
+      <c r="N29" s="159">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O29" s="96"/>
-      <c r="P29" s="97">
+      <c r="O29" s="95"/>
+      <c r="P29" s="96">
         <f t="shared" si="5"/>
-        <v>117465.83384750003</v>
-      </c>
-      <c r="Q29" s="98">
+        <v>182590.59096750003</v>
+      </c>
+      <c r="Q29" s="97">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="R29" s="159">
+        <v>145597.34750000003</v>
+      </c>
+      <c r="R29" s="158">
         <f t="shared" si="11"/>
-        <v>102189.93055555556</v>
-      </c>
-      <c r="S29" s="139">
+        <v>0</v>
+      </c>
+      <c r="S29" s="138">
         <f>ROUND(SUM(M29:R29)+P30+Q30+R30,0) + U29</f>
-        <v>428596.36</v>
-      </c>
-      <c r="T29" s="139">
+        <v>626438.36</v>
+      </c>
+      <c r="T29" s="138">
         <f t="shared" si="1"/>
-        <v>441454.36</v>
-      </c>
-      <c r="U29" s="32">
+        <v>645231.35999999999</v>
+      </c>
+      <c r="U29" s="31">
         <f>A29/100</f>
         <v>0.36</v>
       </c>
     </row>
     <row r="30" spans="1:22" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="155" t="s">
+      <c r="A30" s="154" t="s">
         <v>71</v>
       </c>
-      <c r="B30" s="131">
+      <c r="B30" s="130">
         <v>18</v>
       </c>
-      <c r="C30" s="134"/>
-      <c r="D30" s="233"/>
-      <c r="E30" s="236"/>
-      <c r="F30" s="136">
+      <c r="C30" s="133"/>
+      <c r="D30" s="219"/>
+      <c r="E30" s="222"/>
+      <c r="F30" s="135">
         <f>7.73/2</f>
         <v>3.8650000000000002</v>
       </c>
-      <c r="G30" s="154">
+      <c r="G30" s="153">
         <v>0.12</v>
       </c>
-      <c r="H30" s="137"/>
-      <c r="I30" s="138">
+      <c r="H30" s="136"/>
+      <c r="I30" s="137">
         <f t="shared" si="3"/>
         <v>3.9850000000000003</v>
       </c>
-      <c r="J30" s="101">
-        <v>0</v>
-      </c>
-      <c r="K30" s="118">
+      <c r="J30" s="100">
+        <v>0</v>
+      </c>
+      <c r="K30" s="117">
         <f>J30</f>
         <v>0</v>
       </c>
-      <c r="L30" s="118" t="s">
+      <c r="L30" s="117" t="s">
         <v>126</v>
       </c>
-      <c r="M30" s="124">
+      <c r="M30" s="123">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N30" s="160">
+      <c r="N30" s="159">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O30" s="96"/>
-      <c r="P30" s="97">
+      <c r="O30" s="95"/>
+      <c r="P30" s="96">
         <f t="shared" si="5"/>
-        <v>106750.59244750001</v>
-      </c>
-      <c r="Q30" s="98">
+        <v>165934.66476750001</v>
+      </c>
+      <c r="Q30" s="97">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="R30" s="159">
+        <v>132315.94750000001</v>
+      </c>
+      <c r="R30" s="158">
         <f t="shared" si="11"/>
-        <v>102189.93055555556</v>
-      </c>
-      <c r="S30" s="139">
-        <v>0</v>
-      </c>
-      <c r="T30" s="139">
+        <v>0</v>
+      </c>
+      <c r="S30" s="138">
+        <v>0</v>
+      </c>
+      <c r="T30" s="138">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="U30" s="32"/>
+      <c r="U30" s="31"/>
     </row>
     <row r="31" spans="1:22" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="155">
+      <c r="A31" s="154">
         <v>37</v>
       </c>
-      <c r="B31" s="131">
+      <c r="B31" s="130">
         <v>12</v>
       </c>
-      <c r="C31" s="134" t="s">
+      <c r="C31" s="133" t="s">
         <v>76</v>
       </c>
-      <c r="D31" s="232" t="s">
+      <c r="D31" s="218" t="s">
         <v>95</v>
       </c>
-      <c r="E31" s="232" t="s">
+      <c r="E31" s="218" t="s">
         <v>112</v>
       </c>
-      <c r="F31" s="136">
+      <c r="F31" s="135">
         <f>12.13/3</f>
         <v>4.0433333333333339</v>
       </c>
-      <c r="G31" s="131">
+      <c r="G31" s="130">
         <v>0.12</v>
       </c>
-      <c r="H31" s="137">
+      <c r="H31" s="136">
         <v>0.09</v>
       </c>
-      <c r="I31" s="138">
+      <c r="I31" s="137">
         <f t="shared" si="3"/>
         <v>4.2533333333333339</v>
       </c>
-      <c r="J31" s="101">
+      <c r="J31" s="100">
         <v>651333.37</v>
       </c>
-      <c r="K31" s="194">
+      <c r="K31" s="117">
         <v>528133.37</v>
       </c>
-      <c r="L31" s="118" t="s">
+      <c r="L31" s="117" t="s">
         <v>126</v>
       </c>
-      <c r="M31" s="124">
+      <c r="M31" s="123">
         <f t="shared" si="0"/>
         <v>123200</v>
       </c>
-      <c r="N31" s="160">
-        <v>0</v>
-      </c>
-      <c r="O31" s="96"/>
-      <c r="P31" s="97">
+      <c r="N31" s="159">
+        <v>0</v>
+      </c>
+      <c r="O31" s="95"/>
+      <c r="P31" s="96">
         <f t="shared" si="5"/>
-        <v>113938.73355333335</v>
-      </c>
-      <c r="Q31" s="98">
+        <v>177108.01526000001</v>
+      </c>
+      <c r="Q31" s="97">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="R31" s="159">
+        <v>141225.55333333334</v>
+      </c>
+      <c r="R31" s="158">
         <f t="shared" si="11"/>
-        <v>102189.93055555556</v>
-      </c>
-      <c r="S31" s="139">
+        <v>0</v>
+      </c>
+      <c r="S31" s="138">
         <f>ROUND(SUM(M31:R31)+P32+P33+Q32+Q33+R32+R33,0) + U31</f>
-        <v>774533.37</v>
-      </c>
-      <c r="T31" s="139">
+        <v>1086433.3700000001</v>
+      </c>
+      <c r="T31" s="138">
         <f t="shared" si="1"/>
-        <v>797769.37</v>
-      </c>
-      <c r="U31" s="32">
+        <v>1119026.3700000001</v>
+      </c>
+      <c r="U31" s="31">
         <f>A31/100</f>
         <v>0.37</v>
       </c>
     </row>
     <row r="32" spans="1:22" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="155" t="s">
+      <c r="A32" s="154" t="s">
         <v>71</v>
       </c>
-      <c r="B32" s="131">
+      <c r="B32" s="130">
         <v>3</v>
       </c>
-      <c r="C32" s="135"/>
-      <c r="D32" s="234"/>
-      <c r="E32" s="234"/>
-      <c r="F32" s="136">
+      <c r="C32" s="134"/>
+      <c r="D32" s="220"/>
+      <c r="E32" s="220"/>
+      <c r="F32" s="135">
         <f>12.13/3</f>
         <v>4.0433333333333339</v>
       </c>
-      <c r="G32" s="131">
+      <c r="G32" s="130">
         <v>0.41</v>
       </c>
-      <c r="H32" s="137"/>
-      <c r="I32" s="138">
+      <c r="H32" s="136"/>
+      <c r="I32" s="137">
         <f t="shared" si="3"/>
         <v>4.453333333333334</v>
       </c>
-      <c r="J32" s="101">
-        <v>0</v>
-      </c>
-      <c r="K32" s="118"/>
-      <c r="L32" s="118"/>
-      <c r="M32" s="124">
+      <c r="J32" s="100">
+        <v>0</v>
+      </c>
+      <c r="K32" s="117"/>
+      <c r="L32" s="117"/>
+      <c r="M32" s="123">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N32" s="160">
+      <c r="N32" s="159">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O32" s="96"/>
-      <c r="P32" s="97">
+      <c r="O32" s="95"/>
+      <c r="P32" s="96">
         <f t="shared" si="5"/>
-        <v>119296.35425333335</v>
-      </c>
-      <c r="Q32" s="98">
+        <v>185435.97836000004</v>
+      </c>
+      <c r="Q32" s="97">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="R32" s="159">
+        <v>147866.25333333336</v>
+      </c>
+      <c r="R32" s="158">
         <f t="shared" si="11"/>
-        <v>102189.93055555556</v>
-      </c>
-      <c r="S32" s="139">
-        <v>0</v>
-      </c>
-      <c r="T32" s="139">
+        <v>0</v>
+      </c>
+      <c r="S32" s="138">
+        <v>0</v>
+      </c>
+      <c r="T32" s="138">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="U32" s="32"/>
+      <c r="U32" s="31"/>
     </row>
     <row r="33" spans="1:21" ht="14.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="171" t="s">
+      <c r="A33" s="170" t="s">
         <v>71</v>
       </c>
-      <c r="B33" s="151">
+      <c r="B33" s="150">
         <v>16</v>
       </c>
-      <c r="C33" s="135"/>
-      <c r="D33" s="234"/>
-      <c r="E33" s="234"/>
-      <c r="F33" s="136">
+      <c r="C33" s="134"/>
+      <c r="D33" s="220"/>
+      <c r="E33" s="220"/>
+      <c r="F33" s="135">
         <f>12.13/3</f>
         <v>4.0433333333333339</v>
       </c>
-      <c r="G33" s="151">
+      <c r="G33" s="150">
         <v>0.12</v>
       </c>
-      <c r="H33" s="172"/>
-      <c r="I33" s="173">
+      <c r="H33" s="171"/>
+      <c r="I33" s="172">
         <f t="shared" si="3"/>
         <v>4.163333333333334</v>
       </c>
-      <c r="J33" s="101">
-        <v>0</v>
-      </c>
-      <c r="K33" s="118"/>
-      <c r="L33" s="118"/>
-      <c r="M33" s="174">
+      <c r="J33" s="100">
+        <v>0</v>
+      </c>
+      <c r="K33" s="117"/>
+      <c r="L33" s="117"/>
+      <c r="M33" s="173">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="N33" s="175">
+      <c r="N33" s="174">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="O33" s="176"/>
-      <c r="P33" s="177">
+      <c r="O33" s="175"/>
+      <c r="P33" s="176">
         <f t="shared" si="5"/>
-        <v>111527.80423833335</v>
-      </c>
-      <c r="Q33" s="178">
+        <v>173360.43186500002</v>
+      </c>
+      <c r="Q33" s="177">
         <f t="shared" si="6"/>
-        <v>0</v>
-      </c>
-      <c r="R33" s="185">
+        <v>138237.23833333337</v>
+      </c>
+      <c r="R33" s="184">
         <f t="shared" si="11"/>
-        <v>102189.93055555556</v>
-      </c>
-      <c r="S33" s="179">
-        <v>0</v>
-      </c>
-      <c r="T33" s="179">
+        <v>0</v>
+      </c>
+      <c r="S33" s="178">
+        <v>0</v>
+      </c>
+      <c r="T33" s="178">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="U33" s="32"/>
+      <c r="U33" s="31"/>
     </row>
     <row r="34" spans="1:21" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="229" t="s">
+      <c r="A34" s="213" t="s">
         <v>44</v>
       </c>
-      <c r="B34" s="230"/>
-      <c r="C34" s="230"/>
-      <c r="D34" s="230"/>
-      <c r="E34" s="231"/>
-      <c r="F34" s="180"/>
-      <c r="G34" s="180"/>
-      <c r="H34" s="181">
+      <c r="B34" s="214"/>
+      <c r="C34" s="214"/>
+      <c r="D34" s="214"/>
+      <c r="E34" s="215"/>
+      <c r="F34" s="179"/>
+      <c r="G34" s="179"/>
+      <c r="H34" s="180">
         <f t="shared" ref="H34:N34" si="12">SUM(H10:H33)</f>
         <v>0.52</v>
       </c>
-      <c r="I34" s="181">
+      <c r="I34" s="180">
         <f t="shared" si="12"/>
         <v>100</v>
       </c>
-      <c r="J34" s="182">
+      <c r="J34" s="181">
         <f t="shared" si="12"/>
         <v>4513859.5599999996</v>
       </c>
-      <c r="K34" s="182">
+      <c r="K34" s="181">
         <f>SUM(K10:K33)</f>
-        <v>3916821.1900000004</v>
-      </c>
-      <c r="L34" s="182"/>
-      <c r="M34" s="182">
+        <v>4141479.4400000004</v>
+      </c>
+      <c r="L34" s="181"/>
+      <c r="M34" s="181">
         <f t="shared" si="12"/>
-        <v>597038.37000000011</v>
-      </c>
-      <c r="N34" s="182">
+        <v>372380.12000000005</v>
+      </c>
+      <c r="N34" s="181">
         <f t="shared" si="12"/>
-        <v>9844.4892</v>
-      </c>
-      <c r="O34" s="183"/>
-      <c r="P34" s="183">
+        <v>5351.3242000000009</v>
+      </c>
+      <c r="O34" s="182"/>
+      <c r="P34" s="182">
         <f>SUM(P10:P33)</f>
-        <v>2678810.35</v>
-      </c>
-      <c r="Q34" s="184">
+        <v>4163981.5500000007</v>
+      </c>
+      <c r="Q34" s="183">
         <f>SUM(Q10:Q33)</f>
-        <v>0</v>
-      </c>
-      <c r="R34" s="186">
+        <v>3320350</v>
+      </c>
+      <c r="R34" s="185">
         <f>SUM(R10:R33)</f>
-        <v>1839418.7499999995</v>
-      </c>
-      <c r="S34" s="182">
+        <v>0</v>
+      </c>
+      <c r="S34" s="181">
         <f>SUM(S10:S31)</f>
-        <v>5125118.5599999996</v>
-      </c>
-      <c r="T34" s="182">
+        <v>7862066.5599999996</v>
+      </c>
+      <c r="T34" s="181">
         <f>SUM(T10:T31)</f>
-        <v>5278872.5599999996</v>
+        <v>8097928.5599999996</v>
       </c>
     </row>
     <row r="35" spans="1:21" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="E35" s="38"/>
-      <c r="F35" s="38"/>
-      <c r="G35" s="38"/>
-      <c r="K35" s="103" t="s">
+      <c r="E35" s="37"/>
+      <c r="F35" s="37"/>
+      <c r="G35" s="37"/>
+      <c r="K35" s="102" t="s">
         <v>127</v>
       </c>
-      <c r="L35" s="103">
+      <c r="L35" s="102">
         <f>SUMIF(L10:L33,"B",K10:K33)</f>
-        <v>3698520.92</v>
+        <v>3923179.17</v>
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A36" s="239"/>
-      <c r="B36" s="239"/>
-      <c r="C36" s="129"/>
-      <c r="D36" s="129"/>
-      <c r="H36" s="240"/>
-      <c r="I36" s="130"/>
-      <c r="J36" s="241"/>
-      <c r="K36" s="103" t="s">
+      <c r="A36" s="209"/>
+      <c r="B36" s="209"/>
+      <c r="C36" s="128"/>
+      <c r="D36" s="128"/>
+      <c r="H36" s="210"/>
+      <c r="I36" s="129"/>
+      <c r="J36" s="211"/>
+      <c r="K36" s="102" t="s">
         <v>117</v>
       </c>
-      <c r="L36" s="103">
+      <c r="L36" s="102">
         <f>SUMIF(L10:L33,"E",K10:K33)</f>
         <v>218300.27</v>
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A37" s="239"/>
-      <c r="B37" s="239"/>
-      <c r="C37" s="129"/>
-      <c r="D37" s="129"/>
-      <c r="H37" s="240"/>
-      <c r="I37" s="130"/>
-      <c r="J37" s="241"/>
-      <c r="K37" s="104"/>
-      <c r="L37" s="104"/>
+      <c r="A37" s="209"/>
+      <c r="B37" s="209"/>
+      <c r="C37" s="128"/>
+      <c r="D37" s="128"/>
+      <c r="H37" s="210"/>
+      <c r="I37" s="129"/>
+      <c r="J37" s="211"/>
+      <c r="K37" s="103"/>
+      <c r="L37" s="103"/>
     </row>
     <row r="48" spans="1:21" x14ac:dyDescent="0.25">
       <c r="J48">
@@ -5244,23 +5243,6 @@
     </row>
   </sheetData>
   <mergeCells count="33">
-    <mergeCell ref="R8:R9"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="A36:B37"/>
-    <mergeCell ref="H36:H37"/>
-    <mergeCell ref="J36:J37"/>
-    <mergeCell ref="K2:M2"/>
-    <mergeCell ref="A34:E34"/>
-    <mergeCell ref="O8:O9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="D31:D33"/>
-    <mergeCell ref="E31:E33"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="E27:E28"/>
-    <mergeCell ref="F2:G2"/>
     <mergeCell ref="H1:S1"/>
     <mergeCell ref="N8:N9"/>
     <mergeCell ref="J8:J9"/>
@@ -5277,6 +5259,23 @@
     <mergeCell ref="C8:C9"/>
     <mergeCell ref="D8:D9"/>
     <mergeCell ref="Q2:S2"/>
+    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="D31:D33"/>
+    <mergeCell ref="E31:E33"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="E27:E28"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="R8:R9"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="A36:B37"/>
+    <mergeCell ref="H36:H37"/>
+    <mergeCell ref="J36:J37"/>
   </mergeCells>
   <phoneticPr fontId="21" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/2026/BRIN 2970/Agosto/Agosto-BRIN2970.xlsx
+++ b/2026/BRIN 2970/Agosto/Agosto-BRIN2970.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\BRIN 2970\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1FB03BC1-DC23-44BE-8CE1-FC4AFBDBC610}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83DB27F4-B11A-40C0-9EF0-EA29D0723207}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="850" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="850" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="1">PRORRATEO!$A$1:$T$34</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$117</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$118</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
   <extLst>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="164">
   <si>
     <t>LIQUIDACION DE EXPENSAS</t>
   </si>
@@ -204,9 +204,6 @@
     <t>Particular</t>
   </si>
   <si>
-    <t xml:space="preserve">PREVISION EXTRAORDINARIA </t>
-  </si>
-  <si>
     <t>PREVISION ORDINARIA</t>
   </si>
   <si>
@@ -429,9 +426,6 @@
     <t>Rubinetti Agostina</t>
   </si>
   <si>
-    <t>SALDO EN BANCO AL 26/06</t>
-  </si>
-  <si>
     <t>GASTOS UNIDADES COMPLEMENTARIAS:</t>
   </si>
   <si>
@@ -450,9 +444,6 @@
     <t>MAIL: consorciobrin2970@gmail.com</t>
   </si>
   <si>
-    <t>PAGO DE EXPENSAS BANCO COMAFI - SUCURSAL LANUS - CTA. CTE. Nº 0090-01284-4 "CONSORCIO MINISTRO BRIN 2970" CBU   2990 0093 0090 0128 4400 08 CUIT: 30-71424193-8</t>
-  </si>
-  <si>
     <t>VTO 17/09</t>
   </si>
   <si>
@@ -492,9 +483,6 @@
     <t>Transf 31/08</t>
   </si>
   <si>
-    <t>SA Seguridad - Presupuesto nro. 17753 - Colocacion de motor a cadena para porton guillotina - Mano de obra, instalacion - Automatizacion porton</t>
-  </si>
-  <si>
     <t>Mes de junio</t>
   </si>
   <si>
@@ -520,6 +508,21 @@
   </si>
   <si>
     <t>El 5A, 6A, 7A y dptoo 11/12 Deben recibir una quita de punitorios, ya que pagaron el monto de prorrateo indebido por un error en el importe del primer archivo emitido como pdf, luego se volvio a emitir otro prorrateo con distintos montos pero ellos ya habian pagado</t>
+  </si>
+  <si>
+    <t>PAGO DE EXPENSAS BANCO COMAFI - Banco: Santander - Titular: CDP ED MTRO BRIN 2970 DE LANÚS -  CUIT: 30-71424193-8 - Cuenta: CC 533-033564/1 - CBU: 0720533020000003356418 -  Alias: BANDERA.PALTA.BALDE</t>
+  </si>
+  <si>
+    <t>SA Seguridad - Presupuesto nro. 17753 - Colocacion de motor a cadena para porton guillotina - Mano de obra, instalacion - Automatizacion porton - Cuota 1 de 2</t>
+  </si>
+  <si>
+    <t>Pago efectivo</t>
+  </si>
+  <si>
+    <t>PREVISION EXTRAORDINARIA  - PINTURA FRENTE Y CONTRAFRENTE</t>
+  </si>
+  <si>
+    <t>SALDO INICIAL</t>
   </si>
 </sst>
 </file>
@@ -1544,6 +1547,33 @@
     <xf numFmtId="44" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1556,12 +1586,6 @@
     <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1574,23 +1598,80 @@
     <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="3" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1598,12 +1679,6 @@
     <xf numFmtId="0" fontId="13" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1612,78 +1687,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="2" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -2083,7 +2086,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M121"/>
+  <dimension ref="A1:M122"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="37.5703125" customWidth="1"/>
@@ -2100,17 +2103,17 @@
   <sheetData>
     <row r="1" spans="1:5" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="13"/>
-      <c r="B1" s="192" t="s">
-        <v>138</v>
-      </c>
-      <c r="C1" s="192"/>
-      <c r="D1" s="192"/>
+      <c r="B1" s="201" t="s">
+        <v>136</v>
+      </c>
+      <c r="C1" s="201"/>
+      <c r="D1" s="201"/>
       <c r="E1" s="46"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="14"/>
       <c r="B2" s="47" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C2" s="47"/>
       <c r="D2" s="47"/>
@@ -2118,12 +2121,12 @@
     </row>
     <row r="3" spans="1:5" ht="70.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="14"/>
-      <c r="B3" s="195" t="s">
-        <v>139</v>
-      </c>
-      <c r="C3" s="195"/>
-      <c r="D3" s="195"/>
-      <c r="E3" s="196"/>
+      <c r="B3" s="202" t="s">
+        <v>159</v>
+      </c>
+      <c r="C3" s="202"/>
+      <c r="D3" s="202"/>
+      <c r="E3" s="203"/>
     </row>
     <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="17" t="s">
@@ -2138,10 +2141,10 @@
     </row>
     <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="14" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B5" s="18" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="C5" s="15"/>
       <c r="D5" s="47" t="s">
@@ -2151,7 +2154,7 @@
     </row>
     <row r="6" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="17" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B6" s="18"/>
       <c r="C6" s="18"/>
@@ -2161,49 +2164,49 @@
       <c r="E6" s="19"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="198" t="s">
-        <v>140</v>
-      </c>
-      <c r="C8" s="198"/>
+      <c r="B8" s="205" t="s">
+        <v>137</v>
+      </c>
+      <c r="C8" s="205"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="198"/>
-      <c r="C9" s="198"/>
+      <c r="B9" s="205"/>
+      <c r="C9" s="205"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="198"/>
-      <c r="C10" s="198"/>
+      <c r="B10" s="205"/>
+      <c r="C10" s="205"/>
     </row>
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="197" t="s">
+      <c r="A13" s="204" t="s">
         <v>46</v>
       </c>
-      <c r="B13" s="197"/>
-      <c r="C13" s="197"/>
-      <c r="D13" s="197"/>
-      <c r="E13" s="197"/>
+      <c r="B13" s="204"/>
+      <c r="C13" s="204"/>
+      <c r="D13" s="204"/>
+      <c r="E13" s="204"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="197"/>
-      <c r="B14" s="197"/>
-      <c r="C14" s="197"/>
-      <c r="D14" s="197"/>
-      <c r="E14" s="197"/>
+      <c r="A14" s="204"/>
+      <c r="B14" s="204"/>
+      <c r="C14" s="204"/>
+      <c r="D14" s="204"/>
+      <c r="E14" s="204"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="197"/>
-      <c r="B15" s="197"/>
-      <c r="C15" s="197"/>
-      <c r="D15" s="197"/>
-      <c r="E15" s="197"/>
+      <c r="A15" s="204"/>
+      <c r="B15" s="204"/>
+      <c r="C15" s="204"/>
+      <c r="D15" s="204"/>
+      <c r="E15" s="204"/>
     </row>
     <row r="16" spans="1:5" ht="127.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="197"/>
-      <c r="B16" s="197"/>
-      <c r="C16" s="197"/>
-      <c r="D16" s="197"/>
-      <c r="E16" s="197"/>
+      <c r="A16" s="204"/>
+      <c r="B16" s="204"/>
+      <c r="C16" s="204"/>
+      <c r="D16" s="204"/>
+      <c r="E16" s="204"/>
     </row>
     <row r="17" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D17" s="62"/>
@@ -2235,7 +2238,7 @@
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="52" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B22" s="5"/>
       <c r="C22" s="5"/>
@@ -2344,23 +2347,23 @@
       <c r="E32" s="81"/>
     </row>
     <row r="33" spans="1:7" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="193" t="s">
-        <v>161</v>
-      </c>
-      <c r="B33" s="194"/>
+      <c r="A33" s="194" t="s">
+        <v>157</v>
+      </c>
+      <c r="B33" s="195"/>
       <c r="C33" s="39"/>
       <c r="D33" s="107">
         <v>100000</v>
       </c>
       <c r="E33" s="82" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="34" spans="1:7" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="193" t="s">
-        <v>63</v>
-      </c>
-      <c r="B34" s="194"/>
+      <c r="A34" s="194" t="s">
+        <v>62</v>
+      </c>
+      <c r="B34" s="195"/>
       <c r="C34" s="39"/>
       <c r="D34" s="125">
         <v>0</v>
@@ -2389,29 +2392,29 @@
       <c r="E36" s="84"/>
     </row>
     <row r="37" spans="1:7" s="28" customFormat="1" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="191" t="s">
-        <v>64</v>
-      </c>
-      <c r="B37" s="191"/>
+      <c r="A37" s="200" t="s">
+        <v>63</v>
+      </c>
+      <c r="B37" s="200"/>
       <c r="C37" s="40"/>
-      <c r="D37" s="235">
+      <c r="D37" s="189">
         <v>44249</v>
       </c>
       <c r="E37" s="140" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="141" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B38" s="142"/>
       <c r="C38" s="40"/>
-      <c r="D38" s="235">
+      <c r="D38" s="189">
         <v>4406</v>
       </c>
       <c r="E38" s="146" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="39" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2440,14 +2443,14 @@
         <v>33</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="C41" s="39"/>
       <c r="D41" s="112">
         <v>839936.9</v>
       </c>
       <c r="E41" s="88" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="G41" s="70"/>
     </row>
@@ -2456,20 +2459,20 @@
         <v>33</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="C42" s="39"/>
       <c r="D42" s="112">
         <v>518193.32</v>
       </c>
       <c r="E42" s="88" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="G42" s="70"/>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>53</v>
@@ -2479,7 +2482,7 @@
         <v>84552.82</v>
       </c>
       <c r="E43" s="88" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.25">
@@ -2539,7 +2542,7 @@
     </row>
     <row r="48" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="52" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B48" s="5"/>
       <c r="C48" s="5"/>
@@ -2547,12 +2550,12 @@
         <v>334964.3</v>
       </c>
       <c r="E48" s="88" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="49" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="144" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B49" s="101"/>
       <c r="C49" s="5"/>
@@ -2563,7 +2566,7 @@
     </row>
     <row r="50" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="144" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B50" s="101"/>
       <c r="C50" s="5"/>
@@ -2571,7 +2574,7 @@
         <v>783602.88</v>
       </c>
       <c r="E50" s="104" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="51" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
@@ -2595,7 +2598,7 @@
     </row>
     <row r="53" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="139" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B53" s="145"/>
       <c r="C53" s="5"/>
@@ -2606,7 +2609,7 @@
     </row>
     <row r="54" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="139" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B54" s="187"/>
       <c r="C54" s="5"/>
@@ -2614,164 +2617,164 @@
         <v>48746</v>
       </c>
       <c r="E54" s="104" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="55" spans="1:5" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="189" t="s">
-        <v>149</v>
-      </c>
-      <c r="B55" s="190"/>
+      <c r="A55" s="198" t="s">
+        <v>146</v>
+      </c>
+      <c r="B55" s="199"/>
       <c r="C55" s="5"/>
       <c r="D55" s="112">
         <v>330000</v>
       </c>
       <c r="E55" s="104" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="139" t="s">
-        <v>151</v>
-      </c>
-      <c r="B56" s="145"/>
+        <v>142</v>
+      </c>
+    </row>
+    <row r="56" spans="1:5" ht="43.15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="192" t="s">
+        <v>160</v>
+      </c>
+      <c r="B56" s="193"/>
       <c r="C56" s="5"/>
       <c r="D56" s="112">
-        <v>81000</v>
+        <f>3320350/2</f>
+        <v>1660175</v>
       </c>
       <c r="E56" s="104" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="189" t="s">
-        <v>150</v>
-      </c>
-      <c r="B57" s="190"/>
+        <v>161</v>
+      </c>
+    </row>
+    <row r="57" spans="1:5" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A57" s="139" t="s">
+        <v>148</v>
+      </c>
+      <c r="B57" s="145"/>
       <c r="C57" s="5"/>
       <c r="D57" s="112">
+        <v>81000</v>
+      </c>
+      <c r="E57" s="104" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="58" spans="1:5" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A58" s="198" t="s">
+        <v>147</v>
+      </c>
+      <c r="B58" s="199"/>
+      <c r="C58" s="5"/>
+      <c r="D58" s="112">
         <v>95700</v>
       </c>
-      <c r="E57" s="104" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="22" t="s">
+      <c r="E58" s="104" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="59" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="B58" s="25"/>
-      <c r="C58" s="25"/>
-      <c r="D58" s="24"/>
-      <c r="E58" s="115">
-        <f>SUM(D53:D57)</f>
-        <v>555446</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="25" t="s">
+      <c r="B59" s="25"/>
+      <c r="C59" s="25"/>
+      <c r="D59" s="24"/>
+      <c r="E59" s="115">
+        <f>SUM(D53:D58)</f>
+        <v>2215621</v>
+      </c>
+    </row>
+    <row r="60" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="B59" s="44"/>
-      <c r="C59" s="22"/>
-      <c r="D59" s="110"/>
-      <c r="E59" s="86"/>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B60" s="5"/>
-      <c r="C60" s="5"/>
-      <c r="D60" s="112">
-        <v>0</v>
-      </c>
-      <c r="E60" s="87"/>
+      <c r="B60" s="44"/>
+      <c r="C60" s="22"/>
+      <c r="D60" s="110"/>
+      <c r="E60" s="86"/>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B61" s="5"/>
       <c r="C61" s="5"/>
       <c r="D61" s="112">
+        <v>0</v>
+      </c>
+      <c r="E61" s="87"/>
+    </row>
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A62" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B62" s="5"/>
+      <c r="C62" s="5"/>
+      <c r="D62" s="112">
         <f>6403.5+74344.13</f>
         <v>80747.63</v>
       </c>
-      <c r="E61" s="29"/>
-    </row>
-    <row r="62" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="38" t="s">
+      <c r="E62" s="29"/>
+    </row>
+    <row r="63" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="B62" s="38"/>
-      <c r="C62" s="38"/>
-      <c r="D62" s="58"/>
-      <c r="E62" s="53">
-        <f>SUM(D60:D61)</f>
+      <c r="B63" s="38"/>
+      <c r="C63" s="38"/>
+      <c r="D63" s="58"/>
+      <c r="E63" s="53">
+        <f>SUM(D61:D62)</f>
         <v>80747.63</v>
       </c>
     </row>
-    <row r="63" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="5"/>
-      <c r="B63" s="5"/>
-      <c r="C63" s="5"/>
-      <c r="D63" s="52"/>
-      <c r="E63" s="59"/>
-    </row>
     <row r="64" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="23" t="s">
-        <v>58</v>
-      </c>
-      <c r="B64" s="23"/>
-      <c r="C64" s="23"/>
-      <c r="D64" s="60"/>
-      <c r="E64" s="61">
-        <v>0</v>
-      </c>
+      <c r="A64" s="5"/>
+      <c r="B64" s="5"/>
+      <c r="C64" s="5"/>
+      <c r="D64" s="52"/>
+      <c r="E64" s="59"/>
     </row>
     <row r="65" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="1"/>
-      <c r="D65" s="62"/>
-      <c r="E65" s="63"/>
-      <c r="F65" s="31"/>
+      <c r="A65" s="23" t="s">
+        <v>57</v>
+      </c>
+      <c r="B65" s="23"/>
+      <c r="C65" s="23"/>
+      <c r="D65" s="60"/>
+      <c r="E65" s="61">
+        <v>0</v>
+      </c>
     </row>
     <row r="66" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A66" s="3" t="s">
+      <c r="A66" s="1"/>
+      <c r="D66" s="62"/>
+      <c r="E66" s="63"/>
+      <c r="F66" s="31"/>
+    </row>
+    <row r="67" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B66" s="8"/>
-      <c r="C66" s="4"/>
-      <c r="D66" s="64"/>
-      <c r="E66" s="65">
-        <f>(SUM(E28:E64))</f>
-        <v>4163981.55</v>
-      </c>
-      <c r="F66" s="78"/>
-      <c r="G66" s="31"/>
-      <c r="H66" s="70"/>
-      <c r="I66" s="70"/>
-      <c r="J66" s="70"/>
-      <c r="K66" s="70"/>
-      <c r="L66" s="70"/>
-    </row>
-    <row r="67" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D67" s="62"/>
-      <c r="E67" s="62"/>
+      <c r="B67" s="8"/>
+      <c r="C67" s="4"/>
+      <c r="D67" s="64"/>
+      <c r="E67" s="65">
+        <f>(SUM(E28:E65))</f>
+        <v>5824156.5499999998</v>
+      </c>
+      <c r="F67" s="78"/>
+      <c r="G67" s="31"/>
       <c r="H67" s="70"/>
       <c r="I67" s="70"/>
       <c r="J67" s="70"/>
       <c r="K67" s="70"/>
       <c r="L67" s="70"/>
     </row>
-    <row r="68" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A68" s="9" t="s">
-        <v>133</v>
-      </c>
-      <c r="B68" s="10"/>
-      <c r="C68" s="11"/>
-      <c r="D68" s="66"/>
-      <c r="E68" s="67"/>
+    <row r="68" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D68" s="62"/>
+      <c r="E68" s="62"/>
       <c r="H68" s="70"/>
       <c r="I68" s="70"/>
       <c r="J68" s="70"/>
@@ -2779,11 +2782,13 @@
       <c r="L68" s="70"/>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A69" s="203"/>
-      <c r="B69" s="204"/>
-      <c r="C69" s="5"/>
-      <c r="D69" s="112"/>
-      <c r="E69" s="104"/>
+      <c r="A69" s="9" t="s">
+        <v>131</v>
+      </c>
+      <c r="B69" s="10"/>
+      <c r="C69" s="11"/>
+      <c r="D69" s="66"/>
+      <c r="E69" s="67"/>
       <c r="H69" s="70"/>
       <c r="I69" s="70"/>
       <c r="J69" s="70"/>
@@ -2791,11 +2796,11 @@
       <c r="L69" s="70"/>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A70" s="203"/>
-      <c r="B70" s="204"/>
+      <c r="A70" s="196"/>
+      <c r="B70" s="197"/>
       <c r="C70" s="5"/>
       <c r="D70" s="112"/>
-      <c r="E70" s="54"/>
+      <c r="E70" s="104"/>
       <c r="H70" s="70"/>
       <c r="I70" s="70"/>
       <c r="J70" s="70"/>
@@ -2803,10 +2808,10 @@
       <c r="L70" s="70"/>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A71" s="55"/>
-      <c r="B71" s="57"/>
+      <c r="A71" s="196"/>
+      <c r="B71" s="197"/>
       <c r="C71" s="5"/>
-      <c r="D71" s="56"/>
+      <c r="D71" s="112"/>
       <c r="E71" s="54"/>
       <c r="H71" s="70"/>
       <c r="I71" s="70"/>
@@ -2815,14 +2820,11 @@
       <c r="L71" s="70"/>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A72" s="36"/>
-      <c r="B72" s="35"/>
-      <c r="C72" s="35"/>
-      <c r="D72" s="126"/>
-      <c r="E72" s="169">
-        <f>SUM(D69:D71)</f>
-        <v>0</v>
-      </c>
+      <c r="A72" s="55"/>
+      <c r="B72" s="57"/>
+      <c r="C72" s="5"/>
+      <c r="D72" s="56"/>
+      <c r="E72" s="54"/>
       <c r="H72" s="70"/>
       <c r="I72" s="70"/>
       <c r="J72" s="70"/>
@@ -2830,285 +2832,290 @@
       <c r="L72" s="70"/>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="D73" s="62"/>
-      <c r="E73" s="62"/>
+      <c r="A73" s="36"/>
+      <c r="B73" s="35"/>
+      <c r="C73" s="35"/>
+      <c r="D73" s="126"/>
+      <c r="E73" s="169">
+        <f>SUM(D70:D72)</f>
+        <v>0</v>
+      </c>
       <c r="H73" s="70"/>
       <c r="I73" s="70"/>
       <c r="J73" s="70"/>
       <c r="K73" s="70"/>
       <c r="L73" s="70"/>
     </row>
-    <row r="74" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D74" s="62"/>
       <c r="E74" s="62"/>
-      <c r="H74" s="91"/>
-    </row>
-    <row r="75" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A75" s="9" t="s">
+      <c r="H74" s="70"/>
+      <c r="I74" s="70"/>
+      <c r="J74" s="70"/>
+      <c r="K74" s="70"/>
+      <c r="L74" s="70"/>
+    </row>
+    <row r="75" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D75" s="62"/>
+      <c r="E75" s="62"/>
+      <c r="H75" s="91"/>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A76" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="B75" s="10"/>
-      <c r="C75" s="11"/>
-      <c r="D75" s="66"/>
-      <c r="E75" s="67"/>
-    </row>
-    <row r="76" spans="1:12" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="201" t="s">
-        <v>153</v>
-      </c>
-      <c r="B76" s="202"/>
-      <c r="C76" s="5"/>
-      <c r="D76" s="112">
-        <v>3320350</v>
-      </c>
-      <c r="E76" s="104" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="77" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="193"/>
-      <c r="B77" s="194"/>
+      <c r="B76" s="10"/>
+      <c r="C76" s="11"/>
+      <c r="D76" s="66"/>
+      <c r="E76" s="67"/>
+    </row>
+    <row r="77" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A77" s="192"/>
+      <c r="B77" s="193"/>
       <c r="C77" s="5"/>
-      <c r="D77" s="56"/>
-      <c r="E77" s="54"/>
-    </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A78" s="55"/>
-      <c r="B78" s="57"/>
+      <c r="D77" s="112"/>
+      <c r="E77" s="104"/>
+    </row>
+    <row r="78" spans="1:12" ht="12" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A78" s="194"/>
+      <c r="B78" s="195"/>
       <c r="C78" s="5"/>
       <c r="D78" s="56"/>
       <c r="E78" s="54"/>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A79" s="36"/>
-      <c r="B79" s="35"/>
-      <c r="C79" s="35"/>
-      <c r="D79" s="126"/>
-      <c r="E79" s="169">
-        <f>SUM(D76:D78)</f>
-        <v>3320350</v>
-      </c>
-    </row>
-    <row r="80" spans="1:12" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D80" s="62"/>
-    </row>
-    <row r="81" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="55"/>
+      <c r="B79" s="57"/>
+      <c r="C79" s="5"/>
+      <c r="D79" s="56"/>
+      <c r="E79" s="54"/>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A80" s="36"/>
+      <c r="B80" s="35"/>
+      <c r="C80" s="35"/>
+      <c r="D80" s="126"/>
+      <c r="E80" s="169">
+        <f>SUM(D77:D79)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="1:5" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="D81" s="62"/>
     </row>
-    <row r="82" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A82" s="105" t="s">
-        <v>57</v>
-      </c>
-      <c r="B82" s="106"/>
-      <c r="C82" s="106"/>
-      <c r="D82" s="127"/>
-      <c r="E82" s="116">
-        <v>0</v>
-      </c>
+    <row r="82" spans="1:5" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D82" s="62"/>
     </row>
     <row r="83" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D83" s="62"/>
+      <c r="A83" s="105" t="s">
+        <v>162</v>
+      </c>
+      <c r="B83" s="106"/>
+      <c r="C83" s="106"/>
+      <c r="D83" s="127"/>
+      <c r="E83" s="116">
+        <v>1000000</v>
+      </c>
     </row>
     <row r="84" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A84" s="3" t="s">
+      <c r="D84" s="62"/>
+    </row>
+    <row r="85" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B84" s="8"/>
-      <c r="C84" s="4"/>
-      <c r="D84" s="64"/>
-      <c r="E84" s="45">
-        <f>E79+E82</f>
-        <v>3320350</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D85" s="62"/>
+      <c r="B85" s="8"/>
+      <c r="C85" s="4"/>
+      <c r="D85" s="64"/>
+      <c r="E85" s="45">
+        <f>E80+E83</f>
+        <v>1000000</v>
+      </c>
     </row>
     <row r="86" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A86" s="50" t="s">
-        <v>12</v>
-      </c>
-      <c r="B86" s="51">
-        <f>E66</f>
-        <v>4163981.55</v>
-      </c>
       <c r="D86" s="62"/>
     </row>
     <row r="87" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A87" s="50" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B87" s="51">
-        <f>E66-E64</f>
-        <v>4163981.55</v>
+        <f>E67</f>
+        <v>5824156.5499999998</v>
       </c>
       <c r="D87" s="62"/>
     </row>
     <row r="88" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A88" s="50" t="s">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="B88" s="51">
-        <f>E84-E82</f>
-        <v>3320350</v>
+        <f>E67-E65</f>
+        <v>5824156.5499999998</v>
       </c>
       <c r="D88" s="62"/>
     </row>
     <row r="89" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A89" s="50" t="s">
+        <v>19</v>
+      </c>
+      <c r="B89" s="51">
+        <f>E85-E83</f>
+        <v>0</v>
+      </c>
+      <c r="D89" s="62"/>
+    </row>
+    <row r="90" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="50" t="s">
         <v>30</v>
       </c>
-      <c r="B89" s="51">
-        <f>E84</f>
-        <v>3320350</v>
-      </c>
-      <c r="D89" s="62"/>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B90" s="51">
+        <f>E85</f>
+        <v>1000000</v>
+      </c>
       <c r="D90" s="62"/>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D91" s="62"/>
     </row>
-    <row r="92" spans="1:5" s="28" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A92"/>
-      <c r="B92" s="30"/>
-      <c r="C92" s="27"/>
-      <c r="D92"/>
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D92" s="62"/>
     </row>
     <row r="93" spans="1:5" s="28" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="71" t="s">
-        <v>132</v>
-      </c>
-      <c r="B93" s="72">
+      <c r="A93"/>
+      <c r="B93" s="30"/>
+      <c r="C93" s="27"/>
+      <c r="D93"/>
+    </row>
+    <row r="94" spans="1:5" s="28" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A94" s="71" t="s">
+        <v>163</v>
+      </c>
+      <c r="B94" s="72">
         <v>7227046.5299999993</v>
       </c>
-      <c r="C93" s="27"/>
-      <c r="D93" s="34"/>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A94" s="40" t="s">
-        <v>36</v>
-      </c>
-      <c r="B94" s="76">
-        <f>-B87</f>
-        <v>-4163981.55</v>
-      </c>
-      <c r="E94" s="31"/>
+      <c r="C94" s="27"/>
+      <c r="D94" s="34"/>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="40" t="s">
+        <v>36</v>
+      </c>
+      <c r="B95" s="76">
+        <f>-B88</f>
+        <v>-5824156.5499999998</v>
+      </c>
+      <c r="E95" s="31"/>
+    </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A96" s="40" t="s">
         <v>37</v>
       </c>
-      <c r="B95" s="76">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" ht="30" x14ac:dyDescent="0.25">
-      <c r="A96" s="40" t="s">
-        <v>134</v>
-      </c>
       <c r="B96" s="76">
-        <f>-E72</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="1:5" ht="30" x14ac:dyDescent="0.25">
       <c r="A97" s="40" t="s">
-        <v>158</v>
-      </c>
-      <c r="B97" s="147">
-        <v>-3000000</v>
+        <v>132</v>
+      </c>
+      <c r="B97" s="76">
+        <f>-E73</f>
+        <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="40" t="s">
-        <v>38</v>
-      </c>
-      <c r="B98" s="76">
-        <f>B116</f>
-        <v>0</v>
+        <v>154</v>
+      </c>
+      <c r="B98" s="147">
+        <v>-3000000</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="40" t="s">
-        <v>128</v>
-      </c>
-      <c r="B99" s="77">
+        <v>38</v>
+      </c>
+      <c r="B99" s="76">
+        <f>B117</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A100" s="40" t="s">
+        <v>127</v>
+      </c>
+      <c r="B100" s="77">
         <f>PRORRATEO!L35</f>
         <v>3923179.17</v>
       </c>
     </row>
-    <row r="100" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A100" s="74" t="s">
+    <row r="101" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="74" t="s">
         <v>34</v>
       </c>
-      <c r="B100" s="75">
-        <f>SUM(B93:C99)</f>
-        <v>3986244.1499999994</v>
-      </c>
-      <c r="D100" s="30"/>
-      <c r="E100" s="31"/>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A101" s="73"/>
-      <c r="B101" s="73"/>
-      <c r="D101" s="31"/>
+      <c r="B101" s="75">
+        <f>SUM(B94:C100)</f>
+        <v>2326069.1499999994</v>
+      </c>
+      <c r="D101" s="30"/>
+      <c r="E101" s="31"/>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A102" s="71" t="s">
-        <v>129</v>
-      </c>
-      <c r="B102" s="72">
+      <c r="A102" s="73"/>
+      <c r="B102" s="73"/>
+      <c r="D102" s="31"/>
+    </row>
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A103" s="71" t="s">
+        <v>128</v>
+      </c>
+      <c r="B103" s="72">
         <v>198159.40000000002</v>
       </c>
     </row>
-    <row r="103" spans="1:5" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="40" t="s">
-        <v>157</v>
-      </c>
-      <c r="B103" s="147">
+    <row r="104" spans="1:5" ht="31.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A104" s="40" t="s">
+        <v>153</v>
+      </c>
+      <c r="B104" s="147">
         <v>-75000</v>
-      </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A104" s="40" t="s">
-        <v>159</v>
-      </c>
-      <c r="B104" s="188">
-        <v>3000000</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="40" t="s">
-        <v>37</v>
-      </c>
-      <c r="B105" s="147">
-        <f>-B88</f>
-        <v>-3320350</v>
+        <v>155</v>
+      </c>
+      <c r="B105" s="188">
+        <v>3000000</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="40" t="s">
-        <v>130</v>
-      </c>
-      <c r="B106" s="77">
+        <v>37</v>
+      </c>
+      <c r="B106" s="147">
+        <f>-B89</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A107" s="40" t="s">
+        <v>129</v>
+      </c>
+      <c r="B107" s="77">
         <f>PRORRATEO!L36</f>
         <v>218300.27</v>
       </c>
     </row>
-    <row r="107" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="74" t="s">
+    <row r="108" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="74" t="s">
         <v>34</v>
       </c>
-      <c r="B107" s="75">
-        <f>SUM(B102:C106)</f>
-        <v>21109.669999999896</v>
-      </c>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A108" s="73"/>
-      <c r="B108" s="73"/>
+      <c r="B108" s="75">
+        <f>SUM(B103:C107)</f>
+        <v>3341459.67</v>
+      </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="73"/>
@@ -3122,78 +3129,76 @@
       <c r="A111" s="73"/>
       <c r="B111" s="73"/>
     </row>
-    <row r="112" spans="1:5" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A113" s="200" t="s">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A112" s="73"/>
+      <c r="B112" s="73"/>
+    </row>
+    <row r="113" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A114" s="191" t="s">
         <v>24</v>
       </c>
-      <c r="B113" s="200"/>
-      <c r="C113" s="200"/>
-    </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A114" s="200"/>
-      <c r="B114" s="200"/>
-      <c r="C114" s="200"/>
-    </row>
-    <row r="115" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="68"/>
-      <c r="B115" s="26"/>
-      <c r="C115" s="26">
+      <c r="B114" s="191"/>
+      <c r="C114" s="191"/>
+    </row>
+    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A115" s="191"/>
+      <c r="B115" s="191"/>
+      <c r="C115" s="191"/>
+    </row>
+    <row r="116" spans="1:13" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A116" s="68"/>
+      <c r="B116" s="26"/>
+      <c r="C116" s="26">
         <v>40000</v>
       </c>
-      <c r="E115" s="78"/>
-    </row>
-    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A116" s="32" t="s">
+      <c r="E116" s="78"/>
+    </row>
+    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A117" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="B116" s="69">
-        <f>SUM(B115:B115)</f>
-        <v>0</v>
-      </c>
-      <c r="C116" s="33"/>
-    </row>
-    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="M117" s="7"/>
-    </row>
-    <row r="118" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="199"/>
-      <c r="B118" s="199"/>
-      <c r="C118" s="199"/>
-      <c r="D118" s="199"/>
-      <c r="E118" s="199"/>
-    </row>
-    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A119" s="199"/>
-      <c r="B119" s="199"/>
-      <c r="C119" s="199"/>
-      <c r="D119" s="199"/>
-      <c r="E119" s="199"/>
+      <c r="B117" s="69">
+        <f>SUM(B116:B116)</f>
+        <v>0</v>
+      </c>
+      <c r="C117" s="33"/>
+    </row>
+    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M118" s="7"/>
+    </row>
+    <row r="119" spans="1:13" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A119" s="190"/>
+      <c r="B119" s="190"/>
+      <c r="C119" s="190"/>
+      <c r="D119" s="190"/>
+      <c r="E119" s="190"/>
     </row>
     <row r="120" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A120" s="199"/>
-      <c r="B120" s="199"/>
-      <c r="C120" s="199"/>
-      <c r="D120" s="199"/>
-      <c r="E120" s="199"/>
+      <c r="A120" s="190"/>
+      <c r="B120" s="190"/>
+      <c r="C120" s="190"/>
+      <c r="D120" s="190"/>
+      <c r="E120" s="190"/>
     </row>
     <row r="121" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A121" s="199"/>
-      <c r="B121" s="199"/>
-      <c r="C121" s="199"/>
-      <c r="D121" s="199"/>
-      <c r="E121" s="199"/>
+      <c r="A121" s="190"/>
+      <c r="B121" s="190"/>
+      <c r="C121" s="190"/>
+      <c r="D121" s="190"/>
+      <c r="E121" s="190"/>
+    </row>
+    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A122" s="190"/>
+      <c r="B122" s="190"/>
+      <c r="C122" s="190"/>
+      <c r="D122" s="190"/>
+      <c r="E122" s="190"/>
     </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="A118:E121"/>
-    <mergeCell ref="A113:C114"/>
-    <mergeCell ref="A76:B76"/>
-    <mergeCell ref="A77:B77"/>
-    <mergeCell ref="A69:B69"/>
-    <mergeCell ref="A70:B70"/>
+  <mergeCells count="16">
     <mergeCell ref="A55:B55"/>
-    <mergeCell ref="A57:B57"/>
+    <mergeCell ref="A58:B58"/>
     <mergeCell ref="A37:B37"/>
     <mergeCell ref="B1:D1"/>
     <mergeCell ref="A34:B34"/>
@@ -3201,6 +3206,13 @@
     <mergeCell ref="B3:E3"/>
     <mergeCell ref="A13:E16"/>
     <mergeCell ref="B8:C10"/>
+    <mergeCell ref="A56:B56"/>
+    <mergeCell ref="A119:E122"/>
+    <mergeCell ref="A114:C115"/>
+    <mergeCell ref="A77:B77"/>
+    <mergeCell ref="A78:B78"/>
+    <mergeCell ref="A70:B70"/>
+    <mergeCell ref="A71:B71"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3241,18 +3253,18 @@
       <c r="E1" s="6"/>
       <c r="F1" s="6"/>
       <c r="G1" s="6"/>
-      <c r="H1" s="224"/>
-      <c r="I1" s="224"/>
-      <c r="J1" s="224"/>
-      <c r="K1" s="224"/>
-      <c r="L1" s="224"/>
-      <c r="M1" s="224"/>
-      <c r="N1" s="224"/>
-      <c r="O1" s="224"/>
-      <c r="P1" s="224"/>
-      <c r="Q1" s="224"/>
-      <c r="R1" s="224"/>
-      <c r="S1" s="224"/>
+      <c r="H1" s="206"/>
+      <c r="I1" s="206"/>
+      <c r="J1" s="206"/>
+      <c r="K1" s="206"/>
+      <c r="L1" s="206"/>
+      <c r="M1" s="206"/>
+      <c r="N1" s="206"/>
+      <c r="O1" s="206"/>
+      <c r="P1" s="206"/>
+      <c r="Q1" s="206"/>
+      <c r="R1" s="206"/>
+      <c r="S1" s="206"/>
       <c r="T1" s="6"/>
     </row>
     <row r="2" spans="1:23" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
@@ -3263,36 +3275,35 @@
       <c r="E2" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="F2" s="223">
-        <f>V3</f>
-        <v>3320350</v>
-      </c>
-      <c r="G2" s="223"/>
+      <c r="F2" s="221">
+        <v>1000000</v>
+      </c>
+      <c r="G2" s="221"/>
       <c r="H2" s="168"/>
       <c r="I2" s="168"/>
       <c r="J2" s="15" t="s">
-        <v>135</v>
-      </c>
-      <c r="K2" s="212">
-        <v>0</v>
-      </c>
-      <c r="L2" s="212"/>
-      <c r="M2" s="212"/>
+        <v>133</v>
+      </c>
+      <c r="K2" s="222">
+        <v>0</v>
+      </c>
+      <c r="L2" s="222"/>
+      <c r="M2" s="222"/>
       <c r="N2" s="15"/>
       <c r="O2" s="15"/>
       <c r="P2" s="15" t="s">
         <v>54</v>
       </c>
-      <c r="Q2" s="223">
+      <c r="Q2" s="221">
         <f>V2</f>
-        <v>4163981.55</v>
-      </c>
-      <c r="R2" s="223"/>
-      <c r="S2" s="223"/>
+        <v>5824156.5499999998</v>
+      </c>
+      <c r="R2" s="221"/>
+      <c r="S2" s="221"/>
       <c r="T2" s="41"/>
       <c r="U2" s="20"/>
       <c r="V2">
-        <v>4163981.55</v>
+        <v>5824156.5499999998</v>
       </c>
     </row>
     <row r="3" spans="1:23" ht="13.15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -3321,183 +3332,183 @@
       </c>
     </row>
     <row r="4" spans="1:23" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="227" t="s">
-        <v>160</v>
-      </c>
-      <c r="B4" s="228"/>
-      <c r="C4" s="228"/>
-      <c r="D4" s="228"/>
-      <c r="E4" s="228"/>
-      <c r="F4" s="228"/>
-      <c r="G4" s="228"/>
-      <c r="H4" s="228"/>
-      <c r="I4" s="228"/>
-      <c r="J4" s="228"/>
-      <c r="K4" s="228"/>
-      <c r="L4" s="228"/>
-      <c r="M4" s="228"/>
-      <c r="N4" s="228"/>
-      <c r="O4" s="228"/>
-      <c r="P4" s="228"/>
-      <c r="Q4" s="228"/>
-      <c r="R4" s="228"/>
-      <c r="S4" s="228"/>
-      <c r="T4" s="229"/>
+      <c r="A4" s="213" t="s">
+        <v>156</v>
+      </c>
+      <c r="B4" s="214"/>
+      <c r="C4" s="214"/>
+      <c r="D4" s="214"/>
+      <c r="E4" s="214"/>
+      <c r="F4" s="214"/>
+      <c r="G4" s="214"/>
+      <c r="H4" s="214"/>
+      <c r="I4" s="214"/>
+      <c r="J4" s="214"/>
+      <c r="K4" s="214"/>
+      <c r="L4" s="214"/>
+      <c r="M4" s="214"/>
+      <c r="N4" s="214"/>
+      <c r="O4" s="214"/>
+      <c r="P4" s="214"/>
+      <c r="Q4" s="214"/>
+      <c r="R4" s="214"/>
+      <c r="S4" s="214"/>
+      <c r="T4" s="215"/>
     </row>
     <row r="5" spans="1:23" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="230"/>
-      <c r="B5" s="231"/>
-      <c r="C5" s="231"/>
-      <c r="D5" s="231"/>
-      <c r="E5" s="231"/>
-      <c r="F5" s="231"/>
-      <c r="G5" s="231"/>
-      <c r="H5" s="231"/>
-      <c r="I5" s="231"/>
-      <c r="J5" s="231"/>
-      <c r="K5" s="231"/>
-      <c r="L5" s="231"/>
-      <c r="M5" s="231"/>
-      <c r="N5" s="231"/>
-      <c r="O5" s="231"/>
-      <c r="P5" s="231"/>
-      <c r="Q5" s="231"/>
-      <c r="R5" s="231"/>
-      <c r="S5" s="231"/>
-      <c r="T5" s="232"/>
+      <c r="A5" s="216"/>
+      <c r="B5" s="217"/>
+      <c r="C5" s="217"/>
+      <c r="D5" s="217"/>
+      <c r="E5" s="217"/>
+      <c r="F5" s="217"/>
+      <c r="G5" s="217"/>
+      <c r="H5" s="217"/>
+      <c r="I5" s="217"/>
+      <c r="J5" s="217"/>
+      <c r="K5" s="217"/>
+      <c r="L5" s="217"/>
+      <c r="M5" s="217"/>
+      <c r="N5" s="217"/>
+      <c r="O5" s="217"/>
+      <c r="P5" s="217"/>
+      <c r="Q5" s="217"/>
+      <c r="R5" s="217"/>
+      <c r="S5" s="217"/>
+      <c r="T5" s="218"/>
     </row>
     <row r="6" spans="1:23" ht="13.15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="230"/>
-      <c r="B6" s="231"/>
-      <c r="C6" s="231"/>
-      <c r="D6" s="231"/>
-      <c r="E6" s="231"/>
-      <c r="F6" s="231"/>
-      <c r="G6" s="231"/>
-      <c r="H6" s="231"/>
-      <c r="I6" s="231"/>
-      <c r="J6" s="231"/>
-      <c r="K6" s="231"/>
-      <c r="L6" s="231"/>
-      <c r="M6" s="231"/>
-      <c r="N6" s="231"/>
-      <c r="O6" s="231"/>
-      <c r="P6" s="231"/>
-      <c r="Q6" s="231"/>
-      <c r="R6" s="231"/>
-      <c r="S6" s="231"/>
-      <c r="T6" s="232"/>
+      <c r="A6" s="216"/>
+      <c r="B6" s="217"/>
+      <c r="C6" s="217"/>
+      <c r="D6" s="217"/>
+      <c r="E6" s="217"/>
+      <c r="F6" s="217"/>
+      <c r="G6" s="217"/>
+      <c r="H6" s="217"/>
+      <c r="I6" s="217"/>
+      <c r="J6" s="217"/>
+      <c r="K6" s="217"/>
+      <c r="L6" s="217"/>
+      <c r="M6" s="217"/>
+      <c r="N6" s="217"/>
+      <c r="O6" s="217"/>
+      <c r="P6" s="217"/>
+      <c r="Q6" s="217"/>
+      <c r="R6" s="217"/>
+      <c r="S6" s="217"/>
+      <c r="T6" s="218"/>
     </row>
     <row r="7" spans="1:23" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="230"/>
-      <c r="B7" s="231"/>
-      <c r="C7" s="231"/>
-      <c r="D7" s="231"/>
-      <c r="E7" s="231"/>
-      <c r="F7" s="231"/>
-      <c r="G7" s="231"/>
-      <c r="H7" s="231"/>
-      <c r="I7" s="231"/>
-      <c r="J7" s="231"/>
-      <c r="K7" s="231"/>
-      <c r="L7" s="231"/>
-      <c r="M7" s="231"/>
-      <c r="N7" s="231"/>
-      <c r="O7" s="231"/>
-      <c r="P7" s="231"/>
-      <c r="Q7" s="231"/>
-      <c r="R7" s="231"/>
-      <c r="S7" s="231"/>
-      <c r="T7" s="232"/>
+      <c r="A7" s="216"/>
+      <c r="B7" s="217"/>
+      <c r="C7" s="217"/>
+      <c r="D7" s="217"/>
+      <c r="E7" s="217"/>
+      <c r="F7" s="217"/>
+      <c r="G7" s="217"/>
+      <c r="H7" s="217"/>
+      <c r="I7" s="217"/>
+      <c r="J7" s="217"/>
+      <c r="K7" s="217"/>
+      <c r="L7" s="217"/>
+      <c r="M7" s="217"/>
+      <c r="N7" s="217"/>
+      <c r="O7" s="217"/>
+      <c r="P7" s="217"/>
+      <c r="Q7" s="217"/>
+      <c r="R7" s="217"/>
+      <c r="S7" s="217"/>
+      <c r="T7" s="218"/>
     </row>
     <row r="8" spans="1:23" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="216" t="s">
+      <c r="A8" s="207" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="207" t="s">
+      <c r="B8" s="209" t="s">
+        <v>71</v>
+      </c>
+      <c r="C8" s="209" t="s">
         <v>72</v>
       </c>
-      <c r="C8" s="207" t="s">
-        <v>73</v>
-      </c>
-      <c r="D8" s="207" t="s">
-        <v>77</v>
-      </c>
-      <c r="E8" s="207" t="s">
+      <c r="D8" s="209" t="s">
+        <v>76</v>
+      </c>
+      <c r="E8" s="209" t="s">
         <v>6</v>
       </c>
-      <c r="F8" s="207" t="s">
+      <c r="F8" s="209" t="s">
+        <v>114</v>
+      </c>
+      <c r="G8" s="209" t="s">
         <v>115</v>
       </c>
-      <c r="G8" s="207" t="s">
-        <v>116</v>
-      </c>
-      <c r="H8" s="216" t="s">
-        <v>114</v>
+      <c r="H8" s="207" t="s">
+        <v>113</v>
       </c>
       <c r="I8" s="148" t="s">
         <v>14</v>
       </c>
-      <c r="J8" s="216" t="s">
+      <c r="J8" s="207" t="s">
         <v>35</v>
       </c>
-      <c r="K8" s="207" t="s">
+      <c r="K8" s="209" t="s">
         <v>7</v>
       </c>
-      <c r="L8" s="207" t="s">
-        <v>125</v>
-      </c>
-      <c r="M8" s="225" t="s">
+      <c r="L8" s="209" t="s">
+        <v>124</v>
+      </c>
+      <c r="M8" s="211" t="s">
         <v>22</v>
       </c>
-      <c r="N8" s="216" t="s">
-        <v>137</v>
-      </c>
-      <c r="O8" s="216" t="s">
+      <c r="N8" s="207" t="s">
+        <v>135</v>
+      </c>
+      <c r="O8" s="207" t="s">
         <v>56</v>
       </c>
-      <c r="P8" s="216" t="s">
+      <c r="P8" s="207" t="s">
         <v>20</v>
       </c>
-      <c r="Q8" s="216" t="s">
+      <c r="Q8" s="207" t="s">
         <v>43</v>
       </c>
-      <c r="R8" s="205" t="s">
-        <v>136</v>
+      <c r="R8" s="231" t="s">
+        <v>134</v>
       </c>
       <c r="S8" s="149" t="s">
         <v>28</v>
       </c>
-      <c r="T8" s="233" t="s">
+      <c r="T8" s="219" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="9" spans="1:23" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="217"/>
-      <c r="B9" s="208"/>
-      <c r="C9" s="208"/>
-      <c r="D9" s="208"/>
-      <c r="E9" s="208"/>
-      <c r="F9" s="208"/>
-      <c r="G9" s="208"/>
-      <c r="H9" s="217"/>
+      <c r="A9" s="208"/>
+      <c r="B9" s="210"/>
+      <c r="C9" s="210"/>
+      <c r="D9" s="210"/>
+      <c r="E9" s="210"/>
+      <c r="F9" s="210"/>
+      <c r="G9" s="210"/>
+      <c r="H9" s="208"/>
       <c r="I9" s="161" t="s">
-        <v>113</v>
-      </c>
-      <c r="J9" s="217"/>
-      <c r="K9" s="208"/>
-      <c r="L9" s="208"/>
-      <c r="M9" s="226"/>
-      <c r="N9" s="217"/>
-      <c r="O9" s="217"/>
-      <c r="P9" s="217"/>
-      <c r="Q9" s="217"/>
-      <c r="R9" s="206"/>
+        <v>112</v>
+      </c>
+      <c r="J9" s="208"/>
+      <c r="K9" s="210"/>
+      <c r="L9" s="210"/>
+      <c r="M9" s="212"/>
+      <c r="N9" s="208"/>
+      <c r="O9" s="208"/>
+      <c r="P9" s="208"/>
+      <c r="Q9" s="208"/>
+      <c r="R9" s="232"/>
       <c r="S9" s="186" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 17/09</v>
       </c>
-      <c r="T9" s="234"/>
+      <c r="T9" s="220"/>
     </row>
     <row r="10" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="166">
@@ -3508,10 +3519,10 @@
       </c>
       <c r="C10" s="151"/>
       <c r="D10" s="151" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E10" s="163" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F10" s="164">
         <v>5.44</v>
@@ -3532,7 +3543,7 @@
         <v>251132.19</v>
       </c>
       <c r="L10" s="160" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M10" s="159">
         <f t="shared" ref="M10:M33" si="0">J10-K10</f>
@@ -3545,11 +3556,11 @@
       <c r="O10" s="159"/>
       <c r="P10" s="157">
         <f>Q$2*I10/100</f>
-        <v>231517.37418000001</v>
+        <v>323823.10418000002</v>
       </c>
       <c r="Q10" s="158">
         <f>F$2*I10/100</f>
-        <v>184611.46</v>
+        <v>55600.000000000007</v>
       </c>
       <c r="R10" s="158">
         <f>K$2/18</f>
@@ -3557,18 +3568,18 @@
       </c>
       <c r="S10" s="156">
         <f>ROUND(SUM(M10:R10),0) + U10</f>
-        <v>416129.19</v>
+        <v>379423.19</v>
       </c>
       <c r="T10" s="156">
         <f t="shared" ref="T10:T33" si="1">ROUND(S10*3%,0) + S10</f>
-        <v>428613.19</v>
+        <v>390806.19</v>
       </c>
       <c r="U10" s="31">
         <f t="shared" ref="U10:U15" si="2">A10/100</f>
         <v>0.19</v>
       </c>
       <c r="V10" s="31" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="11" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3578,10 +3589,10 @@
       <c r="B11" s="130"/>
       <c r="C11" s="130"/>
       <c r="D11" s="130" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="E11" s="92" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F11" s="93">
         <v>2.87</v>
@@ -3599,7 +3610,7 @@
         <v>99395</v>
       </c>
       <c r="L11" s="117" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M11" s="95">
         <f t="shared" si="0"/>
@@ -3612,27 +3623,27 @@
       <c r="O11" s="95"/>
       <c r="P11" s="96">
         <f t="shared" ref="P11:P33" si="5">Q$2*I11/100</f>
-        <v>119506.270485</v>
+        <v>167153.29298500001</v>
       </c>
       <c r="Q11" s="97">
         <f t="shared" ref="Q11:Q33" si="6">F$2*I11/100</f>
-        <v>95294.044999999998</v>
+        <v>28700</v>
       </c>
       <c r="R11" s="97"/>
       <c r="S11" s="156">
         <f t="shared" ref="S11:S26" si="7">ROUND(SUM(M11:R11),0) + U11</f>
-        <v>192288.2</v>
+        <v>173340.2</v>
       </c>
       <c r="T11" s="138">
         <f t="shared" si="1"/>
-        <v>198057.2</v>
+        <v>178540.2</v>
       </c>
       <c r="U11" s="31">
         <f t="shared" si="2"/>
         <v>0.2</v>
       </c>
       <c r="V11" s="31" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="12" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -3644,10 +3655,10 @@
       </c>
       <c r="C12" s="131"/>
       <c r="D12" s="131" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="E12" s="98" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F12" s="93">
         <v>5.44</v>
@@ -3667,7 +3678,7 @@
         <v>0</v>
       </c>
       <c r="L12" s="117" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M12" s="95">
         <f t="shared" si="0"/>
@@ -3680,11 +3691,11 @@
       <c r="O12" s="95"/>
       <c r="P12" s="96">
         <f t="shared" si="5"/>
-        <v>231517.37418000001</v>
+        <v>323823.10418000002</v>
       </c>
       <c r="Q12" s="97">
         <f t="shared" si="6"/>
-        <v>184611.46</v>
+        <v>55600.000000000007</v>
       </c>
       <c r="R12" s="158">
         <f>K$2/18</f>
@@ -3692,11 +3703,11 @@
       </c>
       <c r="S12" s="156">
         <f t="shared" si="7"/>
-        <v>689046.21</v>
+        <v>652341.21</v>
       </c>
       <c r="T12" s="138">
         <f t="shared" si="1"/>
-        <v>709717.21</v>
+        <v>671911.21</v>
       </c>
       <c r="U12" s="31">
         <f t="shared" si="2"/>
@@ -3711,10 +3722,10 @@
       <c r="B13" s="130"/>
       <c r="C13" s="130"/>
       <c r="D13" s="130" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E13" s="92" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F13" s="93">
         <v>2.87</v>
@@ -3733,7 +3744,7 @@
         <v>76882.22</v>
       </c>
       <c r="L13" s="117" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M13" s="95">
         <f t="shared" si="0"/>
@@ -3746,27 +3757,27 @@
       <c r="O13" s="95"/>
       <c r="P13" s="96">
         <f t="shared" si="5"/>
-        <v>119506.270485</v>
+        <v>167153.29298500001</v>
       </c>
       <c r="Q13" s="97">
         <f t="shared" si="6"/>
-        <v>95294.044999999998</v>
+        <v>28700</v>
       </c>
       <c r="R13" s="97"/>
       <c r="S13" s="156">
         <f t="shared" si="7"/>
-        <v>214800.22</v>
+        <v>195853.22</v>
       </c>
       <c r="T13" s="138">
         <f t="shared" si="1"/>
-        <v>221244.22</v>
+        <v>201729.22</v>
       </c>
       <c r="U13" s="31">
         <f t="shared" si="2"/>
         <v>0.22</v>
       </c>
       <c r="V13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="W13" s="31"/>
     </row>
@@ -3778,13 +3789,13 @@
         <v>7</v>
       </c>
       <c r="C14" s="130" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D14" s="130" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="E14" s="92" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F14" s="93">
         <v>5.44</v>
@@ -3807,7 +3818,7 @@
         <v>261311.46000000002</v>
       </c>
       <c r="L14" s="117" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M14" s="95">
         <f t="shared" si="0"/>
@@ -3820,11 +3831,11 @@
       <c r="O14" s="95"/>
       <c r="P14" s="96">
         <f t="shared" si="5"/>
-        <v>247340.50407000002</v>
+        <v>345954.89906999998</v>
       </c>
       <c r="Q14" s="97">
         <f t="shared" si="6"/>
-        <v>197228.79</v>
+        <v>59400</v>
       </c>
       <c r="R14" s="158">
         <f>K$2/18</f>
@@ -3832,11 +3843,11 @@
       </c>
       <c r="S14" s="156">
         <f t="shared" si="7"/>
-        <v>444569.23</v>
+        <v>405355.23</v>
       </c>
       <c r="T14" s="138">
         <f t="shared" si="1"/>
-        <v>457906.23</v>
+        <v>417516.23</v>
       </c>
       <c r="U14" s="31">
         <f t="shared" si="2"/>
@@ -3851,10 +3862,10 @@
       <c r="B15" s="130"/>
       <c r="C15" s="130"/>
       <c r="D15" s="130" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="E15" s="92" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F15" s="93">
         <v>2.87</v>
@@ -3872,7 +3883,7 @@
         <v>114800.24</v>
       </c>
       <c r="L15" s="117" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M15" s="95">
         <f t="shared" si="0"/>
@@ -3885,42 +3896,42 @@
       <c r="O15" s="95"/>
       <c r="P15" s="96">
         <f t="shared" si="5"/>
-        <v>119506.270485</v>
+        <v>167153.29298500001</v>
       </c>
       <c r="Q15" s="97">
         <f t="shared" si="6"/>
-        <v>95294.044999999998</v>
+        <v>28700</v>
       </c>
       <c r="R15" s="97"/>
       <c r="S15" s="156">
         <f t="shared" si="7"/>
-        <v>176882.24</v>
+        <v>157935.24</v>
       </c>
       <c r="T15" s="138">
         <f t="shared" si="1"/>
-        <v>182188.24</v>
+        <v>162673.24</v>
       </c>
       <c r="U15" s="31">
         <f t="shared" si="2"/>
         <v>0.24</v>
       </c>
       <c r="V15" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16" spans="1:23" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="154" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B16" s="130">
         <v>9</v>
       </c>
       <c r="C16" s="130"/>
       <c r="D16" s="130" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E16" s="92" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F16" s="93"/>
       <c r="G16" s="93">
@@ -3939,7 +3950,7 @@
         <v>116388.24</v>
       </c>
       <c r="L16" s="117" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M16" s="95">
         <f t="shared" si="0"/>
@@ -3952,11 +3963,11 @@
       <c r="O16" s="95"/>
       <c r="P16" s="96">
         <f t="shared" si="5"/>
-        <v>22069.102214999999</v>
+        <v>30868.029715000001</v>
       </c>
       <c r="Q16" s="97">
         <f t="shared" si="6"/>
-        <v>17597.855</v>
+        <v>5300</v>
       </c>
       <c r="R16" s="158">
         <f t="shared" ref="R16:R21" si="8">K$2/18</f>
@@ -3964,11 +3975,11 @@
       </c>
       <c r="S16" s="156">
         <f t="shared" si="7"/>
-        <v>39667.24</v>
+        <v>36168.239999999998</v>
       </c>
       <c r="T16" s="138">
         <f t="shared" si="1"/>
-        <v>40857.24</v>
+        <v>37253.24</v>
       </c>
       <c r="U16" s="31">
         <v>0.24</v>
@@ -3983,10 +3994,10 @@
       </c>
       <c r="C17" s="130"/>
       <c r="D17" s="130" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E17" s="92" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F17" s="93">
         <v>5.44</v>
@@ -4007,7 +4018,7 @@
         <v>224658.25</v>
       </c>
       <c r="L17" s="117" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M17" s="95">
         <f t="shared" si="0"/>
@@ -4020,11 +4031,11 @@
       <c r="O17" s="95"/>
       <c r="P17" s="96">
         <f t="shared" si="5"/>
-        <v>231517.37418000001</v>
+        <v>323823.10418000002</v>
       </c>
       <c r="Q17" s="97">
         <f t="shared" si="6"/>
-        <v>184611.46</v>
+        <v>55600.000000000007</v>
       </c>
       <c r="R17" s="158">
         <f t="shared" si="8"/>
@@ -4032,11 +4043,11 @@
       </c>
       <c r="S17" s="156">
         <f t="shared" si="7"/>
-        <v>416129.25</v>
+        <v>379423.25</v>
       </c>
       <c r="T17" s="138">
         <f t="shared" si="1"/>
-        <v>428613.25</v>
+        <v>390806.25</v>
       </c>
       <c r="U17" s="31">
         <f t="shared" ref="U17:U27" si="9">A17/100</f>
@@ -4053,10 +4064,10 @@
       </c>
       <c r="C18" s="130"/>
       <c r="D18" s="130" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="E18" s="92" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F18" s="93">
         <v>2.87</v>
@@ -4077,7 +4088,7 @@
         <v>190055.26</v>
       </c>
       <c r="L18" s="117" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M18" s="95">
         <f t="shared" si="0"/>
@@ -4090,11 +4101,11 @@
       <c r="O18" s="95"/>
       <c r="P18" s="96">
         <f t="shared" si="5"/>
-        <v>136578.59484000001</v>
+        <v>191032.33484000002</v>
       </c>
       <c r="Q18" s="97">
         <f t="shared" si="6"/>
-        <v>108907.48</v>
+        <v>32800.000000000007</v>
       </c>
       <c r="R18" s="158">
         <f t="shared" si="8"/>
@@ -4102,18 +4113,18 @@
       </c>
       <c r="S18" s="156">
         <f t="shared" si="7"/>
-        <v>245486.26</v>
+        <v>223832.26</v>
       </c>
       <c r="T18" s="138">
         <f t="shared" si="1"/>
-        <v>252851.26</v>
+        <v>230547.26</v>
       </c>
       <c r="U18" s="31">
         <f t="shared" si="9"/>
         <v>0.26</v>
       </c>
       <c r="V18" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="19" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -4126,10 +4137,10 @@
       </c>
       <c r="C19" s="130"/>
       <c r="D19" s="130" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="E19" s="92" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F19" s="93">
         <v>5.44</v>
@@ -4161,11 +4172,11 @@
       <c r="O19" s="95"/>
       <c r="P19" s="96">
         <f t="shared" si="5"/>
-        <v>231517.37418000001</v>
+        <v>323823.10418000002</v>
       </c>
       <c r="Q19" s="97">
         <f t="shared" si="6"/>
-        <v>184611.46</v>
+        <v>55600.000000000007</v>
       </c>
       <c r="R19" s="158">
         <f t="shared" si="8"/>
@@ -4173,11 +4184,11 @@
       </c>
       <c r="S19" s="156">
         <f t="shared" si="7"/>
-        <v>440416.27</v>
+        <v>403710.27</v>
       </c>
       <c r="T19" s="138">
         <f t="shared" si="1"/>
-        <v>453628.27</v>
+        <v>415821.27</v>
       </c>
       <c r="U19" s="31">
         <f t="shared" si="9"/>
@@ -4194,10 +4205,10 @@
       </c>
       <c r="C20" s="130"/>
       <c r="D20" s="130" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E20" s="92" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F20" s="93">
         <v>2.87</v>
@@ -4218,7 +4229,7 @@
         <v>190055.28</v>
       </c>
       <c r="L20" s="117" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M20" s="123">
         <f t="shared" si="0"/>
@@ -4231,11 +4242,11 @@
       <c r="O20" s="95"/>
       <c r="P20" s="96">
         <f t="shared" si="5"/>
-        <v>136578.59484000001</v>
+        <v>191032.33484000002</v>
       </c>
       <c r="Q20" s="97">
         <f t="shared" si="6"/>
-        <v>108907.48</v>
+        <v>32800.000000000007</v>
       </c>
       <c r="R20" s="158">
         <f t="shared" si="8"/>
@@ -4243,18 +4254,18 @@
       </c>
       <c r="S20" s="156">
         <f t="shared" si="7"/>
-        <v>245486.28</v>
+        <v>223832.28</v>
       </c>
       <c r="T20" s="138">
         <f t="shared" si="1"/>
-        <v>252851.28</v>
+        <v>230547.28</v>
       </c>
       <c r="U20" s="31">
         <f t="shared" si="9"/>
         <v>0.28000000000000003</v>
       </c>
       <c r="V20" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="21" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -4266,13 +4277,13 @@
         <v>11</v>
       </c>
       <c r="C21" s="130" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D21" s="130" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E21" s="92" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F21" s="93">
         <v>5.44</v>
@@ -4294,7 +4305,7 @@
         <v>233644.29</v>
       </c>
       <c r="L21" s="117" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M21" s="123">
         <f t="shared" si="0"/>
@@ -4306,11 +4317,11 @@
       <c r="O21" s="95"/>
       <c r="P21" s="96">
         <f t="shared" si="5"/>
-        <v>238596.142815</v>
+        <v>333724.170315</v>
       </c>
       <c r="Q21" s="97">
         <f t="shared" si="6"/>
-        <v>190256.05499999999</v>
+        <v>57300</v>
       </c>
       <c r="R21" s="158">
         <f t="shared" si="8"/>
@@ -4318,11 +4329,11 @@
       </c>
       <c r="S21" s="156">
         <f t="shared" si="7"/>
-        <v>450894.29</v>
+        <v>413066.29</v>
       </c>
       <c r="T21" s="138">
         <f t="shared" si="1"/>
-        <v>464421.29</v>
+        <v>425458.29</v>
       </c>
       <c r="U21" s="31">
         <f t="shared" si="9"/>
@@ -4337,10 +4348,10 @@
       <c r="B22" s="130"/>
       <c r="C22" s="130"/>
       <c r="D22" s="130" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="E22" s="92" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F22" s="93">
         <v>2.87</v>
@@ -4358,7 +4369,7 @@
         <v>76700</v>
       </c>
       <c r="L22" s="117" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M22" s="123">
         <f t="shared" si="0"/>
@@ -4371,27 +4382,27 @@
       <c r="O22" s="95"/>
       <c r="P22" s="96">
         <f t="shared" si="5"/>
-        <v>119506.270485</v>
+        <v>167153.29298500001</v>
       </c>
       <c r="Q22" s="97">
         <f t="shared" si="6"/>
-        <v>95294.044999999998</v>
+        <v>28700</v>
       </c>
       <c r="R22" s="97"/>
       <c r="S22" s="156">
         <f t="shared" si="7"/>
-        <v>214738.3</v>
+        <v>195791.3</v>
       </c>
       <c r="T22" s="138">
         <f t="shared" si="1"/>
-        <v>221180.3</v>
+        <v>201665.3</v>
       </c>
       <c r="U22" s="31">
         <f t="shared" si="9"/>
         <v>0.3</v>
       </c>
       <c r="V22" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="23" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -4403,13 +4414,13 @@
         <v>1</v>
       </c>
       <c r="C23" s="130" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="D23" s="130" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E23" s="92" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F23" s="93">
         <v>5.44</v>
@@ -4431,7 +4442,7 @@
         <v>244944.31</v>
       </c>
       <c r="L23" s="117" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M23" s="123">
         <f t="shared" si="0"/>
@@ -4443,11 +4454,11 @@
       <c r="O23" s="95"/>
       <c r="P23" s="96">
         <f t="shared" si="5"/>
-        <v>250255.29115499998</v>
+        <v>350031.80865499994</v>
       </c>
       <c r="Q23" s="97">
         <f t="shared" si="6"/>
-        <v>199553.035</v>
+        <v>60100</v>
       </c>
       <c r="R23" s="158">
         <f>K$2/18</f>
@@ -4455,11 +4466,11 @@
       </c>
       <c r="S23" s="156">
         <f t="shared" si="7"/>
-        <v>468050.31</v>
+        <v>428374.31</v>
       </c>
       <c r="T23" s="138">
         <f t="shared" si="1"/>
-        <v>482092.31</v>
+        <v>441225.31</v>
       </c>
       <c r="U23" s="31">
         <f t="shared" si="9"/>
@@ -4474,10 +4485,10 @@
       <c r="B24" s="131"/>
       <c r="C24" s="131"/>
       <c r="D24" s="131" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E24" s="98" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F24" s="93">
         <v>2.87</v>
@@ -4496,7 +4507,7 @@
         <v>79187.320000000007</v>
       </c>
       <c r="L24" s="117" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M24" s="123">
         <f t="shared" si="0"/>
@@ -4509,27 +4520,27 @@
       <c r="O24" s="95"/>
       <c r="P24" s="96">
         <f t="shared" si="5"/>
-        <v>119506.270485</v>
+        <v>167153.29298500001</v>
       </c>
       <c r="Q24" s="97">
         <f t="shared" si="6"/>
-        <v>95294.044999999998</v>
+        <v>28700</v>
       </c>
       <c r="R24" s="97"/>
       <c r="S24" s="156">
         <f t="shared" si="7"/>
-        <v>214800.32</v>
+        <v>195853.32</v>
       </c>
       <c r="T24" s="138">
         <f t="shared" si="1"/>
-        <v>221244.32</v>
+        <v>201729.32</v>
       </c>
       <c r="U24" s="31">
         <f t="shared" si="9"/>
         <v>0.32</v>
       </c>
       <c r="V24" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="25" spans="1:22" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
@@ -4542,10 +4553,10 @@
       </c>
       <c r="C25" s="130"/>
       <c r="D25" s="130" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E25" s="92" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F25" s="93">
         <v>5.44</v>
@@ -4566,7 +4577,7 @@
         <v>259972.33</v>
       </c>
       <c r="L25" s="117" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M25" s="123">
         <f t="shared" si="0"/>
@@ -4579,11 +4590,11 @@
       <c r="O25" s="95"/>
       <c r="P25" s="96">
         <f t="shared" si="5"/>
-        <v>245258.51329500001</v>
+        <v>343042.82079500007</v>
       </c>
       <c r="Q25" s="97">
         <f t="shared" si="6"/>
-        <v>195568.61500000005</v>
+        <v>58900.000000000007</v>
       </c>
       <c r="R25" s="158">
         <f>K$2/18</f>
@@ -4591,11 +4602,11 @@
       </c>
       <c r="S25" s="156">
         <f t="shared" si="7"/>
-        <v>440827.33</v>
+        <v>401943.33</v>
       </c>
       <c r="T25" s="138">
         <f t="shared" si="1"/>
-        <v>454052.33</v>
+        <v>414001.33</v>
       </c>
       <c r="U25" s="31">
         <f t="shared" si="9"/>
@@ -4610,10 +4621,10 @@
       <c r="B26" s="130"/>
       <c r="C26" s="130"/>
       <c r="D26" s="130" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E26" s="92" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F26" s="93">
         <v>2.87</v>
@@ -4631,7 +4642,7 @@
         <v>99345.34</v>
       </c>
       <c r="L26" s="117" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M26" s="123">
         <f t="shared" si="0"/>
@@ -4644,20 +4655,20 @@
       <c r="O26" s="95"/>
       <c r="P26" s="96">
         <f t="shared" si="5"/>
-        <v>119506.270485</v>
+        <v>167153.29298500001</v>
       </c>
       <c r="Q26" s="97">
         <f t="shared" si="6"/>
-        <v>95294.044999999998</v>
+        <v>28700</v>
       </c>
       <c r="R26" s="97"/>
       <c r="S26" s="156">
         <f t="shared" si="7"/>
-        <v>192337.34</v>
+        <v>173390.34</v>
       </c>
       <c r="T26" s="138">
         <f t="shared" si="1"/>
-        <v>198107.34</v>
+        <v>178592.34</v>
       </c>
       <c r="U26" s="31">
         <f t="shared" si="9"/>
@@ -4675,11 +4686,11 @@
       <c r="C27" s="130" t="s">
         <v>55</v>
       </c>
-      <c r="D27" s="218">
+      <c r="D27" s="226">
         <v>9</v>
       </c>
-      <c r="E27" s="218" t="s">
-        <v>110</v>
+      <c r="E27" s="226" t="s">
+        <v>109</v>
       </c>
       <c r="F27" s="135">
         <f>7.73/2</f>
@@ -4703,7 +4714,7 @@
         <v>447977.35</v>
       </c>
       <c r="L27" s="117" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M27" s="123">
         <f t="shared" si="0"/>
@@ -4716,11 +4727,11 @@
       <c r="O27" s="95"/>
       <c r="P27" s="96">
         <f t="shared" si="5"/>
-        <v>181757.79465750002</v>
+        <v>254224.43340750001</v>
       </c>
       <c r="Q27" s="97">
         <f t="shared" si="6"/>
-        <v>144933.2775</v>
+        <v>43650</v>
       </c>
       <c r="R27" s="158">
         <f t="shared" ref="R27:R33" si="11">K$2/18</f>
@@ -4728,11 +4739,11 @@
       </c>
       <c r="S27" s="138">
         <f>ROUND(SUM(M27:R27)+P28+Q28+R28,0) + U27</f>
-        <v>646646.35</v>
+        <v>589607.35</v>
       </c>
       <c r="T27" s="138">
         <f t="shared" si="1"/>
-        <v>666045.35</v>
+        <v>607295.35</v>
       </c>
       <c r="U27" s="31">
         <f t="shared" si="9"/>
@@ -4741,14 +4752,14 @@
     </row>
     <row r="28" spans="1:22" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="154" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B28" s="130">
         <v>5</v>
       </c>
       <c r="C28" s="133"/>
-      <c r="D28" s="219"/>
-      <c r="E28" s="219"/>
+      <c r="D28" s="227"/>
+      <c r="E28" s="227"/>
       <c r="F28" s="135">
         <f>7.73/2</f>
         <v>3.8650000000000002</v>
@@ -4769,7 +4780,7 @@
         <v>0</v>
       </c>
       <c r="L28" s="117" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M28" s="123">
         <f t="shared" si="0"/>
@@ -4782,11 +4793,11 @@
       <c r="O28" s="95"/>
       <c r="P28" s="96">
         <f t="shared" si="5"/>
-        <v>178010.21126250003</v>
+        <v>248982.69251250001</v>
       </c>
       <c r="Q28" s="97">
         <f t="shared" si="6"/>
-        <v>141944.96250000002</v>
+        <v>42750</v>
       </c>
       <c r="R28" s="158">
         <f t="shared" si="11"/>
@@ -4811,11 +4822,11 @@
       <c r="C29" s="133" t="s">
         <v>45</v>
       </c>
-      <c r="D29" s="218">
+      <c r="D29" s="226">
         <v>10</v>
       </c>
-      <c r="E29" s="221" t="s">
-        <v>111</v>
+      <c r="E29" s="229" t="s">
+        <v>110</v>
       </c>
       <c r="F29" s="135">
         <f>7.73/2</f>
@@ -4839,7 +4850,7 @@
         <v>428596.72</v>
       </c>
       <c r="L29" s="117" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M29" s="123">
         <f t="shared" si="0"/>
@@ -4852,11 +4863,11 @@
       <c r="O29" s="95"/>
       <c r="P29" s="96">
         <f t="shared" si="5"/>
-        <v>182590.59096750003</v>
+        <v>255389.26471750002</v>
       </c>
       <c r="Q29" s="97">
         <f t="shared" si="6"/>
-        <v>145597.34750000003</v>
+        <v>43850.000000000007</v>
       </c>
       <c r="R29" s="158">
         <f t="shared" si="11"/>
@@ -4864,11 +4875,11 @@
       </c>
       <c r="S29" s="138">
         <f>ROUND(SUM(M29:R29)+P30+Q30+R30,0) + U29</f>
-        <v>626438.36</v>
+        <v>571182.36</v>
       </c>
       <c r="T29" s="138">
         <f t="shared" si="1"/>
-        <v>645231.35999999999</v>
+        <v>588317.36</v>
       </c>
       <c r="U29" s="31">
         <f>A29/100</f>
@@ -4877,14 +4888,14 @@
     </row>
     <row r="30" spans="1:22" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="154" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B30" s="130">
         <v>18</v>
       </c>
       <c r="C30" s="133"/>
-      <c r="D30" s="219"/>
-      <c r="E30" s="222"/>
+      <c r="D30" s="227"/>
+      <c r="E30" s="230"/>
       <c r="F30" s="135">
         <f>7.73/2</f>
         <v>3.8650000000000002</v>
@@ -4905,7 +4916,7 @@
         <v>0</v>
       </c>
       <c r="L30" s="117" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M30" s="123">
         <f t="shared" si="0"/>
@@ -4918,11 +4929,11 @@
       <c r="O30" s="95"/>
       <c r="P30" s="96">
         <f t="shared" si="5"/>
-        <v>165934.66476750001</v>
+        <v>232092.63851750002</v>
       </c>
       <c r="Q30" s="97">
         <f t="shared" si="6"/>
-        <v>132315.94750000001</v>
+        <v>39850.000000000007</v>
       </c>
       <c r="R30" s="158">
         <f t="shared" si="11"/>
@@ -4945,13 +4956,13 @@
         <v>12</v>
       </c>
       <c r="C31" s="133" t="s">
-        <v>76</v>
-      </c>
-      <c r="D31" s="218" t="s">
-        <v>95</v>
-      </c>
-      <c r="E31" s="218" t="s">
-        <v>112</v>
+        <v>75</v>
+      </c>
+      <c r="D31" s="226" t="s">
+        <v>94</v>
+      </c>
+      <c r="E31" s="226" t="s">
+        <v>111</v>
       </c>
       <c r="F31" s="135">
         <f>12.13/3</f>
@@ -4974,7 +4985,7 @@
         <v>528133.37</v>
       </c>
       <c r="L31" s="117" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M31" s="123">
         <f t="shared" si="0"/>
@@ -4986,11 +4997,11 @@
       <c r="O31" s="95"/>
       <c r="P31" s="96">
         <f t="shared" si="5"/>
-        <v>177108.01526000001</v>
+        <v>247720.79192666669</v>
       </c>
       <c r="Q31" s="97">
         <f t="shared" si="6"/>
-        <v>141225.55333333334</v>
+        <v>42533.333333333343</v>
       </c>
       <c r="R31" s="158">
         <f t="shared" si="11"/>
@@ -4998,11 +5009,11 @@
       </c>
       <c r="S31" s="138">
         <f>ROUND(SUM(M31:R31)+P32+P33+Q32+Q33+R32+R33,0) + U31</f>
-        <v>1086433.3700000001</v>
+        <v>1001469.37</v>
       </c>
       <c r="T31" s="138">
         <f t="shared" si="1"/>
-        <v>1119026.3700000001</v>
+        <v>1031513.37</v>
       </c>
       <c r="U31" s="31">
         <f>A31/100</f>
@@ -5011,14 +5022,14 @@
     </row>
     <row r="32" spans="1:22" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="154" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B32" s="130">
         <v>3</v>
       </c>
       <c r="C32" s="134"/>
-      <c r="D32" s="220"/>
-      <c r="E32" s="220"/>
+      <c r="D32" s="228"/>
+      <c r="E32" s="228"/>
       <c r="F32" s="135">
         <f>12.13/3</f>
         <v>4.0433333333333339</v>
@@ -5047,11 +5058,11 @@
       <c r="O32" s="95"/>
       <c r="P32" s="96">
         <f t="shared" si="5"/>
-        <v>185435.97836000004</v>
+        <v>259369.10502666672</v>
       </c>
       <c r="Q32" s="97">
         <f t="shared" si="6"/>
-        <v>147866.25333333336</v>
+        <v>44533.333333333343</v>
       </c>
       <c r="R32" s="158">
         <f t="shared" si="11"/>
@@ -5068,14 +5079,14 @@
     </row>
     <row r="33" spans="1:21" ht="14.65" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="170" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B33" s="150">
         <v>16</v>
       </c>
       <c r="C33" s="134"/>
-      <c r="D33" s="220"/>
-      <c r="E33" s="220"/>
+      <c r="D33" s="228"/>
+      <c r="E33" s="228"/>
       <c r="F33" s="135">
         <f>12.13/3</f>
         <v>4.0433333333333339</v>
@@ -5104,11 +5115,11 @@
       <c r="O33" s="175"/>
       <c r="P33" s="176">
         <f t="shared" si="5"/>
-        <v>173360.43186500002</v>
+        <v>242479.05103166669</v>
       </c>
       <c r="Q33" s="177">
         <f t="shared" si="6"/>
-        <v>138237.23833333337</v>
+        <v>41633.333333333343</v>
       </c>
       <c r="R33" s="184">
         <f t="shared" si="11"/>
@@ -5124,13 +5135,13 @@
       <c r="U33" s="31"/>
     </row>
     <row r="34" spans="1:21" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="213" t="s">
+      <c r="A34" s="223" t="s">
         <v>44</v>
       </c>
-      <c r="B34" s="214"/>
-      <c r="C34" s="214"/>
-      <c r="D34" s="214"/>
-      <c r="E34" s="215"/>
+      <c r="B34" s="224"/>
+      <c r="C34" s="224"/>
+      <c r="D34" s="224"/>
+      <c r="E34" s="225"/>
       <c r="F34" s="179"/>
       <c r="G34" s="179"/>
       <c r="H34" s="180">
@@ -5161,11 +5172,11 @@
       <c r="O34" s="182"/>
       <c r="P34" s="182">
         <f>SUM(P10:P33)</f>
-        <v>4163981.5500000007</v>
+        <v>5824156.5500000007</v>
       </c>
       <c r="Q34" s="183">
         <f>SUM(Q10:Q33)</f>
-        <v>3320350</v>
+        <v>1000000.0000000001</v>
       </c>
       <c r="R34" s="185">
         <f>SUM(R10:R33)</f>
@@ -5173,11 +5184,11 @@
       </c>
       <c r="S34" s="181">
         <f>SUM(S10:S31)</f>
-        <v>7862066.5599999996</v>
+        <v>7201892.5599999996</v>
       </c>
       <c r="T34" s="181">
         <f>SUM(T10:T31)</f>
-        <v>8097928.5599999996</v>
+        <v>7417949.5599999996</v>
       </c>
     </row>
     <row r="35" spans="1:21" ht="22.15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5185,7 +5196,7 @@
       <c r="F35" s="37"/>
       <c r="G35" s="37"/>
       <c r="K35" s="102" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L35" s="102">
         <f>SUMIF(L10:L33,"B",K10:K33)</f>
@@ -5193,15 +5204,15 @@
       </c>
     </row>
     <row r="36" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A36" s="209"/>
-      <c r="B36" s="209"/>
+      <c r="A36" s="233"/>
+      <c r="B36" s="233"/>
       <c r="C36" s="128"/>
       <c r="D36" s="128"/>
-      <c r="H36" s="210"/>
+      <c r="H36" s="234"/>
       <c r="I36" s="129"/>
-      <c r="J36" s="211"/>
+      <c r="J36" s="235"/>
       <c r="K36" s="102" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="L36" s="102">
         <f>SUMIF(L10:L33,"E",K10:K33)</f>
@@ -5209,13 +5220,13 @@
       </c>
     </row>
     <row r="37" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A37" s="209"/>
-      <c r="B37" s="209"/>
+      <c r="A37" s="233"/>
+      <c r="B37" s="233"/>
       <c r="C37" s="128"/>
       <c r="D37" s="128"/>
-      <c r="H37" s="210"/>
+      <c r="H37" s="234"/>
       <c r="I37" s="129"/>
-      <c r="J37" s="211"/>
+      <c r="J37" s="235"/>
       <c r="K37" s="103"/>
       <c r="L37" s="103"/>
     </row>
@@ -5243,6 +5254,23 @@
     </row>
   </sheetData>
   <mergeCells count="33">
+    <mergeCell ref="R8:R9"/>
+    <mergeCell ref="L8:L9"/>
+    <mergeCell ref="A36:B37"/>
+    <mergeCell ref="H36:H37"/>
+    <mergeCell ref="J36:J37"/>
+    <mergeCell ref="K2:M2"/>
+    <mergeCell ref="A34:E34"/>
+    <mergeCell ref="O8:O9"/>
+    <mergeCell ref="G8:G9"/>
+    <mergeCell ref="F8:F9"/>
+    <mergeCell ref="D27:D28"/>
+    <mergeCell ref="D29:D30"/>
+    <mergeCell ref="D31:D33"/>
+    <mergeCell ref="E31:E33"/>
+    <mergeCell ref="E29:E30"/>
+    <mergeCell ref="E27:E28"/>
+    <mergeCell ref="F2:G2"/>
     <mergeCell ref="H1:S1"/>
     <mergeCell ref="N8:N9"/>
     <mergeCell ref="J8:J9"/>
@@ -5259,23 +5287,6 @@
     <mergeCell ref="C8:C9"/>
     <mergeCell ref="D8:D9"/>
     <mergeCell ref="Q2:S2"/>
-    <mergeCell ref="K2:M2"/>
-    <mergeCell ref="A34:E34"/>
-    <mergeCell ref="O8:O9"/>
-    <mergeCell ref="G8:G9"/>
-    <mergeCell ref="F8:F9"/>
-    <mergeCell ref="D27:D28"/>
-    <mergeCell ref="D29:D30"/>
-    <mergeCell ref="D31:D33"/>
-    <mergeCell ref="E31:E33"/>
-    <mergeCell ref="E29:E30"/>
-    <mergeCell ref="E27:E28"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="R8:R9"/>
-    <mergeCell ref="L8:L9"/>
-    <mergeCell ref="A36:B37"/>
-    <mergeCell ref="H36:H37"/>
-    <mergeCell ref="J36:J37"/>
   </mergeCells>
   <phoneticPr fontId="21" type="noConversion"/>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5290,7 +5301,7 @@
   <sheetData>
     <row r="3" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C3" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>
